--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -1257,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1335,26 +1335,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>Robotics Adoption Hubs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/semiconductors-and-components-for-smart-electronic-platforms/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-23 10:38</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46076.44305555556</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1363,25 +1363,19 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20/02/2026</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46073</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>01/04/2026                              11:00</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£18.5 million</t>
+          <t>£7.5 million</t>
         </is>
       </c>
       <c r="N2" s="1" t="n">
@@ -1391,26 +1385,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iX Challenge - Dry ice alternatives that maintain LUSH spa's sensory and theatrical magic</t>
+          <t>Robotics Adoption Central Convening Body</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-dry-ice-alternatives-maintaining-lush-spas-sensory-and-theatrical-magic/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-23 10:38</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46076.44305555556</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -1419,25 +1413,19 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>23/02/2026</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>46076</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>17/04/2026                              23:59</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46129.99930555555</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£99</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N3" s="1" t="n">
@@ -1452,21 +1440,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>iX Challenge - Enabling regional carbon dioxide utilisation in Southwest Wales through geospatial intelligence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/contracts-for-innovation-industrial-human-relevant-drug-models/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-enabling-regional-carbon-dioxide-utilisation-southwest-wales/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-21 10:13</t>
+          <t>2026-02-24 10:36</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46074.42569444444</v>
+        <v>46077.44166666667</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -1477,23 +1465,23 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>15/04/2026                              11:00</t>
+          <t>23/04/2026                              23:59</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46135.99930555555</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N4" s="1" t="n">
@@ -1503,7 +1491,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1513,16 +1501,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/semiconductors-and-components-for-smart-electronic-platforms/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-23 10:38</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46076.44305555556</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1531,11 +1519,17 @@
       <c r="H5" t="b">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>46073</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>01/04/2026                              11:00</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
@@ -1543,7 +1537,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£18.5 million</t>
         </is>
       </c>
       <c r="N5" s="1" t="n">
@@ -1558,21 +1552,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AI Management Practitioner Training</t>
+          <t>iX Challenge - Dry ice alternatives that maintain LUSH spa's sensory and theatrical magic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ai-management-practitioner-training/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-dry-ice-alternatives-maintaining-lush-spas-sensory-and-theatrical-magic/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-20 10:25</t>
+          <t>2026-02-23 10:38</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46073.43402777778</v>
+        <v>46076.44305555556</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1581,11 +1575,27 @@
       <c r="H6" t="b">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>17/04/2026                              23:59</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>46129.99930555555</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>£99</t>
+        </is>
+      </c>
       <c r="N6" s="1" t="n">
         <v>46071</v>
       </c>
@@ -1598,21 +1608,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Southwest Wales Net Zero Industry Launchpad Round 2 - Call for challenge holders</t>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/southwest-wales-net-zero-industry-launchpad-round-2-call-for-challenge-holders/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/contracts-for-innovation-industrial-human-relevant-drug-models/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-18 10:32</t>
+          <t>2026-02-21 10:13</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46071.43888888889</v>
+        <v>46074.42569444444</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -1623,26 +1633,172 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>15/04/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Semiconductors and components for smart electronic platforms</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:32</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46073.43888888889</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Wednesday 1 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AI Management Practitioner Training</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/ai-management-practitioner-training/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:25</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46073.43402777778</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Southwest Wales Net Zero Industry Launchpad Round 2 - Call for challenge holders</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/southwest-wales-net-zero-industry-launchpad-round-2-call-for-challenge-holders/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-18 10:32</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46071.43888888889</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>18/02/2026</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J10" s="1" t="n">
         <v>46071</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>13/03/2026                              00:00</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="L10" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>£25,000</t>
         </is>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N10" s="1" t="n">
         <v>46071</v>
       </c>
     </row>
@@ -1687,13 +1843,13 @@
         <v>46071</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2211,7 +2367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N256"/>
+  <dimension ref="A1:N259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9825,26 +9981,26 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
+          <t>iX Challenge - Enabling regional carbon dioxide utilisation in Southwest Wales through geospatial intelligence</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-enabling-regional-carbon-dioxide-utilisation-southwest-wales/</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-02-24 10:36</t>
         </is>
       </c>
       <c r="E152" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46077.44166666667</v>
       </c>
       <c r="F152" t="b">
         <v>1</v>
@@ -9853,23 +10009,29 @@
       <c r="H152" t="b">
         <v>0</v>
       </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="J152" s="1" t="n">
+        <v>46077</v>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>23/04/2026                              23:59</t>
         </is>
       </c>
       <c r="L152" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>46135.99930555555</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N152" s="1" t="n">
-        <v>45819</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="153">
@@ -9880,12 +10042,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 2</t>
+          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9907,15 +10069,15 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Thursday 24 July 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L153" s="1" t="n">
-        <v>45862.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N153" s="1" t="n">
@@ -9930,12 +10092,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
+          <t>ADOPT Facilitator Support Grant: Round 2</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9957,15 +10119,15 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 24 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L154" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45862.45833333334</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N154" s="1" t="n">
@@ -9980,12 +10142,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>New Innovators in Marine and Maritime, Great South West</t>
+          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -10015,7 +10177,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N155" s="1" t="n">
@@ -10030,12 +10192,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>New Innovators in Marine and Maritime, Great South West</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -10057,15 +10219,15 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Thursday 4 September 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L156" s="1" t="n">
-        <v>45904.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N156" s="1" t="n">
@@ -10080,12 +10242,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – June 2025</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -10107,13 +10269,17 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Thursday 4 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L157" s="1" t="n">
-        <v>45826.45833333334</v>
-      </c>
-      <c r="M157" t="inlineStr"/>
+        <v>45904.45833333334</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N157" s="1" t="n">
         <v>45819</v>
       </c>
@@ -10126,12 +10292,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>ATI Programme strategic batch: EoI – June 2025</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10153,17 +10319,13 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L158" s="1" t="n">
-        <v>45840.45833333334</v>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45826.45833333334</v>
+      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" s="1" t="n">
         <v>45819</v>
       </c>
@@ -10176,12 +10338,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10203,15 +10365,15 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L159" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N159" s="1" t="n">
@@ -10226,12 +10388,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10276,12 +10438,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
+          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10303,15 +10465,15 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L161" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N161" s="1" t="n">
@@ -10326,12 +10488,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
+          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10353,15 +10515,15 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L162" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N162" s="1" t="n">
@@ -10376,12 +10538,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
+          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10403,15 +10565,15 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L163" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N163" s="1" t="n">
@@ -10426,12 +10588,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Clean Air, Phase 3</t>
+          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10476,12 +10638,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
+          <t>Contracts for Innovation: Clean Air, Phase 3</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10503,15 +10665,15 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L165" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N165" s="1" t="n">
@@ -10526,12 +10688,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10561,7 +10723,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N166" s="1" t="n">
@@ -10576,12 +10738,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Canada-UK Semiconductors</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10603,15 +10765,15 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L167" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N167" s="1" t="n">
@@ -10626,12 +10788,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
+          <t>Canada-UK Semiconductors</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10653,15 +10815,15 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L168" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N168" s="1" t="n">
@@ -10676,12 +10838,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Innovate UK innovation loans future economy: Round 21</t>
+          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10711,7 +10873,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N169" s="1" t="n">
@@ -10726,12 +10888,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
+          <t>Innovate UK innovation loans future economy: Round 21</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10753,15 +10915,15 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L170" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N170" s="1" t="n">
@@ -10776,12 +10938,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
+          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10826,12 +10988,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
+          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10853,15 +11015,15 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L172" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N172" s="1" t="n">
@@ -10876,12 +11038,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 1</t>
+          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10903,15 +11065,15 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L173" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N173" s="1" t="n">
@@ -10926,12 +11088,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
+          <t>Full ADOPT Grant: Round 1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10953,11 +11115,17 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L174" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N174" s="1" t="n">
         <v>45819</v>
       </c>
@@ -10970,12 +11138,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee Extension</t>
+          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11014,21 +11182,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
+          <t>Horizon Europe Guarantee Extension</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025-06-16 22:04</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E176" s="1" t="n">
-        <v>45824.91944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F176" t="b">
         <v>1</v>
@@ -11041,17 +11209,11 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L176" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>£8,500</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
       <c r="N176" s="1" t="n">
         <v>45819</v>
       </c>
@@ -11064,21 +11226,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-16 22:04</t>
         </is>
       </c>
       <c r="E177" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45824.91944444444</v>
       </c>
       <c r="F177" t="b">
         <v>1</v>
@@ -11091,19 +11253,19 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L177" s="1" t="n">
-        <v>45889.45833333334</v>
+        <v>45917.45833333334</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N177" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="178">
@@ -11114,12 +11276,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 2</t>
+          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11149,7 +11311,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N178" s="1" t="n">
@@ -11164,21 +11326,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 22</t>
+          <t>Full ADOPT Grant Round 2</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025-07-03 08:52</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E179" s="1" t="n">
-        <v>45841.36944444444</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F179" t="b">
         <v>1</v>
@@ -11191,19 +11353,19 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L179" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N179" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="180">
@@ -11214,21 +11376,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Growth Catalyst Early Stage: New Innovators</t>
+          <t>Innovate UK Innovation Loans Round 22</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-07-03 08:52</t>
         </is>
       </c>
       <c r="E180" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45841.36944444444</v>
       </c>
       <c r="F180" t="b">
         <v>1</v>
@@ -11241,15 +11403,15 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Wednesday 6 August 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L180" s="1" t="n">
-        <v>45875.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N180" s="1" t="n">
@@ -11264,12 +11426,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – July 2025</t>
+          <t>Growth Catalyst Early Stage: New Innovators</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11291,13 +11453,17 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Wednesday 23 July 2025 11:00am</t>
+          <t>Wednesday 6 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L181" s="1" t="n">
-        <v>45861.45833333334</v>
-      </c>
-      <c r="M181" t="inlineStr"/>
+        <v>45875.45833333334</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>£50,000</t>
+        </is>
+      </c>
       <c r="N181" s="1" t="n">
         <v>45840</v>
       </c>
@@ -11310,21 +11476,21 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
+          <t>ATI Programme strategic batch: EoI – July 2025</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E182" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F182" t="b">
         <v>1</v>
@@ -11337,19 +11503,15 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 23 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L182" s="1" t="n">
-        <v>45896.45833333334</v>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+        <v>45861.45833333334</v>
+      </c>
+      <c r="M182" t="inlineStr"/>
       <c r="N182" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="183">
@@ -11360,12 +11522,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11410,12 +11572,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11460,12 +11622,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Future Flight: Regional Demonstrator 2</t>
+          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11487,15 +11649,15 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Thursday 17 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L185" s="1" t="n">
-        <v>45855.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N185" s="1" t="n">
@@ -11510,21 +11672,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies</t>
+          <t>Future Flight: Regional Demonstrator 2</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E186" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F186" t="b">
         <v>1</v>
@@ -11537,15 +11699,15 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Thursday 17 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L186" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45855.45833333334</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N186" s="1" t="n">
@@ -11560,12 +11722,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11587,15 +11749,15 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L187" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N187" s="1" t="n">
@@ -11610,12 +11772,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11645,7 +11807,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N188" s="1" t="n">
@@ -11660,21 +11822,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 3</t>
+          <t>DRIVE35 Innovation Fund: Collaborate</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025-07-25 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E189" s="1" t="n">
-        <v>45863.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F189" t="b">
         <v>1</v>
@@ -11687,19 +11849,19 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L189" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N189" s="1" t="n">
-        <v>45861</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="190">
@@ -11710,21 +11872,21 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sovereign AI - Proof of concept</t>
+          <t>ADOPT Facilitator Support Grant: Round 3</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025-08-07 08:21</t>
+          <t>2025-07-25 08:20</t>
         </is>
       </c>
       <c r="E190" s="1" t="n">
-        <v>45876.34791666667</v>
+        <v>45863.34722222222</v>
       </c>
       <c r="F190" t="b">
         <v>1</v>
@@ -11737,19 +11899,19 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L190" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>£120,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N190" s="1" t="n">
-        <v>45875</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="191">
@@ -11760,21 +11922,21 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
+          <t>Sovereign AI - Proof of concept</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-08-07 08:21</t>
         </is>
       </c>
       <c r="E191" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45876.34791666667</v>
       </c>
       <c r="F191" t="b">
         <v>1</v>
@@ -11787,19 +11949,19 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L191" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£120,000</t>
         </is>
       </c>
       <c r="N191" s="1" t="n">
-        <v>45882</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="192">
@@ -11810,12 +11972,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11845,7 +12007,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>£4.5 million</t>
+          <t>£8.0 million</t>
         </is>
       </c>
       <c r="N192" s="1" t="n">
@@ -11860,12 +12022,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11895,7 +12057,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£4.5 million</t>
         </is>
       </c>
       <c r="N193" s="1" t="n">
@@ -11910,21 +12072,21 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025-08-26 08:20</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E194" s="1" t="n">
-        <v>45895.34722222222</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F194" t="b">
         <v>1</v>
@@ -11937,19 +12099,19 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L194" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N194" s="1" t="n">
-        <v>45889</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="195">
@@ -11960,21 +12122,21 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 3</t>
+          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025-08-27 08:18</t>
+          <t>2025-08-26 08:20</t>
         </is>
       </c>
       <c r="E195" s="1" t="n">
-        <v>45896.34583333333</v>
+        <v>45895.34722222222</v>
       </c>
       <c r="F195" t="b">
         <v>1</v>
@@ -11987,11 +12149,11 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L195" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -11999,7 +12161,7 @@
         </is>
       </c>
       <c r="N195" s="1" t="n">
-        <v>45896</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="196">
@@ -12010,21 +12172,21 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – September 2025</t>
+          <t>Full ADOPT Grant Round 3</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025-09-01 08:20</t>
+          <t>2025-08-27 08:18</t>
         </is>
       </c>
       <c r="E196" s="1" t="n">
-        <v>45901.34722222222</v>
+        <v>45896.34583333333</v>
       </c>
       <c r="F196" t="b">
         <v>1</v>
@@ -12037,13 +12199,17 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L196" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M196" t="inlineStr"/>
+        <v>45945.45833333334</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N196" s="1" t="n">
         <v>45896</v>
       </c>
@@ -12056,21 +12222,21 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
+          <t>ATI Programme strategic batch: EoI – September 2025</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025-09-02 08:19</t>
+          <t>2025-09-01 08:20</t>
         </is>
       </c>
       <c r="E197" s="1" t="n">
-        <v>45902.34652777778</v>
+        <v>45901.34722222222</v>
       </c>
       <c r="F197" t="b">
         <v>1</v>
@@ -12083,17 +12249,13 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L197" s="1" t="n">
-        <v>45966.45833333334</v>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45917.45833333334</v>
+      </c>
+      <c r="M197" t="inlineStr"/>
       <c r="N197" s="1" t="n">
         <v>45896</v>
       </c>
@@ -12106,21 +12268,21 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 4</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025-09-04 08:18</t>
+          <t>2025-09-02 08:19</t>
         </is>
       </c>
       <c r="E198" s="1" t="n">
-        <v>45904.34583333333</v>
+        <v>45902.34652777778</v>
       </c>
       <c r="F198" t="b">
         <v>1</v>
@@ -12133,19 +12295,19 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L198" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N198" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="199">
@@ -12156,21 +12318,21 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 23</t>
+          <t>ADOPT Facilitator Support Grant: Round 4</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025-09-05 08:18</t>
+          <t>2025-09-04 08:18</t>
         </is>
       </c>
       <c r="E199" s="1" t="n">
-        <v>45905.34583333333</v>
+        <v>45904.34583333333</v>
       </c>
       <c r="F199" t="b">
         <v>1</v>
@@ -12183,15 +12345,15 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L199" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N199" s="1" t="n">
@@ -12206,21 +12368,21 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
+          <t>Innovate UK Innovation Loans Round 23</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025-09-12 08:17</t>
+          <t>2025-09-05 08:18</t>
         </is>
       </c>
       <c r="E200" s="1" t="n">
-        <v>45912.34513888889</v>
+        <v>45905.34583333333</v>
       </c>
       <c r="F200" t="b">
         <v>1</v>
@@ -12233,19 +12395,19 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Tuesday 28 October 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L200" s="1" t="n">
-        <v>45958.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N200" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="201">
@@ -12256,21 +12418,21 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
+          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025-09-16 08:19</t>
+          <t>2025-09-12 08:17</t>
         </is>
       </c>
       <c r="E201" s="1" t="n">
-        <v>45916.34652777778</v>
+        <v>45912.34513888889</v>
       </c>
       <c r="F201" t="b">
         <v>1</v>
@@ -12283,15 +12445,15 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Tuesday 28 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L201" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45958.45833333334</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N201" s="1" t="n">
@@ -12306,21 +12468,21 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025-09-17 08:18</t>
+          <t>2025-09-16 08:19</t>
         </is>
       </c>
       <c r="E202" s="1" t="n">
-        <v>45917.34583333333</v>
+        <v>45916.34652777778</v>
       </c>
       <c r="F202" t="b">
         <v>1</v>
@@ -12333,17 +12495,19 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr"/>
+          <t>Wednesday 15 October 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L202" s="1" t="n">
+        <v>45945.45833333334</v>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="N202" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="203">
@@ -12354,21 +12518,21 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025-09-18 08:17</t>
+          <t>2025-09-17 08:18</t>
         </is>
       </c>
       <c r="E203" s="1" t="n">
-        <v>45918.34513888889</v>
+        <v>45917.34583333333</v>
       </c>
       <c r="F203" t="b">
         <v>1</v>
@@ -12381,15 +12545,13 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Thursday 4 December 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L203" s="1" t="n">
-        <v>45995.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N203" s="1" t="n">
@@ -12404,21 +12566,21 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Resource efficiency for resilience and sustainability FS</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025-09-20 08:16</t>
+          <t>2025-09-18 08:17</t>
         </is>
       </c>
       <c r="E204" s="1" t="n">
-        <v>45920.34444444445</v>
+        <v>45918.34513888889</v>
       </c>
       <c r="F204" t="b">
         <v>1</v>
@@ -12431,15 +12593,15 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Monday 3 November 2025 11:00am</t>
+          <t>Thursday 4 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L204" s="1" t="n">
-        <v>45964.45833333334</v>
+        <v>45995.45833333334</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N204" s="1" t="n">
@@ -12454,21 +12616,21 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
+          <t>Resource efficiency for resilience and sustainability FS</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025-09-23 08:18</t>
+          <t>2025-09-20 08:16</t>
         </is>
       </c>
       <c r="E205" s="1" t="n">
-        <v>45923.34583333333</v>
+        <v>45920.34444444445</v>
       </c>
       <c r="F205" t="b">
         <v>1</v>
@@ -12481,15 +12643,15 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Monday 3 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L205" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45964.45833333334</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N205" s="1" t="n">
@@ -12504,21 +12666,21 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 4</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025-09-29 08:20</t>
+          <t>2025-09-23 08:18</t>
         </is>
       </c>
       <c r="E206" s="1" t="n">
-        <v>45929.34722222222</v>
+        <v>45923.34583333333</v>
       </c>
       <c r="F206" t="b">
         <v>1</v>
@@ -12531,19 +12693,19 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Wednesday 3 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L206" s="1" t="n">
-        <v>45994.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N206" s="1" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="207">
@@ -12554,21 +12716,21 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Eureka GlobalStars Japan 2026</t>
+          <t>Farming Innovation Programme: Feasibility Round 4</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025-10-03 08:17</t>
+          <t>2025-09-29 08:20</t>
         </is>
       </c>
       <c r="E207" s="1" t="n">
-        <v>45933.34513888889</v>
+        <v>45929.34722222222</v>
       </c>
       <c r="F207" t="b">
         <v>1</v>
@@ -12581,19 +12743,19 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Wednesday 21 January 2026 11:00am</t>
+          <t>Wednesday 3 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L207" s="1" t="n">
-        <v>46043.45833333334</v>
+        <v>45994.45833333334</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N207" s="1" t="n">
-        <v>45931</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="208">
@@ -12604,21 +12766,21 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Feasibility studies 2</t>
+          <t>Eureka GlobalStars Japan 2026</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025-10-10 08:18</t>
+          <t>2025-10-03 08:17</t>
         </is>
       </c>
       <c r="E208" s="1" t="n">
-        <v>45940.34583333333</v>
+        <v>45933.34513888889</v>
       </c>
       <c r="F208" t="b">
         <v>1</v>
@@ -12631,19 +12793,19 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 21 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L208" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46043.45833333334</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£600,000</t>
         </is>
       </c>
       <c r="N208" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="209">
@@ -12654,21 +12816,21 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – October 2025</t>
+          <t>CAM Pathfinder: Feasibility studies 2</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025-10-14 08:17</t>
+          <t>2025-10-10 08:18</t>
         </is>
       </c>
       <c r="E209" s="1" t="n">
-        <v>45944.34513888889</v>
+        <v>45940.34583333333</v>
       </c>
       <c r="F209" t="b">
         <v>1</v>
@@ -12681,13 +12843,17 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L209" s="1" t="n">
-        <v>45952.45833333334</v>
-      </c>
-      <c r="M209" t="inlineStr"/>
+        <v>45987.45833333334</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N209" s="1" t="n">
         <v>45938</v>
       </c>
@@ -12700,21 +12866,21 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Enable</t>
+          <t>ATI Programme strategic batch EoI – October 2025</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-14 08:17</t>
         </is>
       </c>
       <c r="E210" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45944.34513888889</v>
       </c>
       <c r="F210" t="b">
         <v>1</v>
@@ -12727,19 +12893,15 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L210" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>£4.0 million</t>
-        </is>
-      </c>
+        <v>45952.45833333334</v>
+      </c>
+      <c r="M210" t="inlineStr"/>
       <c r="N210" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="211">
@@ -12750,12 +12912,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Demonstrate</t>
+          <t>CAM Pathfinder: Enable</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -12785,7 +12947,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N211" s="1" t="n">
@@ -12800,21 +12962,21 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
+          <t>CAM Pathfinder: Demonstrate</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025-10-16 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E212" s="1" t="n">
-        <v>45946.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F212" t="b">
         <v>1</v>
@@ -12827,15 +12989,15 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L212" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N212" s="1" t="n">
@@ -12850,21 +13012,21 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 5</t>
+          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025-10-17 08:19</t>
+          <t>2025-10-16 08:19</t>
         </is>
       </c>
       <c r="E213" s="1" t="n">
-        <v>45947.34652777778</v>
+        <v>45946.34652777778</v>
       </c>
       <c r="F213" t="b">
         <v>1</v>
@@ -12885,7 +13047,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N213" s="1" t="n">
@@ -12900,21 +13062,21 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Battery Innovation Feasibility Studies Round 1</t>
+          <t>ADOPT Facilitator Support Grant: Round 5</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-17 08:19</t>
         </is>
       </c>
       <c r="E214" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45947.34652777778</v>
       </c>
       <c r="F214" t="b">
         <v>1</v>
@@ -12927,15 +13089,15 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L214" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N214" s="1" t="n">
@@ -12950,12 +13112,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Battery Innovation Concept Development Round 1</t>
+          <t>Battery Innovation Feasibility Studies Round 1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -12985,7 +13147,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N215" s="1" t="n">
@@ -13000,21 +13162,21 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>The Agentic AI Pioneers Prize</t>
+          <t>Battery Innovation Concept Development Round 1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025-10-21 08:20</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E216" s="1" t="n">
-        <v>45951.34722222222</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F216" t="b">
         <v>1</v>
@@ -13027,13 +13189,17 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L216" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M216" t="inlineStr"/>
+        <v>46008.45833333334</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N216" s="1" t="n">
         <v>45945</v>
       </c>
@@ -13046,21 +13212,21 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy efficiency – industrial research</t>
+          <t>The Agentic AI Pioneers Prize</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-21 08:20</t>
         </is>
       </c>
       <c r="E217" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45951.34722222222</v>
       </c>
       <c r="F217" t="b">
         <v>1</v>
@@ -13073,19 +13239,15 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L217" s="1" t="n">
-        <v>46001.45833333334</v>
-      </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>£1.0 million</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M217" t="inlineStr"/>
       <c r="N217" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="218">
@@ -13096,12 +13258,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
+          <t>MSI: SME resource and energy efficiency – industrial research</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -13131,7 +13293,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N218" s="1" t="n">
@@ -13146,21 +13308,21 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 4</t>
+          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025-10-23 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E219" s="1" t="n">
-        <v>45953.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F219" t="b">
         <v>1</v>
@@ -13181,7 +13343,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N219" s="1" t="n">
@@ -13196,21 +13358,21 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 24</t>
+          <t>Full ADOPT Grant Round 4</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025-10-24 08:19</t>
+          <t>2025-10-23 08:19</t>
         </is>
       </c>
       <c r="E220" s="1" t="n">
-        <v>45954.34652777778</v>
+        <v>45953.34652777778</v>
       </c>
       <c r="F220" t="b">
         <v>1</v>
@@ -13223,15 +13385,15 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Wednesday 7 January 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L220" s="1" t="n">
-        <v>46029.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N220" s="1" t="n">
@@ -13246,21 +13408,21 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
+          <t>Innovate UK Innovation Loans Round 24</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025-10-25 08:16</t>
+          <t>2025-10-24 08:19</t>
         </is>
       </c>
       <c r="E221" s="1" t="n">
-        <v>45955.34444444445</v>
+        <v>45954.34652777778</v>
       </c>
       <c r="F221" t="b">
         <v>1</v>
@@ -13273,15 +13435,15 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 7 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L221" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46029.45833333334</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N221" s="1" t="n">
@@ -13296,21 +13458,21 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility Studies</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025-10-31 08:18</t>
+          <t>2025-10-25 08:16</t>
         </is>
       </c>
       <c r="E222" s="1" t="n">
-        <v>45961.34583333333</v>
+        <v>45955.34444444445</v>
       </c>
       <c r="F222" t="b">
         <v>1</v>
@@ -13323,19 +13485,19 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L222" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N222" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="223">
@@ -13346,21 +13508,21 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
+          <t>National Materials Innovation Programme: Feasibility Studies</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-31 08:18</t>
         </is>
       </c>
       <c r="E223" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45961.34583333333</v>
       </c>
       <c r="F223" t="b">
         <v>1</v>
@@ -13373,15 +13535,15 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L223" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>£3.4 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N223" s="1" t="n">
@@ -13396,12 +13558,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Increasing EV charging capacity on the strategic road network</t>
+          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -13423,15 +13585,15 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L224" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£3.4 million</t>
         </is>
       </c>
       <c r="N224" s="1" t="n">
@@ -13446,21 +13608,21 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
+          <t>Increasing EV charging capacity on the strategic road network</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E225" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F225" t="b">
         <v>1</v>
@@ -13473,19 +13635,19 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L225" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N225" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="226">
@@ -13496,12 +13658,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -13531,7 +13693,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N226" s="1" t="n">
@@ -13546,12 +13708,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – November 2025</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -13573,13 +13735,17 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L227" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M227" t="inlineStr"/>
+        <v>46001.45833333334</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N227" s="1" t="n">
         <v>45966</v>
       </c>
@@ -13592,21 +13758,21 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
+          <t>ATI Programme strategic batch EoI – November 2025</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025-11-11 08:19</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E228" s="1" t="n">
-        <v>45972.34652777778</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F228" t="b">
         <v>1</v>
@@ -13619,17 +13785,13 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L228" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>£750,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M228" t="inlineStr"/>
       <c r="N228" s="1" t="n">
         <v>45966</v>
       </c>
@@ -13642,21 +13804,21 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Women in Innovation Awards 2025/26</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-11-27 13:23</t>
+          <t>2025-11-11 08:19</t>
         </is>
       </c>
       <c r="E229" s="1" t="n">
-        <v>45988.55763888889</v>
+        <v>45972.34652777778</v>
       </c>
       <c r="F229" t="b">
         <v>1</v>
@@ -13669,19 +13831,19 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L229" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>£75,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N229" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="230">
@@ -13692,21 +13854,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
+          <t>Women in Innovation Awards 2025/26</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025-12-02 08:22</t>
+          <t>2025-11-27 13:23</t>
         </is>
       </c>
       <c r="E230" s="1" t="n">
-        <v>45993.34861111111</v>
+        <v>45988.55763888889</v>
       </c>
       <c r="F230" t="b">
         <v>1</v>
@@ -13727,7 +13889,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£75,000</t>
         </is>
       </c>
       <c r="N230" s="1" t="n">
@@ -13742,21 +13904,21 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025-12-11 08:22</t>
+          <t>2025-12-02 08:22</t>
         </is>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46002.34861111111</v>
+        <v>45993.34861111111</v>
       </c>
       <c r="F231" t="b">
         <v>1</v>
@@ -13769,19 +13931,19 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Tuesday 3 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L231" s="1" t="n">
-        <v>46056.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N231" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="232">
@@ -13792,21 +13954,21 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 5</t>
+          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025-12-12 08:22</t>
+          <t>2025-12-11 08:22</t>
         </is>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46003.34861111111</v>
+        <v>46002.34861111111</v>
       </c>
       <c r="F232" t="b">
         <v>1</v>
@@ -13819,15 +13981,15 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Tuesday 3 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L232" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46056.45833333334</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N232" s="1" t="n">
@@ -13842,21 +14004,21 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 6</t>
+          <t>Full ADOPT Grant: Round 5</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-12 08:22</t>
         </is>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46003.34861111111</v>
       </c>
       <c r="F233" t="b">
         <v>1</v>
@@ -13869,19 +14031,19 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L233" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N233" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="234">
@@ -13892,12 +14054,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
+          <t>ADOPT Facilitator Support Grant: Round 6</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -13919,15 +14081,15 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Thursday 7 May 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L234" s="1" t="n">
-        <v>46149.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N234" s="1" t="n">
@@ -13942,21 +14104,21 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – mid stage</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F235" t="b">
         <v>1</v>
@@ -13969,19 +14131,19 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Thursday 7 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L235" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N235" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="236">
@@ -13992,12 +14154,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – late stage</t>
+          <t>Energy catalyst round 11 – mid stage</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -14027,7 +14189,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N236" s="1" t="n">
@@ -14042,12 +14204,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – early stage</t>
+          <t>Energy catalyst round 11 – late stage</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -14077,7 +14239,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N237" s="1" t="n">
@@ -14092,12 +14254,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
+          <t>Energy catalyst round 11 – early stage</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -14119,15 +14281,15 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L238" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N238" s="1" t="n">
@@ -14142,12 +14304,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -14169,15 +14331,15 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L239" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N239" s="1" t="n">
@@ -14192,21 +14354,21 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 25</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-01-08 08:22</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46030.34861111111</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F240" t="b">
         <v>1</v>
@@ -14219,19 +14381,19 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L240" s="1" t="n">
-        <v>46085.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N240" s="1" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="241">
@@ -14242,21 +14404,21 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
+          <t>Innovate UK Innovation Loans Round 25</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-01-15 08:23</t>
+          <t>2026-01-08 08:22</t>
         </is>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46037.34930555556</v>
+        <v>46030.34861111111</v>
       </c>
       <c r="F241" t="b">
         <v>1</v>
@@ -14269,19 +14431,19 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Wednesday 11 February 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L241" s="1" t="n">
-        <v>46064.45833333334</v>
+        <v>46085.45833333334</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N241" s="1" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="242">
@@ -14292,21 +14454,21 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
+          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-01-20 08:24</t>
+          <t>2026-01-15 08:23</t>
         </is>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46042.35</v>
+        <v>46037.34930555556</v>
       </c>
       <c r="F242" t="b">
         <v>1</v>
@@ -14319,15 +14481,15 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 11 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L242" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46064.45833333334</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N242" s="1" t="n">
@@ -14342,21 +14504,21 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation FS</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-01-26 12:10</t>
+          <t>2026-01-20 08:24</t>
         </is>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46048.50694444445</v>
+        <v>46042.35</v>
       </c>
       <c r="F243" t="b">
         <v>1</v>
@@ -14369,19 +14531,19 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L243" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N243" s="1" t="n">
-        <v>46043</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="244">
@@ -14392,21 +14554,21 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
+          <t>Advanced manufacturing supply chain innovation FS</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-26 12:10</t>
         </is>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46048.50694444445</v>
       </c>
       <c r="F244" t="b">
         <v>1</v>
@@ -14419,19 +14581,19 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L244" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>£225,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N244" s="1" t="n">
-        <v>46050</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="245">
@@ -14442,12 +14604,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
+          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -14477,7 +14639,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£225,000</t>
         </is>
       </c>
       <c r="N245" s="1" t="n">
@@ -14492,21 +14654,21 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Robotics Adoption Programme skills development</t>
+          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-02-02 10:39</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46055.44375</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F246" t="b">
         <v>1</v>
@@ -14519,15 +14681,15 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L246" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N246" s="1" t="n">
@@ -14542,21 +14704,21 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
+          <t>Robotics Adoption Programme skills development</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-02-02 10:39</t>
         </is>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46055.44375</v>
       </c>
       <c r="F247" t="b">
         <v>1</v>
@@ -14569,15 +14731,15 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L247" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N247" s="1" t="n">
@@ -14592,12 +14754,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -14619,13 +14781,17 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L248" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M248" t="inlineStr"/>
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N248" s="1" t="n">
         <v>46050</v>
       </c>
@@ -14638,12 +14804,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -14684,21 +14850,21 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 6</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-02-09 10:53</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46062.45347222222</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F250" t="b">
         <v>1</v>
@@ -14711,19 +14877,15 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L250" s="1" t="n">
-        <v>46120.45833333334</v>
-      </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>£100,000</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M250" t="inlineStr"/>
       <c r="N250" s="1" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="251">
@@ -14734,21 +14896,21 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Zero Emission Flight Demonstrator Round 1</t>
+          <t>Full ADOPT Grant: Round 6</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-09 10:53</t>
         </is>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46062.45347222222</v>
       </c>
       <c r="F251" t="b">
         <v>1</v>
@@ -14761,19 +14923,19 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L251" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N251" s="1" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="252">
@@ -14784,12 +14946,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
+          <t>Zero Emission Flight Demonstrator Round 1</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -14811,15 +14973,15 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L252" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N252" s="1" t="n">
@@ -14834,12 +14996,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
+          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -14869,7 +15031,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>£10.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N253" s="1" t="n">
@@ -14884,21 +15046,21 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
+          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46066.44097222222</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F254" t="b">
         <v>1</v>
@@ -14911,15 +15073,15 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L254" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N254" s="1" t="n">
@@ -14934,21 +15096,21 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-02-17 10:40</t>
+          <t>2026-02-13 10:35</t>
         </is>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46070.44444444445</v>
+        <v>46066.44097222222</v>
       </c>
       <c r="F255" t="b">
         <v>1</v>
@@ -14969,7 +15131,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N255" s="1" t="n">
@@ -14984,21 +15146,21 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-17 10:40</t>
         </is>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46070.44444444445</v>
       </c>
       <c r="F256" t="b">
         <v>1</v>
@@ -15011,18 +15173,168 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L256" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>£200,000</t>
+        </is>
+      </c>
+      <c r="N256" s="1" t="n">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Semiconductors and components for smart electronic platforms</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:32</t>
+        </is>
+      </c>
+      <c r="E257" s="1" t="n">
+        <v>46073.43888888889</v>
+      </c>
+      <c r="F257" t="b">
+        <v>1</v>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="b">
+        <v>0</v>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
           <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
-      <c r="L256" s="1" t="n">
+      <c r="L257" s="1" t="n">
         <v>46113.45833333334</v>
       </c>
-      <c r="M256" t="inlineStr">
+      <c r="M257" t="inlineStr">
         <is>
           <t>£2.0 million</t>
         </is>
       </c>
-      <c r="N256" s="1" t="n">
+      <c r="N257" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Robotics Adoption Hubs</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:43</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="n">
+        <v>46077.44652777778</v>
+      </c>
+      <c r="F258" t="b">
+        <v>1</v>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="b">
+        <v>0</v>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L258" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>£7.5 million</t>
+        </is>
+      </c>
+      <c r="N258" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Robotics Adoption Central Convening Body</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:43</t>
+        </is>
+      </c>
+      <c r="E259" s="1" t="n">
+        <v>46077.44652777778</v>
+      </c>
+      <c r="F259" t="b">
+        <v>1</v>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="b">
+        <v>0</v>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L259" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N259" s="1" t="n">
         <v>46071</v>
       </c>
     </row>
@@ -15064,10 +15376,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
@@ -15077,10 +15389,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C3" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
@@ -15090,10 +15402,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C4" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -981,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1059,26 +1059,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/robotics-adoption-hubs/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-25 10:38</t>
+          <t>2026-02-26 10:40</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46078.44305555556</v>
+        <v>46079.44444444445</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1087,25 +1087,19 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>24/02/2026</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46077</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>15/04/2026                              11:00</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£38.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N2" s="1" t="n">
@@ -1120,21 +1114,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>ARIA: Universal Fabricators - concept papers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/robotics-adoption-central-convening-body/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-universal-fabricators-concept-papers/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-25 10:38</t>
+          <t>2026-02-26 10:34</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46078.44305555556</v>
+        <v>46079.44027777778</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -1145,23 +1139,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>46077</v>
+        <v>46069</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15/04/2026                              11:00</t>
+          <t>09/03/2026                              14:00</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46090.58333333334</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="N3" s="1" t="n">
@@ -1176,21 +1170,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iX Challenge: CCTV / AI Waste Monitoring for High Accuracy Recycling</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-cctv-ai-waste-monitoring-for-high-accuracy-recycling/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/adopt-facilitator-support-grant-round-7/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-25 10:38</t>
+          <t>2026-02-26 10:34</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46078.44305555556</v>
+        <v>46079.44027777778</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -1201,23 +1195,23 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>07/04/2026                              17:00</t>
+          <t>08/04/2026                              11:00</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46119.70833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N4" s="1" t="n">
@@ -1232,21 +1226,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iX Challenge: Digital Material Flow Mapping and Packaging Reduction</t>
+          <t>UK Defence Innovation Competition: Innovation Support to Operations Phase 3 (Cycle 7)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-digital-material-flow-mapping-and-packaging-reduction/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/uk-defence-innovation-competition-innovation-support-to-operations-phase-3-cycle-7/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-25 10:38</t>
+          <t>2026-02-26 10:34</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46078.44305555556</v>
+        <v>46079.44027777778</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1257,26 +1251,306 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12/05/2026                              12:00</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>46154.5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Countering Illegal Use of UAS Around Prisons and Sensitive Sites</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/countering-illegal-use-of-uas-around-prisons-and-sensitive-sites/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-26 10:34</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46079.44027777778</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>31/03/2026                              12:00</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>46112.5</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>£5,000</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Robotics Adoption Hubs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/robotics-adoption-hubs/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:38</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46078.44305555556</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>46077</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>15/04/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>£38.0 million</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Robotics Adoption Central Convening Body</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/robotics-adoption-central-convening-body/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:38</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46078.44305555556</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>15/04/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>iX Challenge: CCTV / AI Waste Monitoring for High Accuracy Recycling</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-cctv-ai-waste-monitoring-for-high-accuracy-recycling/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:38</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46078.44305555556</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>07/04/2026                              17:00</t>
         </is>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="L9" s="1" t="n">
         <v>46119.70833333334</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>£25,000</t>
         </is>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N9" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>iX Challenge: Digital Material Flow Mapping and Packaging Reduction</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-digital-material-flow-mapping-and-packaging-reduction/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:38</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46078.44305555556</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>07/04/2026                              17:00</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>46119.70833333334</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>£25,000</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="n">
         <v>46078</v>
       </c>
     </row>
@@ -1321,13 +1595,13 @@
         <v>46078</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1859,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N263"/>
+  <dimension ref="A1:N268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9753,26 +10027,26 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
+          <t>ARIA: Universal Fabricators - concept papers</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-universal-fabricators-concept-papers/</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-02-26 10:34</t>
         </is>
       </c>
       <c r="E157" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46079.44027777778</v>
       </c>
       <c r="F157" t="b">
         <v>1</v>
@@ -9781,48 +10055,54 @@
       <c r="H157" t="b">
         <v>0</v>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J157" s="1" t="n">
+        <v>46069</v>
+      </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>09/03/2026                              14:00</t>
         </is>
       </c>
       <c r="L157" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>46090.58333333334</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="N157" s="1" t="n">
-        <v>45819</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 2</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/adopt-facilitator-support-grant-round-7/</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-02-26 10:34</t>
         </is>
       </c>
       <c r="E158" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46079.44027777778</v>
       </c>
       <c r="F158" t="b">
         <v>1</v>
@@ -9831,48 +10111,54 @@
       <c r="H158" t="b">
         <v>0</v>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="J158" s="1" t="n">
+        <v>46079</v>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Thursday 24 July 2025 11:00am</t>
+          <t>08/04/2026                              11:00</t>
         </is>
       </c>
       <c r="L158" s="1" t="n">
-        <v>45862.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N158" s="1" t="n">
-        <v>45819</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
+          <t>UK Defence Innovation Competition: Innovation Support to Operations Phase 3 (Cycle 7)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/uk-defence-innovation-competition-innovation-support-to-operations-phase-3-cycle-7/</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-02-26 10:34</t>
         </is>
       </c>
       <c r="E159" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46079.44027777778</v>
       </c>
       <c r="F159" t="b">
         <v>1</v>
@@ -9881,48 +10167,54 @@
       <c r="H159" t="b">
         <v>0</v>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J159" s="1" t="n">
+        <v>46076</v>
+      </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>12/05/2026                              12:00</t>
         </is>
       </c>
       <c r="L159" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>46154.5</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N159" s="1" t="n">
-        <v>45819</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>New Innovators in Marine and Maritime, Great South West</t>
+          <t>Countering Illegal Use of UAS Around Prisons and Sensitive Sites</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/countering-illegal-use-of-uas-around-prisons-and-sensitive-sites/</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-02-26 10:34</t>
         </is>
       </c>
       <c r="E160" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46079.44027777778</v>
       </c>
       <c r="F160" t="b">
         <v>1</v>
@@ -9931,23 +10223,29 @@
       <c r="H160" t="b">
         <v>0</v>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J160" s="1" t="n">
+        <v>46069</v>
+      </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>31/03/2026                              12:00</t>
         </is>
       </c>
       <c r="L160" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>46112.5</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£5,000</t>
         </is>
       </c>
       <c r="N160" s="1" t="n">
-        <v>45819</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="161">
@@ -9958,12 +10256,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9985,15 +10283,15 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Thursday 4 September 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L161" s="1" t="n">
-        <v>45904.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N161" s="1" t="n">
@@ -10008,12 +10306,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – June 2025</t>
+          <t>ADOPT Facilitator Support Grant: Round 2</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10035,13 +10333,17 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Thursday 24 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L162" s="1" t="n">
-        <v>45826.45833333334</v>
-      </c>
-      <c r="M162" t="inlineStr"/>
+        <v>45862.45833333334</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>£2,500</t>
+        </is>
+      </c>
       <c r="N162" s="1" t="n">
         <v>45819</v>
       </c>
@@ -10054,12 +10356,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10089,7 +10391,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N163" s="1" t="n">
@@ -10104,12 +10406,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
+          <t>New Innovators in Marine and Maritime, Great South West</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10131,15 +10433,15 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L164" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N164" s="1" t="n">
@@ -10154,12 +10456,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10181,15 +10483,15 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Thursday 4 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L165" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45904.45833333334</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N165" s="1" t="n">
@@ -10204,12 +10506,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
+          <t>ATI Programme strategic batch: EoI – June 2025</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10237,11 +10539,7 @@
       <c r="L166" s="1" t="n">
         <v>45826.45833333334</v>
       </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>£250,000</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" s="1" t="n">
         <v>45819</v>
       </c>
@@ -10254,12 +10552,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10289,7 +10587,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N167" s="1" t="n">
@@ -10304,12 +10602,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10339,7 +10637,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N168" s="1" t="n">
@@ -10354,12 +10652,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Clean Air, Phase 3</t>
+          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10389,7 +10687,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N169" s="1" t="n">
@@ -10404,12 +10702,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
+          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10439,7 +10737,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N170" s="1" t="n">
@@ -10454,12 +10752,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
+          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10481,15 +10779,15 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L171" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N171" s="1" t="n">
@@ -10504,12 +10802,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Canada-UK Semiconductors</t>
+          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10531,15 +10829,15 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L172" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N172" s="1" t="n">
@@ -10554,12 +10852,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
+          <t>Contracts for Innovation: Clean Air, Phase 3</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10581,15 +10879,15 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L173" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N173" s="1" t="n">
@@ -10604,12 +10902,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Innovate UK innovation loans future economy: Round 21</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10631,15 +10929,15 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L174" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N174" s="1" t="n">
@@ -10654,12 +10952,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10681,15 +10979,15 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L175" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N175" s="1" t="n">
@@ -10704,12 +11002,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
+          <t>Canada-UK Semiconductors</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10731,15 +11029,15 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L176" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N176" s="1" t="n">
@@ -10754,12 +11052,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
+          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10789,7 +11087,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N177" s="1" t="n">
@@ -10804,12 +11102,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 1</t>
+          <t>Innovate UK innovation loans future economy: Round 21</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10831,15 +11129,15 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L178" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N178" s="1" t="n">
@@ -10854,12 +11152,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
+          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10881,11 +11179,17 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L179" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>£2.5 million</t>
+        </is>
+      </c>
       <c r="N179" s="1" t="n">
         <v>45819</v>
       </c>
@@ -10898,12 +11202,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee Extension</t>
+          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -10925,11 +11229,17 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L180" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>£2.5 million</t>
+        </is>
+      </c>
       <c r="N180" s="1" t="n">
         <v>45819</v>
       </c>
@@ -10942,21 +11252,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
+          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025-06-16 22:04</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E181" s="1" t="n">
-        <v>45824.91944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F181" t="b">
         <v>1</v>
@@ -10969,15 +11279,15 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L181" s="1" t="n">
-        <v>45917.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N181" s="1" t="n">
@@ -10992,21 +11302,21 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
+          <t>Full ADOPT Grant: Round 1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E182" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F182" t="b">
         <v>1</v>
@@ -11019,19 +11329,19 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L182" s="1" t="n">
-        <v>45889.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N182" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="183">
@@ -11042,21 +11352,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 2</t>
+          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E183" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F183" t="b">
         <v>1</v>
@@ -11069,19 +11379,13 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L183" s="1" t="n">
-        <v>45889.45833333334</v>
-      </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>£100,000</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
       <c r="N183" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="184">
@@ -11092,21 +11396,21 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 22</t>
+          <t>Horizon Europe Guarantee Extension</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025-07-03 08:52</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E184" s="1" t="n">
-        <v>45841.36944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F184" t="b">
         <v>1</v>
@@ -11119,19 +11423,13 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L184" s="1" t="n">
-        <v>45896.45833333334</v>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>£5.0 million</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
       <c r="N184" s="1" t="n">
-        <v>45840</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="185">
@@ -11142,21 +11440,21 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Growth Catalyst Early Stage: New Innovators</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-06-16 22:04</t>
         </is>
       </c>
       <c r="E185" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45824.91944444444</v>
       </c>
       <c r="F185" t="b">
         <v>1</v>
@@ -11169,19 +11467,19 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Wednesday 6 August 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L185" s="1" t="n">
-        <v>45875.45833333334</v>
+        <v>45917.45833333334</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N185" s="1" t="n">
-        <v>45840</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="186">
@@ -11192,21 +11490,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – July 2025</t>
+          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E186" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F186" t="b">
         <v>1</v>
@@ -11219,15 +11517,19 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Wednesday 23 July 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L186" s="1" t="n">
-        <v>45861.45833333334</v>
-      </c>
-      <c r="M186" t="inlineStr"/>
+        <v>45889.45833333334</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>£500,000</t>
+        </is>
+      </c>
       <c r="N186" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="187">
@@ -11238,21 +11540,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
+          <t>Full ADOPT Grant Round 2</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E187" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F187" t="b">
         <v>1</v>
@@ -11265,19 +11567,19 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L187" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N187" s="1" t="n">
-        <v>45847</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="188">
@@ -11288,21 +11590,21 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
+          <t>Innovate UK Innovation Loans Round 22</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-03 08:52</t>
         </is>
       </c>
       <c r="E188" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45841.36944444444</v>
       </c>
       <c r="F188" t="b">
         <v>1</v>
@@ -11323,11 +11625,11 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N188" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="189">
@@ -11338,21 +11640,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
+          <t>Growth Catalyst Early Stage: New Innovators</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E189" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F189" t="b">
         <v>1</v>
@@ -11365,19 +11667,19 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 6 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L189" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45875.45833333334</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N189" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="190">
@@ -11388,21 +11690,21 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Future Flight: Regional Demonstrator 2</t>
+          <t>ATI Programme strategic batch: EoI – July 2025</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E190" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F190" t="b">
         <v>1</v>
@@ -11415,19 +11717,15 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Thursday 17 July 2025 11:00am</t>
+          <t>Wednesday 23 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L190" s="1" t="n">
-        <v>45855.45833333334</v>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>£200,000</t>
-        </is>
-      </c>
+        <v>45861.45833333334</v>
+      </c>
+      <c r="M190" t="inlineStr"/>
       <c r="N190" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="191">
@@ -11438,21 +11736,21 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies</t>
+          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E191" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F191" t="b">
         <v>1</v>
@@ -11465,15 +11763,15 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L191" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N191" s="1" t="n">
@@ -11488,21 +11786,21 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate</t>
+          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E192" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F192" t="b">
         <v>1</v>
@@ -11515,15 +11813,15 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L192" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N192" s="1" t="n">
@@ -11538,21 +11836,21 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate</t>
+          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E193" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F193" t="b">
         <v>1</v>
@@ -11565,15 +11863,15 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L193" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N193" s="1" t="n">
@@ -11588,21 +11886,21 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 3</t>
+          <t>Future Flight: Regional Demonstrator 2</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025-07-25 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E194" s="1" t="n">
-        <v>45863.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F194" t="b">
         <v>1</v>
@@ -11615,19 +11913,19 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Thursday 17 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L194" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45855.45833333334</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N194" s="1" t="n">
-        <v>45861</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="195">
@@ -11638,21 +11936,21 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Sovereign AI - Proof of concept</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025-08-07 08:21</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E195" s="1" t="n">
-        <v>45876.34791666667</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F195" t="b">
         <v>1</v>
@@ -11665,19 +11963,19 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L195" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>£120,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N195" s="1" t="n">
-        <v>45875</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="196">
@@ -11688,21 +11986,21 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E196" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F196" t="b">
         <v>1</v>
@@ -11715,19 +12013,19 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L196" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N196" s="1" t="n">
-        <v>45882</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="197">
@@ -11738,21 +12036,21 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
+          <t>DRIVE35 Innovation Fund: Collaborate</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E197" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F197" t="b">
         <v>1</v>
@@ -11765,19 +12063,19 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L197" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>£4.5 million</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N197" s="1" t="n">
-        <v>45882</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="198">
@@ -11788,21 +12086,21 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
+          <t>ADOPT Facilitator Support Grant: Round 3</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-07-25 08:20</t>
         </is>
       </c>
       <c r="E198" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45863.34722222222</v>
       </c>
       <c r="F198" t="b">
         <v>1</v>
@@ -11815,19 +12113,19 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L198" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N198" s="1" t="n">
-        <v>45882</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="199">
@@ -11838,21 +12136,21 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
+          <t>Sovereign AI - Proof of concept</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025-08-26 08:20</t>
+          <t>2025-08-07 08:21</t>
         </is>
       </c>
       <c r="E199" s="1" t="n">
-        <v>45895.34722222222</v>
+        <v>45876.34791666667</v>
       </c>
       <c r="F199" t="b">
         <v>1</v>
@@ -11873,11 +12171,11 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£120,000</t>
         </is>
       </c>
       <c r="N199" s="1" t="n">
-        <v>45889</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="200">
@@ -11888,21 +12186,21 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 3</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025-08-27 08:18</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E200" s="1" t="n">
-        <v>45896.34583333333</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F200" t="b">
         <v>1</v>
@@ -11915,19 +12213,19 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L200" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8.0 million</t>
         </is>
       </c>
       <c r="N200" s="1" t="n">
-        <v>45896</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="201">
@@ -11938,21 +12236,21 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – September 2025</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025-09-01 08:20</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E201" s="1" t="n">
-        <v>45901.34722222222</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F201" t="b">
         <v>1</v>
@@ -11965,15 +12263,19 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L201" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M201" t="inlineStr"/>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>£4.5 million</t>
+        </is>
+      </c>
       <c r="N201" s="1" t="n">
-        <v>45896</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="202">
@@ -11984,21 +12286,21 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025-09-02 08:19</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E202" s="1" t="n">
-        <v>45902.34652777778</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F202" t="b">
         <v>1</v>
@@ -12011,19 +12313,19 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L202" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N202" s="1" t="n">
-        <v>45896</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="203">
@@ -12034,21 +12336,21 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 4</t>
+          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025-09-04 08:18</t>
+          <t>2025-08-26 08:20</t>
         </is>
       </c>
       <c r="E203" s="1" t="n">
-        <v>45904.34583333333</v>
+        <v>45895.34722222222</v>
       </c>
       <c r="F203" t="b">
         <v>1</v>
@@ -12061,19 +12363,19 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L203" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N203" s="1" t="n">
-        <v>45903</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="204">
@@ -12084,21 +12386,21 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 23</t>
+          <t>Full ADOPT Grant Round 3</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025-09-05 08:18</t>
+          <t>2025-08-27 08:18</t>
         </is>
       </c>
       <c r="E204" s="1" t="n">
-        <v>45905.34583333333</v>
+        <v>45896.34583333333</v>
       </c>
       <c r="F204" t="b">
         <v>1</v>
@@ -12111,19 +12413,19 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L204" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N204" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="205">
@@ -12134,21 +12436,21 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
+          <t>ATI Programme strategic batch: EoI – September 2025</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025-09-12 08:17</t>
+          <t>2025-09-01 08:20</t>
         </is>
       </c>
       <c r="E205" s="1" t="n">
-        <v>45912.34513888889</v>
+        <v>45901.34722222222</v>
       </c>
       <c r="F205" t="b">
         <v>1</v>
@@ -12161,19 +12463,15 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Tuesday 28 October 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L205" s="1" t="n">
-        <v>45958.45833333334</v>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+        <v>45917.45833333334</v>
+      </c>
+      <c r="M205" t="inlineStr"/>
       <c r="N205" s="1" t="n">
-        <v>45910</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="206">
@@ -12184,21 +12482,21 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025-09-16 08:19</t>
+          <t>2025-09-02 08:19</t>
         </is>
       </c>
       <c r="E206" s="1" t="n">
-        <v>45916.34652777778</v>
+        <v>45902.34652777778</v>
       </c>
       <c r="F206" t="b">
         <v>1</v>
@@ -12211,19 +12509,19 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L206" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N206" s="1" t="n">
-        <v>45910</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="207">
@@ -12234,21 +12532,21 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>ADOPT Facilitator Support Grant: Round 4</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025-09-17 08:18</t>
+          <t>2025-09-04 08:18</t>
         </is>
       </c>
       <c r="E207" s="1" t="n">
-        <v>45917.34583333333</v>
+        <v>45904.34583333333</v>
       </c>
       <c r="F207" t="b">
         <v>1</v>
@@ -12261,17 +12559,19 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr"/>
+          <t>Wednesday 15 October 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L207" s="1" t="n">
+        <v>45945.45833333334</v>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N207" s="1" t="n">
-        <v>45917</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="208">
@@ -12282,21 +12582,21 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>Innovate UK Innovation Loans Round 23</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025-09-18 08:17</t>
+          <t>2025-09-05 08:18</t>
         </is>
       </c>
       <c r="E208" s="1" t="n">
-        <v>45918.34513888889</v>
+        <v>45905.34583333333</v>
       </c>
       <c r="F208" t="b">
         <v>1</v>
@@ -12309,19 +12609,19 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Thursday 4 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L208" s="1" t="n">
-        <v>45995.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N208" s="1" t="n">
-        <v>45917</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="209">
@@ -12332,21 +12632,21 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Resource efficiency for resilience and sustainability FS</t>
+          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025-09-20 08:16</t>
+          <t>2025-09-12 08:17</t>
         </is>
       </c>
       <c r="E209" s="1" t="n">
-        <v>45920.34444444445</v>
+        <v>45912.34513888889</v>
       </c>
       <c r="F209" t="b">
         <v>1</v>
@@ -12359,19 +12659,19 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Monday 3 November 2025 11:00am</t>
+          <t>Tuesday 28 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L209" s="1" t="n">
-        <v>45964.45833333334</v>
+        <v>45958.45833333334</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N209" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="210">
@@ -12382,21 +12682,21 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
+          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025-09-23 08:18</t>
+          <t>2025-09-16 08:19</t>
         </is>
       </c>
       <c r="E210" s="1" t="n">
-        <v>45923.34583333333</v>
+        <v>45916.34652777778</v>
       </c>
       <c r="F210" t="b">
         <v>1</v>
@@ -12409,19 +12709,19 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L210" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="N210" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="211">
@@ -12432,21 +12732,21 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 4</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025-09-29 08:20</t>
+          <t>2025-09-17 08:18</t>
         </is>
       </c>
       <c r="E211" s="1" t="n">
-        <v>45929.34722222222</v>
+        <v>45917.34583333333</v>
       </c>
       <c r="F211" t="b">
         <v>1</v>
@@ -12459,19 +12759,17 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Wednesday 3 December 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L211" s="1" t="n">
-        <v>45994.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N211" s="1" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="212">
@@ -12482,21 +12780,21 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Eureka GlobalStars Japan 2026</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025-10-03 08:17</t>
+          <t>2025-09-18 08:17</t>
         </is>
       </c>
       <c r="E212" s="1" t="n">
-        <v>45933.34513888889</v>
+        <v>45918.34513888889</v>
       </c>
       <c r="F212" t="b">
         <v>1</v>
@@ -12509,19 +12807,19 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Wednesday 21 January 2026 11:00am</t>
+          <t>Thursday 4 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L212" s="1" t="n">
-        <v>46043.45833333334</v>
+        <v>45995.45833333334</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N212" s="1" t="n">
-        <v>45931</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="213">
@@ -12532,21 +12830,21 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Feasibility studies 2</t>
+          <t>Resource efficiency for resilience and sustainability FS</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025-10-10 08:18</t>
+          <t>2025-09-20 08:16</t>
         </is>
       </c>
       <c r="E213" s="1" t="n">
-        <v>45940.34583333333</v>
+        <v>45920.34444444445</v>
       </c>
       <c r="F213" t="b">
         <v>1</v>
@@ -12559,19 +12857,19 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Monday 3 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L213" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>45964.45833333334</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N213" s="1" t="n">
-        <v>45938</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="214">
@@ -12582,21 +12880,21 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – October 2025</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025-10-14 08:17</t>
+          <t>2025-09-23 08:18</t>
         </is>
       </c>
       <c r="E214" s="1" t="n">
-        <v>45944.34513888889</v>
+        <v>45923.34583333333</v>
       </c>
       <c r="F214" t="b">
         <v>1</v>
@@ -12615,9 +12913,13 @@
       <c r="L214" s="1" t="n">
         <v>45952.45833333334</v>
       </c>
-      <c r="M214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>£150,000</t>
+        </is>
+      </c>
       <c r="N214" s="1" t="n">
-        <v>45938</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="215">
@@ -12628,21 +12930,21 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Enable</t>
+          <t>Farming Innovation Programme: Feasibility Round 4</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-09-29 08:20</t>
         </is>
       </c>
       <c r="E215" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45929.34722222222</v>
       </c>
       <c r="F215" t="b">
         <v>1</v>
@@ -12655,19 +12957,19 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 3 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L215" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45994.45833333334</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N215" s="1" t="n">
-        <v>45945</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="216">
@@ -12678,21 +12980,21 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Demonstrate</t>
+          <t>Eureka GlobalStars Japan 2026</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-03 08:17</t>
         </is>
       </c>
       <c r="E216" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45933.34513888889</v>
       </c>
       <c r="F216" t="b">
         <v>1</v>
@@ -12705,19 +13007,19 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 21 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L216" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>46043.45833333334</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£600,000</t>
         </is>
       </c>
       <c r="N216" s="1" t="n">
-        <v>45945</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="217">
@@ -12728,21 +13030,21 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
+          <t>CAM Pathfinder: Feasibility studies 2</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025-10-16 08:19</t>
+          <t>2025-10-10 08:18</t>
         </is>
       </c>
       <c r="E217" s="1" t="n">
-        <v>45946.34652777778</v>
+        <v>45940.34583333333</v>
       </c>
       <c r="F217" t="b">
         <v>1</v>
@@ -12763,11 +13065,11 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N217" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="218">
@@ -12778,21 +13080,21 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 5</t>
+          <t>ATI Programme strategic batch EoI – October 2025</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025-10-17 08:19</t>
+          <t>2025-10-14 08:17</t>
         </is>
       </c>
       <c r="E218" s="1" t="n">
-        <v>45947.34652777778</v>
+        <v>45944.34513888889</v>
       </c>
       <c r="F218" t="b">
         <v>1</v>
@@ -12805,19 +13107,15 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L218" s="1" t="n">
-        <v>45987.45833333334</v>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>£2,500</t>
-        </is>
-      </c>
+        <v>45952.45833333334</v>
+      </c>
+      <c r="M218" t="inlineStr"/>
       <c r="N218" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="219">
@@ -12828,21 +13126,21 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Battery Innovation Feasibility Studies Round 1</t>
+          <t>CAM Pathfinder: Enable</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E219" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F219" t="b">
         <v>1</v>
@@ -12863,7 +13161,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N219" s="1" t="n">
@@ -12878,21 +13176,21 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Battery Innovation Concept Development Round 1</t>
+          <t>CAM Pathfinder: Demonstrate</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E220" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F220" t="b">
         <v>1</v>
@@ -12913,7 +13211,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N220" s="1" t="n">
@@ -12928,21 +13226,21 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>The Agentic AI Pioneers Prize</t>
+          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025-10-21 08:20</t>
+          <t>2025-10-16 08:19</t>
         </is>
       </c>
       <c r="E221" s="1" t="n">
-        <v>45951.34722222222</v>
+        <v>45946.34652777778</v>
       </c>
       <c r="F221" t="b">
         <v>1</v>
@@ -12955,13 +13253,17 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L221" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M221" t="inlineStr"/>
+        <v>45987.45833333334</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N221" s="1" t="n">
         <v>45945</v>
       </c>
@@ -12974,21 +13276,21 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy efficiency – industrial research</t>
+          <t>ADOPT Facilitator Support Grant: Round 5</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-17 08:19</t>
         </is>
       </c>
       <c r="E222" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45947.34652777778</v>
       </c>
       <c r="F222" t="b">
         <v>1</v>
@@ -13001,19 +13303,19 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L222" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N222" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="223">
@@ -13024,21 +13326,21 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
+          <t>Battery Innovation Feasibility Studies Round 1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E223" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F223" t="b">
         <v>1</v>
@@ -13051,19 +13353,19 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L223" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N223" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="224">
@@ -13074,21 +13376,21 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 4</t>
+          <t>Battery Innovation Concept Development Round 1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025-10-23 08:19</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E224" s="1" t="n">
-        <v>45953.34652777778</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F224" t="b">
         <v>1</v>
@@ -13101,19 +13403,19 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L224" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N224" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="225">
@@ -13124,21 +13426,21 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 24</t>
+          <t>The Agentic AI Pioneers Prize</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025-10-24 08:19</t>
+          <t>2025-10-21 08:20</t>
         </is>
       </c>
       <c r="E225" s="1" t="n">
-        <v>45954.34652777778</v>
+        <v>45951.34722222222</v>
       </c>
       <c r="F225" t="b">
         <v>1</v>
@@ -13151,19 +13453,15 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Wednesday 7 January 2026 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L225" s="1" t="n">
-        <v>46029.45833333334</v>
-      </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>£5.0 million</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M225" t="inlineStr"/>
       <c r="N225" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="226">
@@ -13174,21 +13472,21 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
+          <t>MSI: SME resource and energy efficiency – industrial research</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025-10-25 08:16</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E226" s="1" t="n">
-        <v>45955.34444444445</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F226" t="b">
         <v>1</v>
@@ -13201,15 +13499,15 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L226" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N226" s="1" t="n">
@@ -13224,21 +13522,21 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility Studies</t>
+          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025-10-31 08:18</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E227" s="1" t="n">
-        <v>45961.34583333333</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F227" t="b">
         <v>1</v>
@@ -13251,19 +13549,19 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L227" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N227" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="228">
@@ -13274,21 +13572,21 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
+          <t>Full ADOPT Grant Round 4</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-23 08:19</t>
         </is>
       </c>
       <c r="E228" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45953.34652777778</v>
       </c>
       <c r="F228" t="b">
         <v>1</v>
@@ -13301,19 +13599,19 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L228" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>£3.4 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N228" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="229">
@@ -13324,21 +13622,21 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Increasing EV charging capacity on the strategic road network</t>
+          <t>Innovate UK Innovation Loans Round 24</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-24 08:19</t>
         </is>
       </c>
       <c r="E229" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45954.34652777778</v>
       </c>
       <c r="F229" t="b">
         <v>1</v>
@@ -13351,19 +13649,19 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 7 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L229" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46029.45833333334</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N229" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="230">
@@ -13374,21 +13672,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-10-25 08:16</t>
         </is>
       </c>
       <c r="E230" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45955.34444444445</v>
       </c>
       <c r="F230" t="b">
         <v>1</v>
@@ -13401,19 +13699,19 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L230" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N230" s="1" t="n">
-        <v>45966</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="231">
@@ -13424,21 +13722,21 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
+          <t>National Materials Innovation Programme: Feasibility Studies</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-10-31 08:18</t>
         </is>
       </c>
       <c r="E231" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45961.34583333333</v>
       </c>
       <c r="F231" t="b">
         <v>1</v>
@@ -13451,19 +13749,19 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L231" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N231" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="232">
@@ -13474,21 +13772,21 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – November 2025</t>
+          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E232" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F232" t="b">
         <v>1</v>
@@ -13501,15 +13799,19 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L232" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M232" t="inlineStr"/>
+        <v>45987.45833333334</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>£3.4 million</t>
+        </is>
+      </c>
       <c r="N232" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="233">
@@ -13520,21 +13822,21 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
+          <t>Increasing EV charging capacity on the strategic road network</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025-11-11 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E233" s="1" t="n">
-        <v>45972.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F233" t="b">
         <v>1</v>
@@ -13547,19 +13849,19 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L233" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N233" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="234">
@@ -13570,21 +13872,21 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Women in Innovation Awards 2025/26</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025-11-27 13:23</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E234" s="1" t="n">
-        <v>45988.55763888889</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F234" t="b">
         <v>1</v>
@@ -13597,19 +13899,19 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L234" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>£75,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N234" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="235">
@@ -13620,21 +13922,21 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025-12-02 08:22</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E235" s="1" t="n">
-        <v>45993.34861111111</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F235" t="b">
         <v>1</v>
@@ -13647,19 +13949,19 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L235" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N235" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="236">
@@ -13670,21 +13972,21 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
+          <t>ATI Programme strategic batch EoI – November 2025</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025-12-11 08:22</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46002.34861111111</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F236" t="b">
         <v>1</v>
@@ -13697,19 +13999,15 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Tuesday 3 February 2026 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L236" s="1" t="n">
-        <v>46056.45833333334</v>
-      </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>£2.0 million</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M236" t="inlineStr"/>
       <c r="N236" s="1" t="n">
-        <v>46001</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="237">
@@ -13720,21 +14018,21 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 5</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025-12-12 08:22</t>
+          <t>2025-11-11 08:19</t>
         </is>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46003.34861111111</v>
+        <v>45972.34652777778</v>
       </c>
       <c r="F237" t="b">
         <v>1</v>
@@ -13747,19 +14045,19 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L237" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N237" s="1" t="n">
-        <v>46001</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="238">
@@ -13770,21 +14068,21 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 6</t>
+          <t>Women in Innovation Awards 2025/26</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-11-27 13:23</t>
         </is>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>45988.55763888889</v>
       </c>
       <c r="F238" t="b">
         <v>1</v>
@@ -13797,19 +14095,19 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L238" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£75,000</t>
         </is>
       </c>
       <c r="N238" s="1" t="n">
-        <v>46008</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="239">
@@ -13820,21 +14118,21 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-02 08:22</t>
         </is>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>45993.34861111111</v>
       </c>
       <c r="F239" t="b">
         <v>1</v>
@@ -13847,19 +14145,19 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Thursday 7 May 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L239" s="1" t="n">
-        <v>46149.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N239" s="1" t="n">
-        <v>46008</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="240">
@@ -13870,21 +14168,21 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – mid stage</t>
+          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-11 08:22</t>
         </is>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46002.34861111111</v>
       </c>
       <c r="F240" t="b">
         <v>1</v>
@@ -13897,19 +14195,19 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Tuesday 3 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L240" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46056.45833333334</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N240" s="1" t="n">
-        <v>46022</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="241">
@@ -13920,21 +14218,21 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – late stage</t>
+          <t>Full ADOPT Grant: Round 5</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-12 08:22</t>
         </is>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46003.34861111111</v>
       </c>
       <c r="F241" t="b">
         <v>1</v>
@@ -13947,19 +14245,19 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L241" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N241" s="1" t="n">
-        <v>46022</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="242">
@@ -13970,21 +14268,21 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – early stage</t>
+          <t>ADOPT Facilitator Support Grant: Round 6</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F242" t="b">
         <v>1</v>
@@ -13997,19 +14295,19 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L242" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N242" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="243">
@@ -14020,21 +14318,21 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F243" t="b">
         <v>1</v>
@@ -14047,19 +14345,19 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Thursday 7 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L243" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N243" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="244">
@@ -14070,12 +14368,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
+          <t>Energy catalyst round 11 – mid stage</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -14097,15 +14395,15 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L244" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N244" s="1" t="n">
@@ -14120,21 +14418,21 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 25</t>
+          <t>Energy catalyst round 11 – late stage</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-01-08 08:22</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46030.34861111111</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F245" t="b">
         <v>1</v>
@@ -14147,11 +14445,11 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L245" s="1" t="n">
-        <v>46085.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
@@ -14159,7 +14457,7 @@
         </is>
       </c>
       <c r="N245" s="1" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="246">
@@ -14170,21 +14468,21 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
+          <t>Energy catalyst round 11 – early stage</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-01-15 08:23</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46037.34930555556</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F246" t="b">
         <v>1</v>
@@ -14197,19 +14495,19 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Wednesday 11 February 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L246" s="1" t="n">
-        <v>46064.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N246" s="1" t="n">
-        <v>46036</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="247">
@@ -14220,21 +14518,21 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-01-20 08:24</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46042.35</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F247" t="b">
         <v>1</v>
@@ -14247,19 +14545,19 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L247" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N247" s="1" t="n">
-        <v>46036</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="248">
@@ -14270,21 +14568,21 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation FS</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-01-26 12:10</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46048.50694444445</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F248" t="b">
         <v>1</v>
@@ -14297,19 +14595,19 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L248" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N248" s="1" t="n">
-        <v>46043</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="249">
@@ -14320,21 +14618,21 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
+          <t>Innovate UK Innovation Loans Round 25</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-08 08:22</t>
         </is>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46030.34861111111</v>
       </c>
       <c r="F249" t="b">
         <v>1</v>
@@ -14347,19 +14645,19 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L249" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46085.45833333334</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>£225,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N249" s="1" t="n">
-        <v>46050</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="250">
@@ -14370,21 +14668,21 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
+          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-15 08:23</t>
         </is>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46037.34930555556</v>
       </c>
       <c r="F250" t="b">
         <v>1</v>
@@ -14397,19 +14695,19 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L250" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46064.45833333334</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N250" s="1" t="n">
-        <v>46050</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="251">
@@ -14420,21 +14718,21 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Robotics Adoption Programme skills development</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-02-02 10:39</t>
+          <t>2026-01-20 08:24</t>
         </is>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46055.44375</v>
+        <v>46042.35</v>
       </c>
       <c r="F251" t="b">
         <v>1</v>
@@ -14447,19 +14745,19 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L251" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N251" s="1" t="n">
-        <v>46050</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="252">
@@ -14470,21 +14768,21 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
+          <t>Advanced manufacturing supply chain innovation FS</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-01-26 12:10</t>
         </is>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46048.50694444445</v>
       </c>
       <c r="F252" t="b">
         <v>1</v>
@@ -14497,19 +14795,19 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L252" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N252" s="1" t="n">
-        <v>46050</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="253">
@@ -14520,21 +14818,21 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
+          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F253" t="b">
         <v>1</v>
@@ -14547,13 +14845,17 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L253" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M253" t="inlineStr"/>
+        <v>46099.45833333334</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>£225,000</t>
+        </is>
+      </c>
       <c r="N253" s="1" t="n">
         <v>46050</v>
       </c>
@@ -14566,21 +14868,21 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
+          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F254" t="b">
         <v>1</v>
@@ -14593,13 +14895,17 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L254" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M254" t="inlineStr"/>
+        <v>46099.45833333334</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>£300,000</t>
+        </is>
+      </c>
       <c r="N254" s="1" t="n">
         <v>46050</v>
       </c>
@@ -14612,21 +14918,21 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 6</t>
+          <t>Robotics Adoption Programme skills development</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-02-09 10:53</t>
+          <t>2026-02-02 10:39</t>
         </is>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46062.45347222222</v>
+        <v>46055.44375</v>
       </c>
       <c r="F255" t="b">
         <v>1</v>
@@ -14639,19 +14945,19 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L255" s="1" t="n">
-        <v>46120.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N255" s="1" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="256">
@@ -14662,21 +14968,21 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Zero Emission Flight Demonstrator Round 1</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F256" t="b">
         <v>1</v>
@@ -14697,11 +15003,11 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N256" s="1" t="n">
-        <v>46064</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="257">
@@ -14712,21 +15018,21 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F257" t="b">
         <v>1</v>
@@ -14739,19 +15045,15 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L257" s="1" t="n">
-        <v>46148.45833333334</v>
-      </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>£1.5 million</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M257" t="inlineStr"/>
       <c r="N257" s="1" t="n">
-        <v>46064</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="258">
@@ -14762,21 +15064,21 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F258" t="b">
         <v>1</v>
@@ -14789,19 +15091,15 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L258" s="1" t="n">
-        <v>46148.45833333334</v>
-      </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>£10.0 million</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M258" t="inlineStr"/>
       <c r="N258" s="1" t="n">
-        <v>46064</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="259">
@@ -14812,21 +15110,21 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
+          <t>Full ADOPT Grant: Round 6</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35</t>
+          <t>2026-02-09 10:53</t>
         </is>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46066.44097222222</v>
+        <v>46062.45347222222</v>
       </c>
       <c r="F259" t="b">
         <v>1</v>
@@ -14839,19 +15137,19 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L259" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N259" s="1" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="260">
@@ -14862,21 +15160,21 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>Zero Emission Flight Demonstrator Round 1</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-02-17 10:40</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46070.44444444445</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F260" t="b">
         <v>1</v>
@@ -14889,15 +15187,15 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L260" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N260" s="1" t="n">
@@ -14912,21 +15210,21 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F261" t="b">
         <v>1</v>
@@ -14939,19 +15237,19 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L261" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N261" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="262">
@@ -14962,21 +15260,21 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F262" t="b">
         <v>1</v>
@@ -14989,19 +15287,19 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L262" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>£7.5 million</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N262" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="263">
@@ -15012,21 +15310,21 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-13 10:35</t>
         </is>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46066.44097222222</v>
       </c>
       <c r="F263" t="b">
         <v>1</v>
@@ -15047,11 +15345,261 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
+      <c r="N263" s="1" t="n">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:40</t>
+        </is>
+      </c>
+      <c r="E264" s="1" t="n">
+        <v>46070.44444444445</v>
+      </c>
+      <c r="F264" t="b">
+        <v>1</v>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="b">
+        <v>0</v>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L264" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>£200,000</t>
+        </is>
+      </c>
+      <c r="N264" s="1" t="n">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Semiconductors and components for smart electronic platforms</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:32</t>
+        </is>
+      </c>
+      <c r="E265" s="1" t="n">
+        <v>46073.43888888889</v>
+      </c>
+      <c r="F265" t="b">
+        <v>1</v>
+      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="b">
+        <v>0</v>
+      </c>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Wednesday 1 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L265" s="1" t="n">
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
           <t>£2.0 million</t>
         </is>
       </c>
-      <c r="N263" s="1" t="n">
+      <c r="N265" s="1" t="n">
         <v>46071</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Robotics Adoption Hubs</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:43</t>
+        </is>
+      </c>
+      <c r="E266" s="1" t="n">
+        <v>46077.44652777778</v>
+      </c>
+      <c r="F266" t="b">
+        <v>1</v>
+      </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="b">
+        <v>0</v>
+      </c>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L266" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>£7.5 million</t>
+        </is>
+      </c>
+      <c r="N266" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Robotics Adoption Central Convening Body</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:43</t>
+        </is>
+      </c>
+      <c r="E267" s="1" t="n">
+        <v>46077.44652777778</v>
+      </c>
+      <c r="F267" t="b">
+        <v>1</v>
+      </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="b">
+        <v>0</v>
+      </c>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L267" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N267" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-02-26 10:40</t>
+        </is>
+      </c>
+      <c r="E268" s="1" t="n">
+        <v>46079.44444444445</v>
+      </c>
+      <c r="F268" t="b">
+        <v>1</v>
+      </c>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="b">
+        <v>0</v>
+      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Wednesday 8 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L268" s="1" t="n">
+        <v>46120.45833333334</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>£2,500</t>
+        </is>
+      </c>
+      <c r="N268" s="1" t="n">
+        <v>46078</v>
       </c>
     </row>
   </sheetData>
@@ -15092,10 +15640,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C2" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
@@ -15105,10 +15653,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
@@ -15118,10 +15666,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C4" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -981,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1059,26 +1059,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARIA: Massively Scalable Neurotechnologies - TA1 concept papers</t>
+          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/aria-massively-scalable-neurotechnologies-ta1-concept-papers/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-02 10:33</t>
+          <t>2026-03-03 10:34</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46083.43958333333</v>
+        <v>46084.44027777778</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1087,25 +1087,19 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>16/02/2026</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46069</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>17/03/2026                              17:00</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46098.70833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£50</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N2" s="1" t="n">
@@ -1120,21 +1114,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICURe Discover Sprint April 2026</t>
+          <t>ARIA: Enduring Atmospheric Platforms - full proposals</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/icure-discover-sprint-april-2026/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-enduring-atmospheric-platforms-full-proposals/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-28 10:12</t>
+          <t>2026-03-03 10:27</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46081.425</v>
+        <v>46084.43541666667</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -1145,23 +1139,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>46056</v>
+        <v>46082</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>12/03/2026                              23:59</t>
+          <t>02/04/2026                              12:00</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46093.99930555555</v>
+        <v>46114.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£500</t>
         </is>
       </c>
       <c r="N3" s="1" t="n">
@@ -1176,21 +1170,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iX Challenge - Preserve Celtic Sea FLOW biodiversity via prediction of marine conditions</t>
+          <t>ARIA: Massively Scalable Neurotechnologies - TA1 concept papers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-preserve-celtic-sea-flow-biodiversity-via-prediction-of-marine-conditions/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-massively-scalable-neurotechnologies-ta1-concept-papers/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-28 10:12</t>
+          <t>2026-03-02 10:33</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46081.425</v>
+        <v>46083.43958333333</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -1201,23 +1195,23 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>46077</v>
+        <v>46069</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>07/04/2026                              23:59</t>
+          <t>17/03/2026                              17:00</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46119.99930555555</v>
+        <v>46098.70833333334</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="N4" s="1" t="n">
@@ -1232,12 +1226,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iX Challenge - Circular solutions for textile waste reduction in Southwest Wales</t>
+          <t>ICURe Discover Sprint April 2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-circular-solutions-for-textile-waste-reduction-in-southwest-wales/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/icure-discover-sprint-april-2026/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1257,23 +1251,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
-        <v>46077</v>
+        <v>46056</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>07/04/2026                              23:59</t>
+          <t>12/03/2026                              23:59</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46119.99930555555</v>
+        <v>46093.99930555555</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N5" s="1" t="n">
@@ -1283,26 +1277,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 7</t>
+          <t>iX Challenge - Preserve Celtic Sea FLOW biodiversity via prediction of marine conditions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-preserve-celtic-sea-flow-biodiversity-via-prediction-of-marine-conditions/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-26 10:40</t>
+          <t>2026-02-28 10:12</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46079.44444444445</v>
+        <v>46081.425</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1311,19 +1305,25 @@
       <c r="H6" t="b">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>46077</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>07/04/2026                              23:59</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46120.45833333334</v>
+        <v>46119.99930555555</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N6" s="1" t="n">
@@ -1338,21 +1338,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARIA: Universal Fabricators - concept papers</t>
+          <t>iX Challenge - Circular solutions for textile waste reduction in Southwest Wales</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/aria-universal-fabricators-concept-papers/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-circular-solutions-for-textile-waste-reduction-in-southwest-wales/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-26 10:34</t>
+          <t>2026-02-28 10:12</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46079.44027777778</v>
+        <v>46081.425</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -1363,23 +1363,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>46069</v>
+        <v>46077</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>09/03/2026                              14:00</t>
+          <t>07/04/2026                              23:59</t>
         </is>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46090.58333333334</v>
+        <v>46119.99930555555</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>£50</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N7" s="1" t="n">
@@ -1389,7 +1389,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1399,16 +1399,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/adopt-facilitator-support-grant-round-7/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-26 10:34</t>
+          <t>2026-02-26 10:40</t>
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46079.44027777778</v>
+        <v>46079.44444444445</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -1417,17 +1417,11 @@
       <c r="H8" t="b">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>26/02/2026</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>46079</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>08/04/2026                              11:00</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L8" s="1" t="n">
@@ -1435,7 +1429,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N8" s="1" t="n">
@@ -1450,12 +1444,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UK Defence Innovation Competition: Innovation Support to Operations Phase 3 (Cycle 7)</t>
+          <t>ARIA: Universal Fabricators - concept papers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/uk-defence-innovation-competition-innovation-support-to-operations-phase-3-cycle-7/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-universal-fabricators-concept-papers/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1475,23 +1469,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>46076</v>
+        <v>46069</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12/05/2026                              12:00</t>
+          <t>09/03/2026                              14:00</t>
         </is>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46154.5</v>
+        <v>46090.58333333334</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="N9" s="1" t="n">
@@ -1506,12 +1500,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Countering Illegal Use of UAS Around Prisons and Sensitive Sites</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/countering-illegal-use-of-uas-around-prisons-and-sensitive-sites/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/adopt-facilitator-support-grant-round-7/</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1531,23 +1525,23 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>46069</v>
+        <v>46079</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>31/03/2026                              12:00</t>
+          <t>08/04/2026                              11:00</t>
         </is>
       </c>
       <c r="L10" s="1" t="n">
-        <v>46112.5</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>£5,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N10" s="1" t="n">
@@ -1562,21 +1556,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>UK Defence Innovation Competition: Innovation Support to Operations Phase 3 (Cycle 7)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/robotics-adoption-hubs/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/uk-defence-innovation-competition-innovation-support-to-operations-phase-3-cycle-7/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-25 10:38</t>
+          <t>2026-02-26 10:34</t>
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46078.44305555556</v>
+        <v>46079.44027777778</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -1587,23 +1581,23 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15/04/2026                              11:00</t>
+          <t>12/05/2026                              12:00</t>
         </is>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46154.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>£38.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N11" s="1" t="n">
@@ -1618,21 +1612,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>Countering Illegal Use of UAS Around Prisons and Sensitive Sites</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/robotics-adoption-central-convening-body/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/countering-illegal-use-of-uas-around-prisons-and-sensitive-sites/</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-25 10:38</t>
+          <t>2026-02-26 10:34</t>
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46078.44305555556</v>
+        <v>46079.44027777778</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -1643,23 +1637,23 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>46077</v>
+        <v>46069</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15/04/2026                              11:00</t>
+          <t>31/03/2026                              12:00</t>
         </is>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46112.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£5,000</t>
         </is>
       </c>
       <c r="N12" s="1" t="n">
@@ -1674,12 +1668,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>iX Challenge: CCTV / AI Waste Monitoring for High Accuracy Recycling</t>
+          <t>Robotics Adoption Hubs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-cctv-ai-waste-monitoring-for-high-accuracy-recycling/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/robotics-adoption-hubs/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1707,15 +1701,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>07/04/2026                              17:00</t>
+          <t>15/04/2026                              11:00</t>
         </is>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46119.70833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£38.0 million</t>
         </is>
       </c>
       <c r="N13" s="1" t="n">
@@ -1730,12 +1724,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>iX Challenge: Digital Material Flow Mapping and Packaging Reduction</t>
+          <t>Robotics Adoption Central Convening Body</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-digital-material-flow-mapping-and-packaging-reduction/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/robotics-adoption-central-convening-body/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1763,18 +1757,130 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>15/04/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>iX Challenge: CCTV / AI Waste Monitoring for High Accuracy Recycling</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-cctv-ai-waste-monitoring-for-high-accuracy-recycling/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:38</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46078.44305555556</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>07/04/2026                              17:00</t>
         </is>
       </c>
-      <c r="L14" s="1" t="n">
+      <c r="L15" s="1" t="n">
         <v>46119.70833333334</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>£25,000</t>
         </is>
       </c>
-      <c r="N14" s="1" t="n">
+      <c r="N15" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>iX Challenge: Digital Material Flow Mapping and Packaging Reduction</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-digital-material-flow-mapping-and-packaging-reduction/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:38</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46078.44305555556</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>07/04/2026                              17:00</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>46119.70833333334</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>£25,000</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="n">
         <v>46078</v>
       </c>
     </row>
@@ -1819,13 +1925,13 @@
         <v>46078</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2357,7 +2463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N272"/>
+  <dimension ref="A1:N274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10699,26 +10805,26 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
+          <t>ARIA: Enduring Atmospheric Platforms - full proposals</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-enduring-atmospheric-platforms-full-proposals/</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-03-03 10:27</t>
         </is>
       </c>
       <c r="E165" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46084.43541666667</v>
       </c>
       <c r="F165" t="b">
         <v>1</v>
@@ -10727,23 +10833,29 @@
       <c r="H165" t="b">
         <v>0</v>
       </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>01/03/2026</t>
+        </is>
+      </c>
+      <c r="J165" s="1" t="n">
+        <v>46082</v>
+      </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>02/04/2026                              12:00</t>
         </is>
       </c>
       <c r="L165" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>46114.5</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£500</t>
         </is>
       </c>
       <c r="N165" s="1" t="n">
-        <v>45819</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="166">
@@ -10754,12 +10866,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 2</t>
+          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10781,15 +10893,15 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Thursday 24 July 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L166" s="1" t="n">
-        <v>45862.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N166" s="1" t="n">
@@ -10804,12 +10916,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
+          <t>ADOPT Facilitator Support Grant: Round 2</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10831,15 +10943,15 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 24 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L167" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45862.45833333334</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N167" s="1" t="n">
@@ -10854,12 +10966,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>New Innovators in Marine and Maritime, Great South West</t>
+          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10889,7 +11001,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N168" s="1" t="n">
@@ -10904,12 +11016,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>New Innovators in Marine and Maritime, Great South West</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10931,15 +11043,15 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Thursday 4 September 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L169" s="1" t="n">
-        <v>45904.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N169" s="1" t="n">
@@ -10954,12 +11066,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – June 2025</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10981,13 +11093,17 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Thursday 4 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L170" s="1" t="n">
-        <v>45826.45833333334</v>
-      </c>
-      <c r="M170" t="inlineStr"/>
+        <v>45904.45833333334</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N170" s="1" t="n">
         <v>45819</v>
       </c>
@@ -11000,12 +11116,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>ATI Programme strategic batch: EoI – June 2025</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -11027,17 +11143,13 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L171" s="1" t="n">
-        <v>45840.45833333334</v>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45826.45833333334</v>
+      </c>
+      <c r="M171" t="inlineStr"/>
       <c r="N171" s="1" t="n">
         <v>45819</v>
       </c>
@@ -11050,12 +11162,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -11077,15 +11189,15 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L172" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N172" s="1" t="n">
@@ -11100,12 +11212,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -11150,12 +11262,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
+          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11177,15 +11289,15 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L174" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N174" s="1" t="n">
@@ -11200,12 +11312,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
+          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11227,15 +11339,15 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L175" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N175" s="1" t="n">
@@ -11250,12 +11362,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
+          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11277,15 +11389,15 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L176" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N176" s="1" t="n">
@@ -11300,12 +11412,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Clean Air, Phase 3</t>
+          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11350,12 +11462,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
+          <t>Contracts for Innovation: Clean Air, Phase 3</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11377,15 +11489,15 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L178" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N178" s="1" t="n">
@@ -11400,12 +11512,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11435,7 +11547,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N179" s="1" t="n">
@@ -11450,12 +11562,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Canada-UK Semiconductors</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11477,15 +11589,15 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L180" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N180" s="1" t="n">
@@ -11500,12 +11612,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
+          <t>Canada-UK Semiconductors</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11527,15 +11639,15 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L181" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N181" s="1" t="n">
@@ -11550,12 +11662,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Innovate UK innovation loans future economy: Round 21</t>
+          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11585,7 +11697,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N182" s="1" t="n">
@@ -11600,12 +11712,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
+          <t>Innovate UK innovation loans future economy: Round 21</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11627,15 +11739,15 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L183" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N183" s="1" t="n">
@@ -11650,12 +11762,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
+          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11700,12 +11812,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
+          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11727,15 +11839,15 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L185" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N185" s="1" t="n">
@@ -11750,12 +11862,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 1</t>
+          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11777,15 +11889,15 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L186" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N186" s="1" t="n">
@@ -11800,12 +11912,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
+          <t>Full ADOPT Grant: Round 1</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11827,11 +11939,17 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L187" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N187" s="1" t="n">
         <v>45819</v>
       </c>
@@ -11844,12 +11962,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee Extension</t>
+          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11888,21 +12006,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
+          <t>Horizon Europe Guarantee Extension</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025-06-16 22:04</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E189" s="1" t="n">
-        <v>45824.91944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F189" t="b">
         <v>1</v>
@@ -11915,17 +12033,11 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L189" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>£8,500</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
       <c r="N189" s="1" t="n">
         <v>45819</v>
       </c>
@@ -11938,21 +12050,21 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-16 22:04</t>
         </is>
       </c>
       <c r="E190" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45824.91944444444</v>
       </c>
       <c r="F190" t="b">
         <v>1</v>
@@ -11965,19 +12077,19 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L190" s="1" t="n">
-        <v>45889.45833333334</v>
+        <v>45917.45833333334</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N190" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="191">
@@ -11988,12 +12100,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 2</t>
+          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12023,7 +12135,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N191" s="1" t="n">
@@ -12038,21 +12150,21 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 22</t>
+          <t>Full ADOPT Grant Round 2</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025-07-03 08:52</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E192" s="1" t="n">
-        <v>45841.36944444444</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F192" t="b">
         <v>1</v>
@@ -12065,19 +12177,19 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L192" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N192" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="193">
@@ -12088,21 +12200,21 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Growth Catalyst Early Stage: New Innovators</t>
+          <t>Innovate UK Innovation Loans Round 22</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-07-03 08:52</t>
         </is>
       </c>
       <c r="E193" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45841.36944444444</v>
       </c>
       <c r="F193" t="b">
         <v>1</v>
@@ -12115,15 +12227,15 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Wednesday 6 August 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L193" s="1" t="n">
-        <v>45875.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N193" s="1" t="n">
@@ -12138,12 +12250,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – July 2025</t>
+          <t>Growth Catalyst Early Stage: New Innovators</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12165,13 +12277,17 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Wednesday 23 July 2025 11:00am</t>
+          <t>Wednesday 6 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L194" s="1" t="n">
-        <v>45861.45833333334</v>
-      </c>
-      <c r="M194" t="inlineStr"/>
+        <v>45875.45833333334</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>£50,000</t>
+        </is>
+      </c>
       <c r="N194" s="1" t="n">
         <v>45840</v>
       </c>
@@ -12184,21 +12300,21 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
+          <t>ATI Programme strategic batch: EoI – July 2025</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E195" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F195" t="b">
         <v>1</v>
@@ -12211,19 +12327,15 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 23 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L195" s="1" t="n">
-        <v>45896.45833333334</v>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+        <v>45861.45833333334</v>
+      </c>
+      <c r="M195" t="inlineStr"/>
       <c r="N195" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="196">
@@ -12234,12 +12346,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12284,12 +12396,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12334,12 +12446,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Future Flight: Regional Demonstrator 2</t>
+          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12361,15 +12473,15 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Thursday 17 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L198" s="1" t="n">
-        <v>45855.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N198" s="1" t="n">
@@ -12384,21 +12496,21 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies</t>
+          <t>Future Flight: Regional Demonstrator 2</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E199" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F199" t="b">
         <v>1</v>
@@ -12411,15 +12523,15 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Thursday 17 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L199" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45855.45833333334</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N199" s="1" t="n">
@@ -12434,12 +12546,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12461,15 +12573,15 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L200" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N200" s="1" t="n">
@@ -12484,12 +12596,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12519,7 +12631,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N201" s="1" t="n">
@@ -12534,21 +12646,21 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 3</t>
+          <t>DRIVE35 Innovation Fund: Collaborate</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025-07-25 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E202" s="1" t="n">
-        <v>45863.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F202" t="b">
         <v>1</v>
@@ -12561,19 +12673,19 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L202" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N202" s="1" t="n">
-        <v>45861</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="203">
@@ -12584,21 +12696,21 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Sovereign AI - Proof of concept</t>
+          <t>ADOPT Facilitator Support Grant: Round 3</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025-08-07 08:21</t>
+          <t>2025-07-25 08:20</t>
         </is>
       </c>
       <c r="E203" s="1" t="n">
-        <v>45876.34791666667</v>
+        <v>45863.34722222222</v>
       </c>
       <c r="F203" t="b">
         <v>1</v>
@@ -12611,19 +12723,19 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L203" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>£120,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N203" s="1" t="n">
-        <v>45875</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="204">
@@ -12634,21 +12746,21 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
+          <t>Sovereign AI - Proof of concept</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-08-07 08:21</t>
         </is>
       </c>
       <c r="E204" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45876.34791666667</v>
       </c>
       <c r="F204" t="b">
         <v>1</v>
@@ -12661,19 +12773,19 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L204" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£120,000</t>
         </is>
       </c>
       <c r="N204" s="1" t="n">
-        <v>45882</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="205">
@@ -12684,12 +12796,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12719,7 +12831,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>£4.5 million</t>
+          <t>£8.0 million</t>
         </is>
       </c>
       <c r="N205" s="1" t="n">
@@ -12734,12 +12846,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12769,7 +12881,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£4.5 million</t>
         </is>
       </c>
       <c r="N206" s="1" t="n">
@@ -12784,21 +12896,21 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025-08-26 08:20</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E207" s="1" t="n">
-        <v>45895.34722222222</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F207" t="b">
         <v>1</v>
@@ -12811,19 +12923,19 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L207" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N207" s="1" t="n">
-        <v>45889</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="208">
@@ -12834,21 +12946,21 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 3</t>
+          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025-08-27 08:18</t>
+          <t>2025-08-26 08:20</t>
         </is>
       </c>
       <c r="E208" s="1" t="n">
-        <v>45896.34583333333</v>
+        <v>45895.34722222222</v>
       </c>
       <c r="F208" t="b">
         <v>1</v>
@@ -12861,11 +12973,11 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L208" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
@@ -12873,7 +12985,7 @@
         </is>
       </c>
       <c r="N208" s="1" t="n">
-        <v>45896</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="209">
@@ -12884,21 +12996,21 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – September 2025</t>
+          <t>Full ADOPT Grant Round 3</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025-09-01 08:20</t>
+          <t>2025-08-27 08:18</t>
         </is>
       </c>
       <c r="E209" s="1" t="n">
-        <v>45901.34722222222</v>
+        <v>45896.34583333333</v>
       </c>
       <c r="F209" t="b">
         <v>1</v>
@@ -12911,13 +13023,17 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L209" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M209" t="inlineStr"/>
+        <v>45945.45833333334</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N209" s="1" t="n">
         <v>45896</v>
       </c>
@@ -12930,21 +13046,21 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
+          <t>ATI Programme strategic batch: EoI – September 2025</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025-09-02 08:19</t>
+          <t>2025-09-01 08:20</t>
         </is>
       </c>
       <c r="E210" s="1" t="n">
-        <v>45902.34652777778</v>
+        <v>45901.34722222222</v>
       </c>
       <c r="F210" t="b">
         <v>1</v>
@@ -12957,17 +13073,13 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L210" s="1" t="n">
-        <v>45966.45833333334</v>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45917.45833333334</v>
+      </c>
+      <c r="M210" t="inlineStr"/>
       <c r="N210" s="1" t="n">
         <v>45896</v>
       </c>
@@ -12980,21 +13092,21 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 4</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025-09-04 08:18</t>
+          <t>2025-09-02 08:19</t>
         </is>
       </c>
       <c r="E211" s="1" t="n">
-        <v>45904.34583333333</v>
+        <v>45902.34652777778</v>
       </c>
       <c r="F211" t="b">
         <v>1</v>
@@ -13007,19 +13119,19 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L211" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N211" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="212">
@@ -13030,21 +13142,21 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 23</t>
+          <t>ADOPT Facilitator Support Grant: Round 4</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025-09-05 08:18</t>
+          <t>2025-09-04 08:18</t>
         </is>
       </c>
       <c r="E212" s="1" t="n">
-        <v>45905.34583333333</v>
+        <v>45904.34583333333</v>
       </c>
       <c r="F212" t="b">
         <v>1</v>
@@ -13057,15 +13169,15 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L212" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N212" s="1" t="n">
@@ -13080,21 +13192,21 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
+          <t>Innovate UK Innovation Loans Round 23</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025-09-12 08:17</t>
+          <t>2025-09-05 08:18</t>
         </is>
       </c>
       <c r="E213" s="1" t="n">
-        <v>45912.34513888889</v>
+        <v>45905.34583333333</v>
       </c>
       <c r="F213" t="b">
         <v>1</v>
@@ -13107,19 +13219,19 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Tuesday 28 October 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L213" s="1" t="n">
-        <v>45958.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N213" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="214">
@@ -13130,21 +13242,21 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
+          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025-09-16 08:19</t>
+          <t>2025-09-12 08:17</t>
         </is>
       </c>
       <c r="E214" s="1" t="n">
-        <v>45916.34652777778</v>
+        <v>45912.34513888889</v>
       </c>
       <c r="F214" t="b">
         <v>1</v>
@@ -13157,15 +13269,15 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Tuesday 28 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L214" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45958.45833333334</v>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N214" s="1" t="n">
@@ -13180,21 +13292,21 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025-09-17 08:18</t>
+          <t>2025-09-16 08:19</t>
         </is>
       </c>
       <c r="E215" s="1" t="n">
-        <v>45917.34583333333</v>
+        <v>45916.34652777778</v>
       </c>
       <c r="F215" t="b">
         <v>1</v>
@@ -13207,17 +13319,19 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
+          <t>Wednesday 15 October 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L215" s="1" t="n">
+        <v>45945.45833333334</v>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="N215" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="216">
@@ -13228,21 +13342,21 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025-09-18 08:17</t>
+          <t>2025-09-17 08:18</t>
         </is>
       </c>
       <c r="E216" s="1" t="n">
-        <v>45918.34513888889</v>
+        <v>45917.34583333333</v>
       </c>
       <c r="F216" t="b">
         <v>1</v>
@@ -13255,15 +13369,13 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Thursday 4 December 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L216" s="1" t="n">
-        <v>45995.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N216" s="1" t="n">
@@ -13278,21 +13390,21 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Resource efficiency for resilience and sustainability FS</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025-09-20 08:16</t>
+          <t>2025-09-18 08:17</t>
         </is>
       </c>
       <c r="E217" s="1" t="n">
-        <v>45920.34444444445</v>
+        <v>45918.34513888889</v>
       </c>
       <c r="F217" t="b">
         <v>1</v>
@@ -13305,15 +13417,15 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Monday 3 November 2025 11:00am</t>
+          <t>Thursday 4 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L217" s="1" t="n">
-        <v>45964.45833333334</v>
+        <v>45995.45833333334</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N217" s="1" t="n">
@@ -13328,21 +13440,21 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
+          <t>Resource efficiency for resilience and sustainability FS</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025-09-23 08:18</t>
+          <t>2025-09-20 08:16</t>
         </is>
       </c>
       <c r="E218" s="1" t="n">
-        <v>45923.34583333333</v>
+        <v>45920.34444444445</v>
       </c>
       <c r="F218" t="b">
         <v>1</v>
@@ -13355,15 +13467,15 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Monday 3 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L218" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45964.45833333334</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N218" s="1" t="n">
@@ -13378,21 +13490,21 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 4</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025-09-29 08:20</t>
+          <t>2025-09-23 08:18</t>
         </is>
       </c>
       <c r="E219" s="1" t="n">
-        <v>45929.34722222222</v>
+        <v>45923.34583333333</v>
       </c>
       <c r="F219" t="b">
         <v>1</v>
@@ -13405,19 +13517,19 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Wednesday 3 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L219" s="1" t="n">
-        <v>45994.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N219" s="1" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="220">
@@ -13428,21 +13540,21 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Eureka GlobalStars Japan 2026</t>
+          <t>Farming Innovation Programme: Feasibility Round 4</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025-10-03 08:17</t>
+          <t>2025-09-29 08:20</t>
         </is>
       </c>
       <c r="E220" s="1" t="n">
-        <v>45933.34513888889</v>
+        <v>45929.34722222222</v>
       </c>
       <c r="F220" t="b">
         <v>1</v>
@@ -13455,19 +13567,19 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Wednesday 21 January 2026 11:00am</t>
+          <t>Wednesday 3 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L220" s="1" t="n">
-        <v>46043.45833333334</v>
+        <v>45994.45833333334</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N220" s="1" t="n">
-        <v>45931</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="221">
@@ -13478,21 +13590,21 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Feasibility studies 2</t>
+          <t>Eureka GlobalStars Japan 2026</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025-10-10 08:18</t>
+          <t>2025-10-03 08:17</t>
         </is>
       </c>
       <c r="E221" s="1" t="n">
-        <v>45940.34583333333</v>
+        <v>45933.34513888889</v>
       </c>
       <c r="F221" t="b">
         <v>1</v>
@@ -13505,19 +13617,19 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 21 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L221" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46043.45833333334</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£600,000</t>
         </is>
       </c>
       <c r="N221" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="222">
@@ -13528,21 +13640,21 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – October 2025</t>
+          <t>CAM Pathfinder: Feasibility studies 2</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025-10-14 08:17</t>
+          <t>2025-10-10 08:18</t>
         </is>
       </c>
       <c r="E222" s="1" t="n">
-        <v>45944.34513888889</v>
+        <v>45940.34583333333</v>
       </c>
       <c r="F222" t="b">
         <v>1</v>
@@ -13555,13 +13667,17 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L222" s="1" t="n">
-        <v>45952.45833333334</v>
-      </c>
-      <c r="M222" t="inlineStr"/>
+        <v>45987.45833333334</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N222" s="1" t="n">
         <v>45938</v>
       </c>
@@ -13574,21 +13690,21 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Enable</t>
+          <t>ATI Programme strategic batch EoI – October 2025</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-14 08:17</t>
         </is>
       </c>
       <c r="E223" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45944.34513888889</v>
       </c>
       <c r="F223" t="b">
         <v>1</v>
@@ -13601,19 +13717,15 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L223" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>£4.0 million</t>
-        </is>
-      </c>
+        <v>45952.45833333334</v>
+      </c>
+      <c r="M223" t="inlineStr"/>
       <c r="N223" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="224">
@@ -13624,12 +13736,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Demonstrate</t>
+          <t>CAM Pathfinder: Enable</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -13659,7 +13771,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N224" s="1" t="n">
@@ -13674,21 +13786,21 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
+          <t>CAM Pathfinder: Demonstrate</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025-10-16 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E225" s="1" t="n">
-        <v>45946.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F225" t="b">
         <v>1</v>
@@ -13701,15 +13813,15 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L225" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N225" s="1" t="n">
@@ -13724,21 +13836,21 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 5</t>
+          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025-10-17 08:19</t>
+          <t>2025-10-16 08:19</t>
         </is>
       </c>
       <c r="E226" s="1" t="n">
-        <v>45947.34652777778</v>
+        <v>45946.34652777778</v>
       </c>
       <c r="F226" t="b">
         <v>1</v>
@@ -13759,7 +13871,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N226" s="1" t="n">
@@ -13774,21 +13886,21 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Battery Innovation Feasibility Studies Round 1</t>
+          <t>ADOPT Facilitator Support Grant: Round 5</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-17 08:19</t>
         </is>
       </c>
       <c r="E227" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45947.34652777778</v>
       </c>
       <c r="F227" t="b">
         <v>1</v>
@@ -13801,15 +13913,15 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L227" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N227" s="1" t="n">
@@ -13824,12 +13936,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Battery Innovation Concept Development Round 1</t>
+          <t>Battery Innovation Feasibility Studies Round 1</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -13859,7 +13971,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N228" s="1" t="n">
@@ -13874,21 +13986,21 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>The Agentic AI Pioneers Prize</t>
+          <t>Battery Innovation Concept Development Round 1</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-10-21 08:20</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E229" s="1" t="n">
-        <v>45951.34722222222</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F229" t="b">
         <v>1</v>
@@ -13901,13 +14013,17 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L229" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M229" t="inlineStr"/>
+        <v>46008.45833333334</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N229" s="1" t="n">
         <v>45945</v>
       </c>
@@ -13920,21 +14036,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy efficiency – industrial research</t>
+          <t>The Agentic AI Pioneers Prize</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-21 08:20</t>
         </is>
       </c>
       <c r="E230" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45951.34722222222</v>
       </c>
       <c r="F230" t="b">
         <v>1</v>
@@ -13947,19 +14063,15 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L230" s="1" t="n">
-        <v>46001.45833333334</v>
-      </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>£1.0 million</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M230" t="inlineStr"/>
       <c r="N230" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="231">
@@ -13970,12 +14082,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
+          <t>MSI: SME resource and energy efficiency – industrial research</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -14005,7 +14117,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N231" s="1" t="n">
@@ -14020,21 +14132,21 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 4</t>
+          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025-10-23 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E232" s="1" t="n">
-        <v>45953.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F232" t="b">
         <v>1</v>
@@ -14055,7 +14167,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N232" s="1" t="n">
@@ -14070,21 +14182,21 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 24</t>
+          <t>Full ADOPT Grant Round 4</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025-10-24 08:19</t>
+          <t>2025-10-23 08:19</t>
         </is>
       </c>
       <c r="E233" s="1" t="n">
-        <v>45954.34652777778</v>
+        <v>45953.34652777778</v>
       </c>
       <c r="F233" t="b">
         <v>1</v>
@@ -14097,15 +14209,15 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Wednesday 7 January 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L233" s="1" t="n">
-        <v>46029.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N233" s="1" t="n">
@@ -14120,21 +14232,21 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
+          <t>Innovate UK Innovation Loans Round 24</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025-10-25 08:16</t>
+          <t>2025-10-24 08:19</t>
         </is>
       </c>
       <c r="E234" s="1" t="n">
-        <v>45955.34444444445</v>
+        <v>45954.34652777778</v>
       </c>
       <c r="F234" t="b">
         <v>1</v>
@@ -14147,15 +14259,15 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 7 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L234" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46029.45833333334</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N234" s="1" t="n">
@@ -14170,21 +14282,21 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility Studies</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025-10-31 08:18</t>
+          <t>2025-10-25 08:16</t>
         </is>
       </c>
       <c r="E235" s="1" t="n">
-        <v>45961.34583333333</v>
+        <v>45955.34444444445</v>
       </c>
       <c r="F235" t="b">
         <v>1</v>
@@ -14197,19 +14309,19 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L235" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N235" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="236">
@@ -14220,21 +14332,21 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
+          <t>National Materials Innovation Programme: Feasibility Studies</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-31 08:18</t>
         </is>
       </c>
       <c r="E236" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45961.34583333333</v>
       </c>
       <c r="F236" t="b">
         <v>1</v>
@@ -14247,15 +14359,15 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L236" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>£3.4 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N236" s="1" t="n">
@@ -14270,12 +14382,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Increasing EV charging capacity on the strategic road network</t>
+          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -14297,15 +14409,15 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L237" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£3.4 million</t>
         </is>
       </c>
       <c r="N237" s="1" t="n">
@@ -14320,21 +14432,21 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
+          <t>Increasing EV charging capacity on the strategic road network</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E238" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F238" t="b">
         <v>1</v>
@@ -14347,19 +14459,19 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L238" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N238" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="239">
@@ -14370,12 +14482,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -14405,7 +14517,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N239" s="1" t="n">
@@ -14420,12 +14532,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – November 2025</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -14447,13 +14559,17 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L240" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M240" t="inlineStr"/>
+        <v>46001.45833333334</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N240" s="1" t="n">
         <v>45966</v>
       </c>
@@ -14466,21 +14582,21 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
+          <t>ATI Programme strategic batch EoI – November 2025</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025-11-11 08:19</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E241" s="1" t="n">
-        <v>45972.34652777778</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F241" t="b">
         <v>1</v>
@@ -14493,17 +14609,13 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L241" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>£750,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M241" t="inlineStr"/>
       <c r="N241" s="1" t="n">
         <v>45966</v>
       </c>
@@ -14516,21 +14628,21 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Women in Innovation Awards 2025/26</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025-11-27 13:23</t>
+          <t>2025-11-11 08:19</t>
         </is>
       </c>
       <c r="E242" s="1" t="n">
-        <v>45988.55763888889</v>
+        <v>45972.34652777778</v>
       </c>
       <c r="F242" t="b">
         <v>1</v>
@@ -14543,19 +14655,19 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L242" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>£75,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N242" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="243">
@@ -14566,21 +14678,21 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
+          <t>Women in Innovation Awards 2025/26</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025-12-02 08:22</t>
+          <t>2025-11-27 13:23</t>
         </is>
       </c>
       <c r="E243" s="1" t="n">
-        <v>45993.34861111111</v>
+        <v>45988.55763888889</v>
       </c>
       <c r="F243" t="b">
         <v>1</v>
@@ -14601,7 +14713,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£75,000</t>
         </is>
       </c>
       <c r="N243" s="1" t="n">
@@ -14616,21 +14728,21 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025-12-11 08:22</t>
+          <t>2025-12-02 08:22</t>
         </is>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46002.34861111111</v>
+        <v>45993.34861111111</v>
       </c>
       <c r="F244" t="b">
         <v>1</v>
@@ -14643,19 +14755,19 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Tuesday 3 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L244" s="1" t="n">
-        <v>46056.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N244" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="245">
@@ -14666,21 +14778,21 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 5</t>
+          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025-12-12 08:22</t>
+          <t>2025-12-11 08:22</t>
         </is>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46003.34861111111</v>
+        <v>46002.34861111111</v>
       </c>
       <c r="F245" t="b">
         <v>1</v>
@@ -14693,15 +14805,15 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Tuesday 3 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L245" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46056.45833333334</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N245" s="1" t="n">
@@ -14716,21 +14828,21 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 6</t>
+          <t>Full ADOPT Grant: Round 5</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-12 08:22</t>
         </is>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46003.34861111111</v>
       </c>
       <c r="F246" t="b">
         <v>1</v>
@@ -14743,19 +14855,19 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L246" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N246" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="247">
@@ -14766,12 +14878,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
+          <t>ADOPT Facilitator Support Grant: Round 6</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -14793,15 +14905,15 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Thursday 7 May 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L247" s="1" t="n">
-        <v>46149.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N247" s="1" t="n">
@@ -14816,21 +14928,21 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – mid stage</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F248" t="b">
         <v>1</v>
@@ -14843,19 +14955,19 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Thursday 7 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L248" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N248" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="249">
@@ -14866,12 +14978,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – late stage</t>
+          <t>Energy catalyst round 11 – mid stage</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -14901,7 +15013,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N249" s="1" t="n">
@@ -14916,12 +15028,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – early stage</t>
+          <t>Energy catalyst round 11 – late stage</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -14951,7 +15063,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N250" s="1" t="n">
@@ -14966,12 +15078,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
+          <t>Energy catalyst round 11 – early stage</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -14993,15 +15105,15 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L251" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N251" s="1" t="n">
@@ -15016,12 +15128,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -15043,15 +15155,15 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L252" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N252" s="1" t="n">
@@ -15066,21 +15178,21 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 25</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-01-08 08:22</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46030.34861111111</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F253" t="b">
         <v>1</v>
@@ -15093,19 +15205,19 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L253" s="1" t="n">
-        <v>46085.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N253" s="1" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="254">
@@ -15116,21 +15228,21 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
+          <t>Innovate UK Innovation Loans Round 25</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-01-15 08:23</t>
+          <t>2026-01-08 08:22</t>
         </is>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46037.34930555556</v>
+        <v>46030.34861111111</v>
       </c>
       <c r="F254" t="b">
         <v>1</v>
@@ -15143,19 +15255,19 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Wednesday 11 February 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L254" s="1" t="n">
-        <v>46064.45833333334</v>
+        <v>46085.45833333334</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N254" s="1" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="255">
@@ -15166,21 +15278,21 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
+          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-01-20 08:24</t>
+          <t>2026-01-15 08:23</t>
         </is>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46042.35</v>
+        <v>46037.34930555556</v>
       </c>
       <c r="F255" t="b">
         <v>1</v>
@@ -15193,15 +15305,15 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 11 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L255" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46064.45833333334</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N255" s="1" t="n">
@@ -15216,21 +15328,21 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation FS</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-01-26 12:10</t>
+          <t>2026-01-20 08:24</t>
         </is>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46048.50694444445</v>
+        <v>46042.35</v>
       </c>
       <c r="F256" t="b">
         <v>1</v>
@@ -15243,19 +15355,19 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L256" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N256" s="1" t="n">
-        <v>46043</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="257">
@@ -15266,21 +15378,21 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
+          <t>Advanced manufacturing supply chain innovation FS</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-26 12:10</t>
         </is>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46048.50694444445</v>
       </c>
       <c r="F257" t="b">
         <v>1</v>
@@ -15293,19 +15405,19 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L257" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>£225,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N257" s="1" t="n">
-        <v>46050</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="258">
@@ -15316,12 +15428,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
+          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -15351,7 +15463,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£225,000</t>
         </is>
       </c>
       <c r="N258" s="1" t="n">
@@ -15366,21 +15478,21 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Robotics Adoption Programme skills development</t>
+          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-02-02 10:39</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46055.44375</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F259" t="b">
         <v>1</v>
@@ -15393,15 +15505,15 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L259" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N259" s="1" t="n">
@@ -15416,21 +15528,21 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
+          <t>Robotics Adoption Programme skills development</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-02-02 10:39</t>
         </is>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46055.44375</v>
       </c>
       <c r="F260" t="b">
         <v>1</v>
@@ -15443,15 +15555,15 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L260" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N260" s="1" t="n">
@@ -15466,12 +15578,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -15493,13 +15605,17 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L261" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M261" t="inlineStr"/>
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N261" s="1" t="n">
         <v>46050</v>
       </c>
@@ -15512,12 +15628,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -15558,21 +15674,21 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 6</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-02-09 10:53</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46062.45347222222</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F263" t="b">
         <v>1</v>
@@ -15585,19 +15701,15 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L263" s="1" t="n">
-        <v>46120.45833333334</v>
-      </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>£100,000</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M263" t="inlineStr"/>
       <c r="N263" s="1" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="264">
@@ -15608,21 +15720,21 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Zero Emission Flight Demonstrator Round 1</t>
+          <t>Full ADOPT Grant: Round 6</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-09 10:53</t>
         </is>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46062.45347222222</v>
       </c>
       <c r="F264" t="b">
         <v>1</v>
@@ -15635,19 +15747,19 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L264" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N264" s="1" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="265">
@@ -15658,12 +15770,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
+          <t>Zero Emission Flight Demonstrator Round 1</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -15685,15 +15797,15 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L265" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N265" s="1" t="n">
@@ -15708,12 +15820,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
+          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -15743,7 +15855,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>£10.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N266" s="1" t="n">
@@ -15758,21 +15870,21 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
+          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46066.44097222222</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F267" t="b">
         <v>1</v>
@@ -15785,15 +15897,15 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L267" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N267" s="1" t="n">
@@ -15808,21 +15920,21 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-02-17 10:40</t>
+          <t>2026-02-13 10:35</t>
         </is>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46070.44444444445</v>
+        <v>46066.44097222222</v>
       </c>
       <c r="F268" t="b">
         <v>1</v>
@@ -15843,7 +15955,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N268" s="1" t="n">
@@ -15858,21 +15970,21 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-17 10:40</t>
         </is>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46070.44444444445</v>
       </c>
       <c r="F269" t="b">
         <v>1</v>
@@ -15885,19 +15997,19 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L269" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N269" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="270">
@@ -15908,21 +16020,21 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>Semiconductors and components for smart electronic platforms</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-20 10:32</t>
         </is>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46073.43888888889</v>
       </c>
       <c r="F270" t="b">
         <v>1</v>
@@ -15935,15 +16047,15 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L270" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>£7.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N270" s="1" t="n">
@@ -15958,12 +16070,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>Robotics Adoption Hubs</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -15993,7 +16105,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£7.5 million</t>
         </is>
       </c>
       <c r="N271" s="1" t="n">
@@ -16008,21 +16120,21 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 7</t>
+          <t>Robotics Adoption Central Convening Body</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-02-26 10:40</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46079.44444444445</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F272" t="b">
         <v>1</v>
@@ -16035,18 +16147,118 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L272" s="1" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N272" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-02-26 10:40</t>
+        </is>
+      </c>
+      <c r="E273" s="1" t="n">
+        <v>46079.44444444445</v>
+      </c>
+      <c r="F273" t="b">
+        <v>1</v>
+      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="b">
+        <v>0</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
           <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
-      <c r="L272" s="1" t="n">
+      <c r="L273" s="1" t="n">
         <v>46120.45833333334</v>
       </c>
-      <c r="M272" t="inlineStr">
+      <c r="M273" t="inlineStr">
         <is>
           <t>£2,500</t>
         </is>
       </c>
-      <c r="N272" s="1" t="n">
+      <c r="N273" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-03-03 10:34</t>
+        </is>
+      </c>
+      <c r="E274" s="1" t="n">
+        <v>46084.44027777778</v>
+      </c>
+      <c r="F274" t="b">
+        <v>1</v>
+      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="b">
+        <v>0</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Wednesday 1 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L274" s="1" t="n">
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
+      <c r="N274" s="1" t="n">
         <v>46078</v>
       </c>
     </row>
@@ -16088,10 +16300,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
@@ -16101,10 +16313,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4">
@@ -16114,10 +16326,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C4" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -895,7 +895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,26 +973,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/clean-maritime-demonstration-competition-7/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-03-12 10:27</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46093.43541666667</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1001,11 +1001,17 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>46092</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>15/07/2026                              11:00</t>
         </is>
       </c>
       <c r="L2" s="1" t="n">
@@ -1013,7 +1019,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£121.0 million</t>
         </is>
       </c>
       <c r="N2" s="1" t="n">
@@ -1028,12 +1034,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
+          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1063,7 +1069,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N3" s="1" t="n">
@@ -1078,12 +1084,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1113,10 +1119,60 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-11 10:34</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46092.44027777778</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Wednesday 15 July 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>46218.45833333334</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>£15.0 million</t>
         </is>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N5" s="1" t="n">
         <v>46092</v>
       </c>
     </row>
@@ -1164,10 +1220,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1727,7 +1783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N284"/>
+  <dimension ref="A1:N285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10509,26 +10565,26 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
+          <t>Clean Maritime Demonstration Competition 7</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/clean-maritime-demonstration-competition-7/</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-03-12 10:27</t>
         </is>
       </c>
       <c r="E173" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46093.43541666667</v>
       </c>
       <c r="F173" t="b">
         <v>1</v>
@@ -10537,23 +10593,29 @@
       <c r="H173" t="b">
         <v>0</v>
       </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="J173" s="1" t="n">
+        <v>46092</v>
+      </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>15/07/2026                              11:00</t>
         </is>
       </c>
       <c r="L173" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£121.0 million</t>
         </is>
       </c>
       <c r="N173" s="1" t="n">
-        <v>45819</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="174">
@@ -10564,12 +10626,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 2</t>
+          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10591,15 +10653,15 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Thursday 24 July 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L174" s="1" t="n">
-        <v>45862.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N174" s="1" t="n">
@@ -10614,12 +10676,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
+          <t>ADOPT Facilitator Support Grant: Round 2</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10641,15 +10703,15 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 24 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L175" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45862.45833333334</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N175" s="1" t="n">
@@ -10664,12 +10726,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>New Innovators in Marine and Maritime, Great South West</t>
+          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10699,7 +10761,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N176" s="1" t="n">
@@ -10714,12 +10776,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>New Innovators in Marine and Maritime, Great South West</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10741,15 +10803,15 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Thursday 4 September 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L177" s="1" t="n">
-        <v>45904.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N177" s="1" t="n">
@@ -10764,12 +10826,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – June 2025</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10791,13 +10853,17 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Thursday 4 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L178" s="1" t="n">
-        <v>45826.45833333334</v>
-      </c>
-      <c r="M178" t="inlineStr"/>
+        <v>45904.45833333334</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N178" s="1" t="n">
         <v>45819</v>
       </c>
@@ -10810,12 +10876,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>ATI Programme strategic batch: EoI – June 2025</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10837,17 +10903,13 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L179" s="1" t="n">
-        <v>45840.45833333334</v>
-      </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45826.45833333334</v>
+      </c>
+      <c r="M179" t="inlineStr"/>
       <c r="N179" s="1" t="n">
         <v>45819</v>
       </c>
@@ -10860,12 +10922,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -10887,15 +10949,15 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L180" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N180" s="1" t="n">
@@ -10910,12 +10972,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -10960,12 +11022,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
+          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10987,15 +11049,15 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L182" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N182" s="1" t="n">
@@ -11010,12 +11072,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
+          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11037,15 +11099,15 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L183" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N183" s="1" t="n">
@@ -11060,12 +11122,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
+          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11087,15 +11149,15 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L184" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N184" s="1" t="n">
@@ -11110,12 +11172,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Clean Air, Phase 3</t>
+          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11160,12 +11222,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
+          <t>Contracts for Innovation: Clean Air, Phase 3</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11187,15 +11249,15 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L186" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N186" s="1" t="n">
@@ -11210,12 +11272,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11245,7 +11307,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N187" s="1" t="n">
@@ -11260,12 +11322,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Canada-UK Semiconductors</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11287,15 +11349,15 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L188" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N188" s="1" t="n">
@@ -11310,12 +11372,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
+          <t>Canada-UK Semiconductors</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11337,15 +11399,15 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L189" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N189" s="1" t="n">
@@ -11360,12 +11422,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Innovate UK innovation loans future economy: Round 21</t>
+          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11395,7 +11457,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N190" s="1" t="n">
@@ -11410,12 +11472,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
+          <t>Innovate UK innovation loans future economy: Round 21</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11437,15 +11499,15 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L191" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N191" s="1" t="n">
@@ -11460,12 +11522,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
+          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11510,12 +11572,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
+          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11537,15 +11599,15 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L193" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N193" s="1" t="n">
@@ -11560,12 +11622,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 1</t>
+          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11587,15 +11649,15 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L194" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N194" s="1" t="n">
@@ -11610,12 +11672,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
+          <t>Full ADOPT Grant: Round 1</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11637,11 +11699,17 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L195" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N195" s="1" t="n">
         <v>45819</v>
       </c>
@@ -11654,12 +11722,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee Extension</t>
+          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -11698,21 +11766,21 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
+          <t>Horizon Europe Guarantee Extension</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025-06-16 22:04</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E197" s="1" t="n">
-        <v>45824.91944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F197" t="b">
         <v>1</v>
@@ -11725,17 +11793,11 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L197" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>£8,500</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
       <c r="N197" s="1" t="n">
         <v>45819</v>
       </c>
@@ -11748,21 +11810,21 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-16 22:04</t>
         </is>
       </c>
       <c r="E198" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45824.91944444444</v>
       </c>
       <c r="F198" t="b">
         <v>1</v>
@@ -11775,19 +11837,19 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L198" s="1" t="n">
-        <v>45889.45833333334</v>
+        <v>45917.45833333334</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N198" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="199">
@@ -11798,12 +11860,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 2</t>
+          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -11833,7 +11895,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N199" s="1" t="n">
@@ -11848,21 +11910,21 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 22</t>
+          <t>Full ADOPT Grant Round 2</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025-07-03 08:52</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E200" s="1" t="n">
-        <v>45841.36944444444</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F200" t="b">
         <v>1</v>
@@ -11875,19 +11937,19 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L200" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N200" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="201">
@@ -11898,21 +11960,21 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Growth Catalyst Early Stage: New Innovators</t>
+          <t>Innovate UK Innovation Loans Round 22</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-07-03 08:52</t>
         </is>
       </c>
       <c r="E201" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45841.36944444444</v>
       </c>
       <c r="F201" t="b">
         <v>1</v>
@@ -11925,15 +11987,15 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Wednesday 6 August 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L201" s="1" t="n">
-        <v>45875.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N201" s="1" t="n">
@@ -11948,12 +12010,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – July 2025</t>
+          <t>Growth Catalyst Early Stage: New Innovators</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11975,13 +12037,17 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Wednesday 23 July 2025 11:00am</t>
+          <t>Wednesday 6 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L202" s="1" t="n">
-        <v>45861.45833333334</v>
-      </c>
-      <c r="M202" t="inlineStr"/>
+        <v>45875.45833333334</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>£50,000</t>
+        </is>
+      </c>
       <c r="N202" s="1" t="n">
         <v>45840</v>
       </c>
@@ -11994,21 +12060,21 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
+          <t>ATI Programme strategic batch: EoI – July 2025</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E203" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F203" t="b">
         <v>1</v>
@@ -12021,19 +12087,15 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 23 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L203" s="1" t="n">
-        <v>45896.45833333334</v>
-      </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+        <v>45861.45833333334</v>
+      </c>
+      <c r="M203" t="inlineStr"/>
       <c r="N203" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="204">
@@ -12044,12 +12106,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12094,12 +12156,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12144,12 +12206,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Future Flight: Regional Demonstrator 2</t>
+          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12171,15 +12233,15 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Thursday 17 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L206" s="1" t="n">
-        <v>45855.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N206" s="1" t="n">
@@ -12194,21 +12256,21 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies</t>
+          <t>Future Flight: Regional Demonstrator 2</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E207" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F207" t="b">
         <v>1</v>
@@ -12221,15 +12283,15 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Thursday 17 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L207" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45855.45833333334</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N207" s="1" t="n">
@@ -12244,12 +12306,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -12271,15 +12333,15 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L208" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N208" s="1" t="n">
@@ -12294,12 +12356,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -12329,7 +12391,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N209" s="1" t="n">
@@ -12344,21 +12406,21 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 3</t>
+          <t>DRIVE35 Innovation Fund: Collaborate</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025-07-25 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E210" s="1" t="n">
-        <v>45863.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F210" t="b">
         <v>1</v>
@@ -12371,19 +12433,19 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L210" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N210" s="1" t="n">
-        <v>45861</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="211">
@@ -12394,21 +12456,21 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Sovereign AI - Proof of concept</t>
+          <t>ADOPT Facilitator Support Grant: Round 3</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025-08-07 08:21</t>
+          <t>2025-07-25 08:20</t>
         </is>
       </c>
       <c r="E211" s="1" t="n">
-        <v>45876.34791666667</v>
+        <v>45863.34722222222</v>
       </c>
       <c r="F211" t="b">
         <v>1</v>
@@ -12421,19 +12483,19 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L211" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>£120,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N211" s="1" t="n">
-        <v>45875</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="212">
@@ -12444,21 +12506,21 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
+          <t>Sovereign AI - Proof of concept</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-08-07 08:21</t>
         </is>
       </c>
       <c r="E212" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45876.34791666667</v>
       </c>
       <c r="F212" t="b">
         <v>1</v>
@@ -12471,19 +12533,19 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L212" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£120,000</t>
         </is>
       </c>
       <c r="N212" s="1" t="n">
-        <v>45882</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="213">
@@ -12494,12 +12556,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -12529,7 +12591,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>£4.5 million</t>
+          <t>£8.0 million</t>
         </is>
       </c>
       <c r="N213" s="1" t="n">
@@ -12544,12 +12606,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -12579,7 +12641,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£4.5 million</t>
         </is>
       </c>
       <c r="N214" s="1" t="n">
@@ -12594,21 +12656,21 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025-08-26 08:20</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E215" s="1" t="n">
-        <v>45895.34722222222</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F215" t="b">
         <v>1</v>
@@ -12621,19 +12683,19 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L215" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N215" s="1" t="n">
-        <v>45889</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="216">
@@ -12644,21 +12706,21 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 3</t>
+          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025-08-27 08:18</t>
+          <t>2025-08-26 08:20</t>
         </is>
       </c>
       <c r="E216" s="1" t="n">
-        <v>45896.34583333333</v>
+        <v>45895.34722222222</v>
       </c>
       <c r="F216" t="b">
         <v>1</v>
@@ -12671,11 +12733,11 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L216" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
@@ -12683,7 +12745,7 @@
         </is>
       </c>
       <c r="N216" s="1" t="n">
-        <v>45896</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="217">
@@ -12694,21 +12756,21 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – September 2025</t>
+          <t>Full ADOPT Grant Round 3</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025-09-01 08:20</t>
+          <t>2025-08-27 08:18</t>
         </is>
       </c>
       <c r="E217" s="1" t="n">
-        <v>45901.34722222222</v>
+        <v>45896.34583333333</v>
       </c>
       <c r="F217" t="b">
         <v>1</v>
@@ -12721,13 +12783,17 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L217" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M217" t="inlineStr"/>
+        <v>45945.45833333334</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N217" s="1" t="n">
         <v>45896</v>
       </c>
@@ -12740,21 +12806,21 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
+          <t>ATI Programme strategic batch: EoI – September 2025</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025-09-02 08:19</t>
+          <t>2025-09-01 08:20</t>
         </is>
       </c>
       <c r="E218" s="1" t="n">
-        <v>45902.34652777778</v>
+        <v>45901.34722222222</v>
       </c>
       <c r="F218" t="b">
         <v>1</v>
@@ -12767,17 +12833,13 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L218" s="1" t="n">
-        <v>45966.45833333334</v>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45917.45833333334</v>
+      </c>
+      <c r="M218" t="inlineStr"/>
       <c r="N218" s="1" t="n">
         <v>45896</v>
       </c>
@@ -12790,21 +12852,21 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 4</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025-09-04 08:18</t>
+          <t>2025-09-02 08:19</t>
         </is>
       </c>
       <c r="E219" s="1" t="n">
-        <v>45904.34583333333</v>
+        <v>45902.34652777778</v>
       </c>
       <c r="F219" t="b">
         <v>1</v>
@@ -12817,19 +12879,19 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L219" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N219" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="220">
@@ -12840,21 +12902,21 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 23</t>
+          <t>ADOPT Facilitator Support Grant: Round 4</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025-09-05 08:18</t>
+          <t>2025-09-04 08:18</t>
         </is>
       </c>
       <c r="E220" s="1" t="n">
-        <v>45905.34583333333</v>
+        <v>45904.34583333333</v>
       </c>
       <c r="F220" t="b">
         <v>1</v>
@@ -12867,15 +12929,15 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L220" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N220" s="1" t="n">
@@ -12890,21 +12952,21 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
+          <t>Innovate UK Innovation Loans Round 23</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025-09-12 08:17</t>
+          <t>2025-09-05 08:18</t>
         </is>
       </c>
       <c r="E221" s="1" t="n">
-        <v>45912.34513888889</v>
+        <v>45905.34583333333</v>
       </c>
       <c r="F221" t="b">
         <v>1</v>
@@ -12917,19 +12979,19 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Tuesday 28 October 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L221" s="1" t="n">
-        <v>45958.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N221" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="222">
@@ -12940,21 +13002,21 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
+          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025-09-16 08:19</t>
+          <t>2025-09-12 08:17</t>
         </is>
       </c>
       <c r="E222" s="1" t="n">
-        <v>45916.34652777778</v>
+        <v>45912.34513888889</v>
       </c>
       <c r="F222" t="b">
         <v>1</v>
@@ -12967,15 +13029,15 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Tuesday 28 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L222" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45958.45833333334</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N222" s="1" t="n">
@@ -12990,21 +13052,21 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025-09-17 08:18</t>
+          <t>2025-09-16 08:19</t>
         </is>
       </c>
       <c r="E223" s="1" t="n">
-        <v>45917.34583333333</v>
+        <v>45916.34652777778</v>
       </c>
       <c r="F223" t="b">
         <v>1</v>
@@ -13017,17 +13079,19 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr"/>
+          <t>Wednesday 15 October 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L223" s="1" t="n">
+        <v>45945.45833333334</v>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="N223" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="224">
@@ -13038,21 +13102,21 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025-09-18 08:17</t>
+          <t>2025-09-17 08:18</t>
         </is>
       </c>
       <c r="E224" s="1" t="n">
-        <v>45918.34513888889</v>
+        <v>45917.34583333333</v>
       </c>
       <c r="F224" t="b">
         <v>1</v>
@@ -13065,15 +13129,13 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Thursday 4 December 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L224" s="1" t="n">
-        <v>45995.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N224" s="1" t="n">
@@ -13088,21 +13150,21 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Resource efficiency for resilience and sustainability FS</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025-09-20 08:16</t>
+          <t>2025-09-18 08:17</t>
         </is>
       </c>
       <c r="E225" s="1" t="n">
-        <v>45920.34444444445</v>
+        <v>45918.34513888889</v>
       </c>
       <c r="F225" t="b">
         <v>1</v>
@@ -13115,15 +13177,15 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Monday 3 November 2025 11:00am</t>
+          <t>Thursday 4 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L225" s="1" t="n">
-        <v>45964.45833333334</v>
+        <v>45995.45833333334</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N225" s="1" t="n">
@@ -13138,21 +13200,21 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
+          <t>Resource efficiency for resilience and sustainability FS</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025-09-23 08:18</t>
+          <t>2025-09-20 08:16</t>
         </is>
       </c>
       <c r="E226" s="1" t="n">
-        <v>45923.34583333333</v>
+        <v>45920.34444444445</v>
       </c>
       <c r="F226" t="b">
         <v>1</v>
@@ -13165,15 +13227,15 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Monday 3 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L226" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45964.45833333334</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N226" s="1" t="n">
@@ -13188,21 +13250,21 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 4</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025-09-29 08:20</t>
+          <t>2025-09-23 08:18</t>
         </is>
       </c>
       <c r="E227" s="1" t="n">
-        <v>45929.34722222222</v>
+        <v>45923.34583333333</v>
       </c>
       <c r="F227" t="b">
         <v>1</v>
@@ -13215,19 +13277,19 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Wednesday 3 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L227" s="1" t="n">
-        <v>45994.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N227" s="1" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="228">
@@ -13238,21 +13300,21 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Eureka GlobalStars Japan 2026</t>
+          <t>Farming Innovation Programme: Feasibility Round 4</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025-10-03 08:17</t>
+          <t>2025-09-29 08:20</t>
         </is>
       </c>
       <c r="E228" s="1" t="n">
-        <v>45933.34513888889</v>
+        <v>45929.34722222222</v>
       </c>
       <c r="F228" t="b">
         <v>1</v>
@@ -13265,19 +13327,19 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Wednesday 21 January 2026 11:00am</t>
+          <t>Wednesday 3 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L228" s="1" t="n">
-        <v>46043.45833333334</v>
+        <v>45994.45833333334</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N228" s="1" t="n">
-        <v>45931</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="229">
@@ -13288,21 +13350,21 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Feasibility studies 2</t>
+          <t>Eureka GlobalStars Japan 2026</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-10-10 08:18</t>
+          <t>2025-10-03 08:17</t>
         </is>
       </c>
       <c r="E229" s="1" t="n">
-        <v>45940.34583333333</v>
+        <v>45933.34513888889</v>
       </c>
       <c r="F229" t="b">
         <v>1</v>
@@ -13315,19 +13377,19 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 21 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L229" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46043.45833333334</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£600,000</t>
         </is>
       </c>
       <c r="N229" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="230">
@@ -13338,21 +13400,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – October 2025</t>
+          <t>CAM Pathfinder: Feasibility studies 2</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025-10-14 08:17</t>
+          <t>2025-10-10 08:18</t>
         </is>
       </c>
       <c r="E230" s="1" t="n">
-        <v>45944.34513888889</v>
+        <v>45940.34583333333</v>
       </c>
       <c r="F230" t="b">
         <v>1</v>
@@ -13365,13 +13427,17 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L230" s="1" t="n">
-        <v>45952.45833333334</v>
-      </c>
-      <c r="M230" t="inlineStr"/>
+        <v>45987.45833333334</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N230" s="1" t="n">
         <v>45938</v>
       </c>
@@ -13384,21 +13450,21 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Enable</t>
+          <t>ATI Programme strategic batch EoI – October 2025</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-14 08:17</t>
         </is>
       </c>
       <c r="E231" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45944.34513888889</v>
       </c>
       <c r="F231" t="b">
         <v>1</v>
@@ -13411,19 +13477,15 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L231" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>£4.0 million</t>
-        </is>
-      </c>
+        <v>45952.45833333334</v>
+      </c>
+      <c r="M231" t="inlineStr"/>
       <c r="N231" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="232">
@@ -13434,12 +13496,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Demonstrate</t>
+          <t>CAM Pathfinder: Enable</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -13469,7 +13531,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N232" s="1" t="n">
@@ -13484,21 +13546,21 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
+          <t>CAM Pathfinder: Demonstrate</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025-10-16 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E233" s="1" t="n">
-        <v>45946.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F233" t="b">
         <v>1</v>
@@ -13511,15 +13573,15 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L233" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N233" s="1" t="n">
@@ -13534,21 +13596,21 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 5</t>
+          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025-10-17 08:19</t>
+          <t>2025-10-16 08:19</t>
         </is>
       </c>
       <c r="E234" s="1" t="n">
-        <v>45947.34652777778</v>
+        <v>45946.34652777778</v>
       </c>
       <c r="F234" t="b">
         <v>1</v>
@@ -13569,7 +13631,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N234" s="1" t="n">
@@ -13584,21 +13646,21 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Battery Innovation Feasibility Studies Round 1</t>
+          <t>ADOPT Facilitator Support Grant: Round 5</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-17 08:19</t>
         </is>
       </c>
       <c r="E235" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45947.34652777778</v>
       </c>
       <c r="F235" t="b">
         <v>1</v>
@@ -13611,15 +13673,15 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L235" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N235" s="1" t="n">
@@ -13634,12 +13696,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Battery Innovation Concept Development Round 1</t>
+          <t>Battery Innovation Feasibility Studies Round 1</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -13669,7 +13731,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N236" s="1" t="n">
@@ -13684,21 +13746,21 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>The Agentic AI Pioneers Prize</t>
+          <t>Battery Innovation Concept Development Round 1</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025-10-21 08:20</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E237" s="1" t="n">
-        <v>45951.34722222222</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F237" t="b">
         <v>1</v>
@@ -13711,13 +13773,17 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L237" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M237" t="inlineStr"/>
+        <v>46008.45833333334</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N237" s="1" t="n">
         <v>45945</v>
       </c>
@@ -13730,21 +13796,21 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy efficiency – industrial research</t>
+          <t>The Agentic AI Pioneers Prize</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-21 08:20</t>
         </is>
       </c>
       <c r="E238" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45951.34722222222</v>
       </c>
       <c r="F238" t="b">
         <v>1</v>
@@ -13757,19 +13823,15 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L238" s="1" t="n">
-        <v>46001.45833333334</v>
-      </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>£1.0 million</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M238" t="inlineStr"/>
       <c r="N238" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="239">
@@ -13780,12 +13842,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
+          <t>MSI: SME resource and energy efficiency – industrial research</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -13815,7 +13877,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N239" s="1" t="n">
@@ -13830,21 +13892,21 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 4</t>
+          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025-10-23 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E240" s="1" t="n">
-        <v>45953.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F240" t="b">
         <v>1</v>
@@ -13865,7 +13927,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N240" s="1" t="n">
@@ -13880,21 +13942,21 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 24</t>
+          <t>Full ADOPT Grant Round 4</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025-10-24 08:19</t>
+          <t>2025-10-23 08:19</t>
         </is>
       </c>
       <c r="E241" s="1" t="n">
-        <v>45954.34652777778</v>
+        <v>45953.34652777778</v>
       </c>
       <c r="F241" t="b">
         <v>1</v>
@@ -13907,15 +13969,15 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Wednesday 7 January 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L241" s="1" t="n">
-        <v>46029.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N241" s="1" t="n">
@@ -13930,21 +13992,21 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
+          <t>Innovate UK Innovation Loans Round 24</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025-10-25 08:16</t>
+          <t>2025-10-24 08:19</t>
         </is>
       </c>
       <c r="E242" s="1" t="n">
-        <v>45955.34444444445</v>
+        <v>45954.34652777778</v>
       </c>
       <c r="F242" t="b">
         <v>1</v>
@@ -13957,15 +14019,15 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 7 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L242" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46029.45833333334</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N242" s="1" t="n">
@@ -13980,21 +14042,21 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility Studies</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025-10-31 08:18</t>
+          <t>2025-10-25 08:16</t>
         </is>
       </c>
       <c r="E243" s="1" t="n">
-        <v>45961.34583333333</v>
+        <v>45955.34444444445</v>
       </c>
       <c r="F243" t="b">
         <v>1</v>
@@ -14007,19 +14069,19 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L243" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N243" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="244">
@@ -14030,21 +14092,21 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
+          <t>National Materials Innovation Programme: Feasibility Studies</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-31 08:18</t>
         </is>
       </c>
       <c r="E244" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45961.34583333333</v>
       </c>
       <c r="F244" t="b">
         <v>1</v>
@@ -14057,15 +14119,15 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L244" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>£3.4 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N244" s="1" t="n">
@@ -14080,12 +14142,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Increasing EV charging capacity on the strategic road network</t>
+          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -14107,15 +14169,15 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L245" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£3.4 million</t>
         </is>
       </c>
       <c r="N245" s="1" t="n">
@@ -14130,21 +14192,21 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
+          <t>Increasing EV charging capacity on the strategic road network</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E246" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F246" t="b">
         <v>1</v>
@@ -14157,19 +14219,19 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L246" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N246" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="247">
@@ -14180,12 +14242,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -14215,7 +14277,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N247" s="1" t="n">
@@ -14230,12 +14292,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – November 2025</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -14257,13 +14319,17 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L248" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M248" t="inlineStr"/>
+        <v>46001.45833333334</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N248" s="1" t="n">
         <v>45966</v>
       </c>
@@ -14276,21 +14342,21 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
+          <t>ATI Programme strategic batch EoI – November 2025</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025-11-11 08:19</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E249" s="1" t="n">
-        <v>45972.34652777778</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F249" t="b">
         <v>1</v>
@@ -14303,17 +14369,13 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L249" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>£750,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M249" t="inlineStr"/>
       <c r="N249" s="1" t="n">
         <v>45966</v>
       </c>
@@ -14326,21 +14388,21 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Women in Innovation Awards 2025/26</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025-11-27 13:23</t>
+          <t>2025-11-11 08:19</t>
         </is>
       </c>
       <c r="E250" s="1" t="n">
-        <v>45988.55763888889</v>
+        <v>45972.34652777778</v>
       </c>
       <c r="F250" t="b">
         <v>1</v>
@@ -14353,19 +14415,19 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L250" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>£75,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N250" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="251">
@@ -14376,21 +14438,21 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
+          <t>Women in Innovation Awards 2025/26</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025-12-02 08:22</t>
+          <t>2025-11-27 13:23</t>
         </is>
       </c>
       <c r="E251" s="1" t="n">
-        <v>45993.34861111111</v>
+        <v>45988.55763888889</v>
       </c>
       <c r="F251" t="b">
         <v>1</v>
@@ -14411,7 +14473,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£75,000</t>
         </is>
       </c>
       <c r="N251" s="1" t="n">
@@ -14426,21 +14488,21 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025-12-11 08:22</t>
+          <t>2025-12-02 08:22</t>
         </is>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46002.34861111111</v>
+        <v>45993.34861111111</v>
       </c>
       <c r="F252" t="b">
         <v>1</v>
@@ -14453,19 +14515,19 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Tuesday 3 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L252" s="1" t="n">
-        <v>46056.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N252" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="253">
@@ -14476,21 +14538,21 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 5</t>
+          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025-12-12 08:22</t>
+          <t>2025-12-11 08:22</t>
         </is>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46003.34861111111</v>
+        <v>46002.34861111111</v>
       </c>
       <c r="F253" t="b">
         <v>1</v>
@@ -14503,15 +14565,15 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Tuesday 3 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L253" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46056.45833333334</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N253" s="1" t="n">
@@ -14526,21 +14588,21 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 6</t>
+          <t>Full ADOPT Grant: Round 5</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-12 08:22</t>
         </is>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46003.34861111111</v>
       </c>
       <c r="F254" t="b">
         <v>1</v>
@@ -14553,19 +14615,19 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L254" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N254" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="255">
@@ -14576,12 +14638,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
+          <t>ADOPT Facilitator Support Grant: Round 6</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -14603,15 +14665,15 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Thursday 7 May 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L255" s="1" t="n">
-        <v>46149.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N255" s="1" t="n">
@@ -14626,21 +14688,21 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – mid stage</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F256" t="b">
         <v>1</v>
@@ -14653,19 +14715,19 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Thursday 7 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L256" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N256" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="257">
@@ -14676,12 +14738,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – late stage</t>
+          <t>Energy catalyst round 11 – mid stage</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -14711,7 +14773,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N257" s="1" t="n">
@@ -14726,12 +14788,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – early stage</t>
+          <t>Energy catalyst round 11 – late stage</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -14761,7 +14823,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N258" s="1" t="n">
@@ -14776,12 +14838,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
+          <t>Energy catalyst round 11 – early stage</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -14803,15 +14865,15 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L259" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N259" s="1" t="n">
@@ -14826,12 +14888,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -14853,15 +14915,15 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L260" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N260" s="1" t="n">
@@ -14876,21 +14938,21 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 25</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-01-08 08:22</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46030.34861111111</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F261" t="b">
         <v>1</v>
@@ -14903,19 +14965,19 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L261" s="1" t="n">
-        <v>46085.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N261" s="1" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="262">
@@ -14926,21 +14988,21 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
+          <t>Innovate UK Innovation Loans Round 25</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-01-15 08:23</t>
+          <t>2026-01-08 08:22</t>
         </is>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46037.34930555556</v>
+        <v>46030.34861111111</v>
       </c>
       <c r="F262" t="b">
         <v>1</v>
@@ -14953,19 +15015,19 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Wednesday 11 February 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L262" s="1" t="n">
-        <v>46064.45833333334</v>
+        <v>46085.45833333334</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N262" s="1" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="263">
@@ -14976,21 +15038,21 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
+          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-01-20 08:24</t>
+          <t>2026-01-15 08:23</t>
         </is>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46042.35</v>
+        <v>46037.34930555556</v>
       </c>
       <c r="F263" t="b">
         <v>1</v>
@@ -15003,15 +15065,15 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 11 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L263" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46064.45833333334</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N263" s="1" t="n">
@@ -15026,21 +15088,21 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation FS</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-01-26 12:10</t>
+          <t>2026-01-20 08:24</t>
         </is>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46048.50694444445</v>
+        <v>46042.35</v>
       </c>
       <c r="F264" t="b">
         <v>1</v>
@@ -15053,19 +15115,19 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L264" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N264" s="1" t="n">
-        <v>46043</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="265">
@@ -15076,21 +15138,21 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
+          <t>Advanced manufacturing supply chain innovation FS</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-26 12:10</t>
         </is>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46048.50694444445</v>
       </c>
       <c r="F265" t="b">
         <v>1</v>
@@ -15103,19 +15165,19 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L265" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>£225,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N265" s="1" t="n">
-        <v>46050</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="266">
@@ -15126,12 +15188,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
+          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -15161,7 +15223,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£225,000</t>
         </is>
       </c>
       <c r="N266" s="1" t="n">
@@ -15176,21 +15238,21 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Robotics Adoption Programme skills development</t>
+          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-02-02 10:39</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46055.44375</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F267" t="b">
         <v>1</v>
@@ -15203,15 +15265,15 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L267" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N267" s="1" t="n">
@@ -15226,21 +15288,21 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
+          <t>Robotics Adoption Programme skills development</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-02-02 10:39</t>
         </is>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46055.44375</v>
       </c>
       <c r="F268" t="b">
         <v>1</v>
@@ -15253,15 +15315,15 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L268" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N268" s="1" t="n">
@@ -15276,12 +15338,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -15303,13 +15365,17 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L269" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M269" t="inlineStr"/>
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N269" s="1" t="n">
         <v>46050</v>
       </c>
@@ -15322,12 +15388,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -15368,21 +15434,21 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 6</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-02-09 10:53</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46062.45347222222</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F271" t="b">
         <v>1</v>
@@ -15395,19 +15461,15 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L271" s="1" t="n">
-        <v>46120.45833333334</v>
-      </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>£100,000</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M271" t="inlineStr"/>
       <c r="N271" s="1" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="272">
@@ -15418,21 +15480,21 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Zero Emission Flight Demonstrator Round 1</t>
+          <t>Full ADOPT Grant: Round 6</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-09 10:53</t>
         </is>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46062.45347222222</v>
       </c>
       <c r="F272" t="b">
         <v>1</v>
@@ -15445,19 +15507,19 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L272" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N272" s="1" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="273">
@@ -15468,12 +15530,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
+          <t>Zero Emission Flight Demonstrator Round 1</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -15495,15 +15557,15 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L273" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N273" s="1" t="n">
@@ -15518,12 +15580,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
+          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -15553,7 +15615,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>£10.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N274" s="1" t="n">
@@ -15568,21 +15630,21 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
+          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46066.44097222222</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F275" t="b">
         <v>1</v>
@@ -15595,15 +15657,15 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L275" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N275" s="1" t="n">
@@ -15618,21 +15680,21 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-02-17 10:40</t>
+          <t>2026-02-13 10:35</t>
         </is>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46070.44444444445</v>
+        <v>46066.44097222222</v>
       </c>
       <c r="F276" t="b">
         <v>1</v>
@@ -15653,7 +15715,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N276" s="1" t="n">
@@ -15668,21 +15730,21 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-17 10:40</t>
         </is>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46070.44444444445</v>
       </c>
       <c r="F277" t="b">
         <v>1</v>
@@ -15695,19 +15757,19 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L277" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N277" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="278">
@@ -15718,21 +15780,21 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>Semiconductors and components for smart electronic platforms</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-20 10:32</t>
         </is>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46073.43888888889</v>
       </c>
       <c r="F278" t="b">
         <v>1</v>
@@ -15745,15 +15807,15 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L278" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>£7.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N278" s="1" t="n">
@@ -15768,12 +15830,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>Robotics Adoption Hubs</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -15803,7 +15865,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£7.5 million</t>
         </is>
       </c>
       <c r="N279" s="1" t="n">
@@ -15818,21 +15880,21 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 7</t>
+          <t>Robotics Adoption Central Convening Body</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-02-26 10:40</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46079.44444444445</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F280" t="b">
         <v>1</v>
@@ -15845,19 +15907,19 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L280" s="1" t="n">
-        <v>46120.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N280" s="1" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="281">
@@ -15868,21 +15930,21 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-03-03 10:34</t>
+          <t>2026-02-26 10:40</t>
         </is>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46084.44027777778</v>
+        <v>46079.44444444445</v>
       </c>
       <c r="F281" t="b">
         <v>1</v>
@@ -15895,15 +15957,15 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L281" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N281" s="1" t="n">
@@ -15918,21 +15980,21 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
+          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-03-03 10:34</t>
         </is>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46084.44027777778</v>
       </c>
       <c r="F282" t="b">
         <v>1</v>
@@ -15945,19 +16007,19 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L282" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N282" s="1" t="n">
-        <v>46092</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="283">
@@ -15968,12 +16030,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
+          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -16003,7 +16065,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N283" s="1" t="n">
@@ -16018,12 +16080,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -16053,10 +16115,60 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
+      <c r="N284" s="1" t="n">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-03-11 10:34</t>
+        </is>
+      </c>
+      <c r="E285" s="1" t="n">
+        <v>46092.44027777778</v>
+      </c>
+      <c r="F285" t="b">
+        <v>1</v>
+      </c>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="b">
+        <v>0</v>
+      </c>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Wednesday 15 July 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L285" s="1" t="n">
+        <v>46218.45833333334</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
           <t>£15.0 million</t>
         </is>
       </c>
-      <c r="N284" s="1" t="n">
+      <c r="N285" s="1" t="n">
         <v>46092</v>
       </c>
     </row>
@@ -16098,10 +16210,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3">
@@ -16124,10 +16236,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C4" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -1253,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1326,6 +1326,118 @@
         <is>
           <t>Week commencing (Wed)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/advanced-manufacturing-supply-chains-potential-high-growth-smes/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-03-18 10:39</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46099.44375</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>22/04/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>46134.45833333334</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Secure Software for Resilient Growth</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/secure-software-for-resilient-growth/</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-03-18 10:39</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46099.44375</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>29/04/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>46141.45833333334</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>£5.0 million</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>46099</v>
       </c>
     </row>
   </sheetData>
@@ -1339,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1366,245 +1478,245 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46071</v>
+        <v>46078</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
         <v>9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46029</v>
+        <v>46036</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46008</v>
+        <v>46015</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45994</v>
+        <v>46001</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45980</v>
+        <v>45987</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45973</v>
+        <v>45980</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -1618,91 +1730,91 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45966</v>
+        <v>45973</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45959</v>
+        <v>45966</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45952</v>
+        <v>45959</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45945</v>
+        <v>45952</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45938</v>
+        <v>45945</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45931</v>
+        <v>45938</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45924</v>
+        <v>45931</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
@@ -1716,35 +1828,35 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45910</v>
+        <v>45917</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45903</v>
+        <v>45910</v>
       </c>
       <c r="B29" t="n">
         <v>2</v>
@@ -1758,169 +1870,183 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45896</v>
+        <v>45903</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45889</v>
+        <v>45896</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45882</v>
+        <v>45889</v>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45875</v>
+        <v>45882</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45868</v>
+        <v>45875</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45861</v>
+        <v>45868</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45854</v>
+        <v>45861</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45847</v>
+        <v>45854</v>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45840</v>
+        <v>45847</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45833</v>
+        <v>45840</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45826</v>
+        <v>45833</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
         <v>45819</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B42" t="n">
         <v>25</v>
       </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1935,7 +2061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N295"/>
+  <dimension ref="A1:N297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11109,26 +11235,26 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
+          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/advanced-manufacturing-supply-chains-potential-high-growth-smes/</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-03-18 10:39</t>
         </is>
       </c>
       <c r="E180" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46099.44375</v>
       </c>
       <c r="F180" t="b">
         <v>1</v>
@@ -11137,48 +11263,54 @@
       <c r="H180" t="b">
         <v>0</v>
       </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="J180" s="1" t="n">
+        <v>46099</v>
+      </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>22/04/2026                              11:00</t>
         </is>
       </c>
       <c r="L180" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N180" s="1" t="n">
-        <v>45819</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 2</t>
+          <t>Secure Software for Resilient Growth</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/secure-software-for-resilient-growth/</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-03-18 10:39</t>
         </is>
       </c>
       <c r="E181" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46099.44375</v>
       </c>
       <c r="F181" t="b">
         <v>1</v>
@@ -11187,23 +11319,29 @@
       <c r="H181" t="b">
         <v>0</v>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J181" s="1" t="n">
+        <v>46097</v>
+      </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Thursday 24 July 2025 11:00am</t>
+          <t>29/04/2026                              11:00</t>
         </is>
       </c>
       <c r="L181" s="1" t="n">
-        <v>45862.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N181" s="1" t="n">
-        <v>45819</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="182">
@@ -11214,12 +11352,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
+          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11241,15 +11379,15 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L182" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N182" s="1" t="n">
@@ -11264,12 +11402,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>New Innovators in Marine and Maritime, Great South West</t>
+          <t>ADOPT Facilitator Support Grant: Round 2</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11291,15 +11429,15 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 24 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L183" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45862.45833333334</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N183" s="1" t="n">
@@ -11314,12 +11452,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11341,15 +11479,15 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Thursday 4 September 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L184" s="1" t="n">
-        <v>45904.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N184" s="1" t="n">
@@ -11364,12 +11502,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – June 2025</t>
+          <t>New Innovators in Marine and Maritime, Great South West</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11391,13 +11529,17 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L185" s="1" t="n">
-        <v>45826.45833333334</v>
-      </c>
-      <c r="M185" t="inlineStr"/>
+        <v>45840.45833333334</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>£50,000</t>
+        </is>
+      </c>
       <c r="N185" s="1" t="n">
         <v>45819</v>
       </c>
@@ -11410,12 +11552,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11437,15 +11579,15 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 4 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L186" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45904.45833333334</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N186" s="1" t="n">
@@ -11460,12 +11602,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
+          <t>ATI Programme strategic batch: EoI – June 2025</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11487,17 +11629,13 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L187" s="1" t="n">
-        <v>45833.45833333334</v>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>£150,000</t>
-        </is>
-      </c>
+        <v>45826.45833333334</v>
+      </c>
+      <c r="M187" t="inlineStr"/>
       <c r="N187" s="1" t="n">
         <v>45819</v>
       </c>
@@ -11510,12 +11648,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11537,15 +11675,15 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L188" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N188" s="1" t="n">
@@ -11560,12 +11698,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11587,15 +11725,15 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L189" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N189" s="1" t="n">
@@ -11610,12 +11748,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
+          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11637,15 +11775,15 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L190" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N190" s="1" t="n">
@@ -11660,12 +11798,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
+          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11687,15 +11825,15 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L191" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N191" s="1" t="n">
@@ -11710,12 +11848,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Clean Air, Phase 3</t>
+          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11737,15 +11875,15 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L192" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N192" s="1" t="n">
@@ -11760,12 +11898,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
+          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11787,15 +11925,15 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L193" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N193" s="1" t="n">
@@ -11810,12 +11948,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
+          <t>Contracts for Innovation: Clean Air, Phase 3</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11837,15 +11975,15 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L194" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N194" s="1" t="n">
@@ -11860,12 +11998,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Canada-UK Semiconductors</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11887,15 +12025,15 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L195" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N195" s="1" t="n">
@@ -11910,12 +12048,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -11937,15 +12075,15 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L196" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N196" s="1" t="n">
@@ -11960,12 +12098,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Innovate UK innovation loans future economy: Round 21</t>
+          <t>Canada-UK Semiconductors</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -11987,15 +12125,15 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L197" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N197" s="1" t="n">
@@ -12010,12 +12148,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
+          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12037,15 +12175,15 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L198" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N198" s="1" t="n">
@@ -12060,12 +12198,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
+          <t>Innovate UK innovation loans future economy: Round 21</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12087,15 +12225,15 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L199" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N199" s="1" t="n">
@@ -12110,12 +12248,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
+          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12137,15 +12275,15 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L200" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N200" s="1" t="n">
@@ -12160,12 +12298,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 1</t>
+          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12195,7 +12333,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N201" s="1" t="n">
@@ -12210,12 +12348,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
+          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12237,11 +12375,17 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
+          <t>Wednesday 2 July 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L202" s="1" t="n">
+        <v>45840.45833333334</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
       <c r="N202" s="1" t="n">
         <v>45819</v>
       </c>
@@ -12254,12 +12398,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee Extension</t>
+          <t>Full ADOPT Grant: Round 1</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12281,11 +12425,17 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L203" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N203" s="1" t="n">
         <v>45819</v>
       </c>
@@ -12298,21 +12448,21 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
+          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025-06-16 22:04</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E204" s="1" t="n">
-        <v>45824.91944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F204" t="b">
         <v>1</v>
@@ -12325,17 +12475,11 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L204" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>£8,500</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
       <c r="N204" s="1" t="n">
         <v>45819</v>
       </c>
@@ -12348,21 +12492,21 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
+          <t>Horizon Europe Guarantee Extension</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E205" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F205" t="b">
         <v>1</v>
@@ -12375,19 +12519,13 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L205" s="1" t="n">
-        <v>45889.45833333334</v>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>£500,000</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
       <c r="N205" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="206">
@@ -12398,21 +12536,21 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 2</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-16 22:04</t>
         </is>
       </c>
       <c r="E206" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45824.91944444444</v>
       </c>
       <c r="F206" t="b">
         <v>1</v>
@@ -12425,19 +12563,19 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L206" s="1" t="n">
-        <v>45889.45833333334</v>
+        <v>45917.45833333334</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N206" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="207">
@@ -12448,21 +12586,21 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 22</t>
+          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025-07-03 08:52</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E207" s="1" t="n">
-        <v>45841.36944444444</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F207" t="b">
         <v>1</v>
@@ -12475,19 +12613,19 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L207" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N207" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="208">
@@ -12498,21 +12636,21 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Growth Catalyst Early Stage: New Innovators</t>
+          <t>Full ADOPT Grant Round 2</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E208" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F208" t="b">
         <v>1</v>
@@ -12525,19 +12663,19 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Wednesday 6 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L208" s="1" t="n">
-        <v>45875.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N208" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="209">
@@ -12548,21 +12686,21 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – July 2025</t>
+          <t>Innovate UK Innovation Loans Round 22</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-07-03 08:52</t>
         </is>
       </c>
       <c r="E209" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45841.36944444444</v>
       </c>
       <c r="F209" t="b">
         <v>1</v>
@@ -12575,13 +12713,17 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Wednesday 23 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L209" s="1" t="n">
-        <v>45861.45833333334</v>
-      </c>
-      <c r="M209" t="inlineStr"/>
+        <v>45896.45833333334</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>£5.0 million</t>
+        </is>
+      </c>
       <c r="N209" s="1" t="n">
         <v>45840</v>
       </c>
@@ -12594,21 +12736,21 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
+          <t>Growth Catalyst Early Stage: New Innovators</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E210" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F210" t="b">
         <v>1</v>
@@ -12621,19 +12763,19 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 6 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L210" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45875.45833333334</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N210" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="211">
@@ -12644,21 +12786,21 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
+          <t>ATI Programme strategic batch: EoI – July 2025</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E211" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F211" t="b">
         <v>1</v>
@@ -12671,19 +12813,15 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 23 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L211" s="1" t="n">
-        <v>45896.45833333334</v>
-      </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+        <v>45861.45833333334</v>
+      </c>
+      <c r="M211" t="inlineStr"/>
       <c r="N211" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="212">
@@ -12694,12 +12832,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -12744,12 +12882,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Future Flight: Regional Demonstrator 2</t>
+          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -12771,15 +12909,15 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Thursday 17 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L213" s="1" t="n">
-        <v>45855.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N213" s="1" t="n">
@@ -12794,21 +12932,21 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies</t>
+          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E214" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F214" t="b">
         <v>1</v>
@@ -12821,15 +12959,15 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L214" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N214" s="1" t="n">
@@ -12844,21 +12982,21 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate</t>
+          <t>Future Flight: Regional Demonstrator 2</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E215" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F215" t="b">
         <v>1</v>
@@ -12871,15 +13009,15 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Thursday 17 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L215" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45855.45833333334</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N215" s="1" t="n">
@@ -12894,12 +13032,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -12921,15 +13059,15 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L216" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N216" s="1" t="n">
@@ -12944,21 +13082,21 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 3</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025-07-25 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E217" s="1" t="n">
-        <v>45863.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F217" t="b">
         <v>1</v>
@@ -12971,19 +13109,19 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L217" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N217" s="1" t="n">
-        <v>45861</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="218">
@@ -12994,21 +13132,21 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Sovereign AI - Proof of concept</t>
+          <t>DRIVE35 Innovation Fund: Collaborate</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025-08-07 08:21</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E218" s="1" t="n">
-        <v>45876.34791666667</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F218" t="b">
         <v>1</v>
@@ -13021,19 +13159,19 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L218" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>£120,000</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N218" s="1" t="n">
-        <v>45875</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="219">
@@ -13044,21 +13182,21 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
+          <t>ADOPT Facilitator Support Grant: Round 3</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-07-25 08:20</t>
         </is>
       </c>
       <c r="E219" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45863.34722222222</v>
       </c>
       <c r="F219" t="b">
         <v>1</v>
@@ -13071,19 +13209,19 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L219" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N219" s="1" t="n">
-        <v>45882</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="220">
@@ -13094,21 +13232,21 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
+          <t>Sovereign AI - Proof of concept</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-08-07 08:21</t>
         </is>
       </c>
       <c r="E220" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45876.34791666667</v>
       </c>
       <c r="F220" t="b">
         <v>1</v>
@@ -13121,19 +13259,19 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L220" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>£4.5 million</t>
+          <t>£120,000</t>
         </is>
       </c>
       <c r="N220" s="1" t="n">
-        <v>45882</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="221">
@@ -13144,12 +13282,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13179,7 +13317,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£8.0 million</t>
         </is>
       </c>
       <c r="N221" s="1" t="n">
@@ -13194,21 +13332,21 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025-08-26 08:20</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E222" s="1" t="n">
-        <v>45895.34722222222</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F222" t="b">
         <v>1</v>
@@ -13221,19 +13359,19 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L222" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£4.5 million</t>
         </is>
       </c>
       <c r="N222" s="1" t="n">
-        <v>45889</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="223">
@@ -13244,21 +13382,21 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 3</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025-08-27 08:18</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E223" s="1" t="n">
-        <v>45896.34583333333</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F223" t="b">
         <v>1</v>
@@ -13271,19 +13409,19 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L223" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N223" s="1" t="n">
-        <v>45896</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="224">
@@ -13294,21 +13432,21 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – September 2025</t>
+          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025-09-01 08:20</t>
+          <t>2025-08-26 08:20</t>
         </is>
       </c>
       <c r="E224" s="1" t="n">
-        <v>45901.34722222222</v>
+        <v>45895.34722222222</v>
       </c>
       <c r="F224" t="b">
         <v>1</v>
@@ -13321,15 +13459,19 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L224" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M224" t="inlineStr"/>
+        <v>45910.45833333334</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N224" s="1" t="n">
-        <v>45896</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="225">
@@ -13340,21 +13482,21 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
+          <t>Full ADOPT Grant Round 3</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025-09-02 08:19</t>
+          <t>2025-08-27 08:18</t>
         </is>
       </c>
       <c r="E225" s="1" t="n">
-        <v>45902.34652777778</v>
+        <v>45896.34583333333</v>
       </c>
       <c r="F225" t="b">
         <v>1</v>
@@ -13367,15 +13509,15 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L225" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N225" s="1" t="n">
@@ -13390,21 +13532,21 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 4</t>
+          <t>ATI Programme strategic batch: EoI – September 2025</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025-09-04 08:18</t>
+          <t>2025-09-01 08:20</t>
         </is>
       </c>
       <c r="E226" s="1" t="n">
-        <v>45904.34583333333</v>
+        <v>45901.34722222222</v>
       </c>
       <c r="F226" t="b">
         <v>1</v>
@@ -13417,19 +13559,15 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L226" s="1" t="n">
-        <v>45945.45833333334</v>
-      </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>£2,500</t>
-        </is>
-      </c>
+        <v>45917.45833333334</v>
+      </c>
+      <c r="M226" t="inlineStr"/>
       <c r="N226" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="227">
@@ -13440,21 +13578,21 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 23</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025-09-05 08:18</t>
+          <t>2025-09-02 08:19</t>
         </is>
       </c>
       <c r="E227" s="1" t="n">
-        <v>45905.34583333333</v>
+        <v>45902.34652777778</v>
       </c>
       <c r="F227" t="b">
         <v>1</v>
@@ -13467,19 +13605,19 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L227" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N227" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="228">
@@ -13490,21 +13628,21 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
+          <t>ADOPT Facilitator Support Grant: Round 4</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025-09-12 08:17</t>
+          <t>2025-09-04 08:18</t>
         </is>
       </c>
       <c r="E228" s="1" t="n">
-        <v>45912.34513888889</v>
+        <v>45904.34583333333</v>
       </c>
       <c r="F228" t="b">
         <v>1</v>
@@ -13517,19 +13655,19 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Tuesday 28 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L228" s="1" t="n">
-        <v>45958.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N228" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="229">
@@ -13540,21 +13678,21 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
+          <t>Innovate UK Innovation Loans Round 23</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-09-16 08:19</t>
+          <t>2025-09-05 08:18</t>
         </is>
       </c>
       <c r="E229" s="1" t="n">
-        <v>45916.34652777778</v>
+        <v>45905.34583333333</v>
       </c>
       <c r="F229" t="b">
         <v>1</v>
@@ -13567,19 +13705,19 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L229" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N229" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="230">
@@ -13590,21 +13728,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025-09-17 08:18</t>
+          <t>2025-09-12 08:17</t>
         </is>
       </c>
       <c r="E230" s="1" t="n">
-        <v>45917.34583333333</v>
+        <v>45912.34513888889</v>
       </c>
       <c r="F230" t="b">
         <v>1</v>
@@ -13617,17 +13755,19 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L230" t="inlineStr"/>
+          <t>Tuesday 28 October 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L230" s="1" t="n">
+        <v>45958.45833333334</v>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N230" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="231">
@@ -13638,21 +13778,21 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025-09-18 08:17</t>
+          <t>2025-09-16 08:19</t>
         </is>
       </c>
       <c r="E231" s="1" t="n">
-        <v>45918.34513888889</v>
+        <v>45916.34652777778</v>
       </c>
       <c r="F231" t="b">
         <v>1</v>
@@ -13665,19 +13805,19 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Thursday 4 December 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L231" s="1" t="n">
-        <v>45995.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="N231" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="232">
@@ -13688,21 +13828,21 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Resource efficiency for resilience and sustainability FS</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025-09-20 08:16</t>
+          <t>2025-09-17 08:18</t>
         </is>
       </c>
       <c r="E232" s="1" t="n">
-        <v>45920.34444444445</v>
+        <v>45917.34583333333</v>
       </c>
       <c r="F232" t="b">
         <v>1</v>
@@ -13715,15 +13855,13 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Monday 3 November 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L232" s="1" t="n">
-        <v>45964.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N232" s="1" t="n">
@@ -13738,21 +13876,21 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025-09-23 08:18</t>
+          <t>2025-09-18 08:17</t>
         </is>
       </c>
       <c r="E233" s="1" t="n">
-        <v>45923.34583333333</v>
+        <v>45918.34513888889</v>
       </c>
       <c r="F233" t="b">
         <v>1</v>
@@ -13765,15 +13903,15 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Thursday 4 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L233" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45995.45833333334</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N233" s="1" t="n">
@@ -13788,21 +13926,21 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 4</t>
+          <t>Resource efficiency for resilience and sustainability FS</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025-09-29 08:20</t>
+          <t>2025-09-20 08:16</t>
         </is>
       </c>
       <c r="E234" s="1" t="n">
-        <v>45929.34722222222</v>
+        <v>45920.34444444445</v>
       </c>
       <c r="F234" t="b">
         <v>1</v>
@@ -13815,19 +13953,19 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Wednesday 3 December 2025 11:00am</t>
+          <t>Monday 3 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L234" s="1" t="n">
-        <v>45994.45833333334</v>
+        <v>45964.45833333334</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N234" s="1" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="235">
@@ -13838,21 +13976,21 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Eureka GlobalStars Japan 2026</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025-10-03 08:17</t>
+          <t>2025-09-23 08:18</t>
         </is>
       </c>
       <c r="E235" s="1" t="n">
-        <v>45933.34513888889</v>
+        <v>45923.34583333333</v>
       </c>
       <c r="F235" t="b">
         <v>1</v>
@@ -13865,19 +14003,19 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Wednesday 21 January 2026 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L235" s="1" t="n">
-        <v>46043.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N235" s="1" t="n">
-        <v>45931</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="236">
@@ -13888,21 +14026,21 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Feasibility studies 2</t>
+          <t>Farming Innovation Programme: Feasibility Round 4</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025-10-10 08:18</t>
+          <t>2025-09-29 08:20</t>
         </is>
       </c>
       <c r="E236" s="1" t="n">
-        <v>45940.34583333333</v>
+        <v>45929.34722222222</v>
       </c>
       <c r="F236" t="b">
         <v>1</v>
@@ -13915,19 +14053,19 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 3 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L236" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>45994.45833333334</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N236" s="1" t="n">
-        <v>45938</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="237">
@@ -13938,21 +14076,21 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – October 2025</t>
+          <t>Eureka GlobalStars Japan 2026</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025-10-14 08:17</t>
+          <t>2025-10-03 08:17</t>
         </is>
       </c>
       <c r="E237" s="1" t="n">
-        <v>45944.34513888889</v>
+        <v>45933.34513888889</v>
       </c>
       <c r="F237" t="b">
         <v>1</v>
@@ -13965,15 +14103,19 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 21 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L237" s="1" t="n">
-        <v>45952.45833333334</v>
-      </c>
-      <c r="M237" t="inlineStr"/>
+        <v>46043.45833333334</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>£600,000</t>
+        </is>
+      </c>
       <c r="N237" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="238">
@@ -13984,21 +14126,21 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Enable</t>
+          <t>CAM Pathfinder: Feasibility studies 2</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-10 08:18</t>
         </is>
       </c>
       <c r="E238" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45940.34583333333</v>
       </c>
       <c r="F238" t="b">
         <v>1</v>
@@ -14011,19 +14153,19 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L238" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N238" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="239">
@@ -14034,21 +14176,21 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Demonstrate</t>
+          <t>ATI Programme strategic batch EoI – October 2025</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-14 08:17</t>
         </is>
       </c>
       <c r="E239" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45944.34513888889</v>
       </c>
       <c r="F239" t="b">
         <v>1</v>
@@ -14061,19 +14203,15 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L239" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>£2.0 million</t>
-        </is>
-      </c>
+        <v>45952.45833333334</v>
+      </c>
+      <c r="M239" t="inlineStr"/>
       <c r="N239" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="240">
@@ -14084,21 +14222,21 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
+          <t>CAM Pathfinder: Enable</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025-10-16 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E240" s="1" t="n">
-        <v>45946.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F240" t="b">
         <v>1</v>
@@ -14111,15 +14249,15 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L240" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N240" s="1" t="n">
@@ -14134,21 +14272,21 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 5</t>
+          <t>CAM Pathfinder: Demonstrate</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025-10-17 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E241" s="1" t="n">
-        <v>45947.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F241" t="b">
         <v>1</v>
@@ -14161,15 +14299,15 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L241" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N241" s="1" t="n">
@@ -14184,21 +14322,21 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Battery Innovation Feasibility Studies Round 1</t>
+          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-16 08:19</t>
         </is>
       </c>
       <c r="E242" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45946.34652777778</v>
       </c>
       <c r="F242" t="b">
         <v>1</v>
@@ -14211,15 +14349,15 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L242" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N242" s="1" t="n">
@@ -14234,21 +14372,21 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Battery Innovation Concept Development Round 1</t>
+          <t>ADOPT Facilitator Support Grant: Round 5</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-17 08:19</t>
         </is>
       </c>
       <c r="E243" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45947.34652777778</v>
       </c>
       <c r="F243" t="b">
         <v>1</v>
@@ -14261,15 +14399,15 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L243" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N243" s="1" t="n">
@@ -14284,21 +14422,21 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>The Agentic AI Pioneers Prize</t>
+          <t>Battery Innovation Feasibility Studies Round 1</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025-10-21 08:20</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E244" s="1" t="n">
-        <v>45951.34722222222</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F244" t="b">
         <v>1</v>
@@ -14311,13 +14449,17 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L244" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M244" t="inlineStr"/>
+        <v>46008.45833333334</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>£500,000</t>
+        </is>
+      </c>
       <c r="N244" s="1" t="n">
         <v>45945</v>
       </c>
@@ -14330,21 +14472,21 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy efficiency – industrial research</t>
+          <t>Battery Innovation Concept Development Round 1</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E245" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F245" t="b">
         <v>1</v>
@@ -14357,19 +14499,19 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L245" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N245" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="246">
@@ -14380,21 +14522,21 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
+          <t>The Agentic AI Pioneers Prize</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-21 08:20</t>
         </is>
       </c>
       <c r="E246" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45951.34722222222</v>
       </c>
       <c r="F246" t="b">
         <v>1</v>
@@ -14407,19 +14549,15 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L246" s="1" t="n">
-        <v>46001.45833333334</v>
-      </c>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>£150,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M246" t="inlineStr"/>
       <c r="N246" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="247">
@@ -14430,21 +14568,21 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 4</t>
+          <t>MSI: SME resource and energy efficiency – industrial research</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025-10-23 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E247" s="1" t="n">
-        <v>45953.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F247" t="b">
         <v>1</v>
@@ -14465,7 +14603,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N247" s="1" t="n">
@@ -14480,21 +14618,21 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 24</t>
+          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025-10-24 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E248" s="1" t="n">
-        <v>45954.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F248" t="b">
         <v>1</v>
@@ -14507,15 +14645,15 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Wednesday 7 January 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L248" s="1" t="n">
-        <v>46029.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N248" s="1" t="n">
@@ -14530,21 +14668,21 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
+          <t>Full ADOPT Grant Round 4</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025-10-25 08:16</t>
+          <t>2025-10-23 08:19</t>
         </is>
       </c>
       <c r="E249" s="1" t="n">
-        <v>45955.34444444445</v>
+        <v>45953.34652777778</v>
       </c>
       <c r="F249" t="b">
         <v>1</v>
@@ -14557,15 +14695,15 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L249" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N249" s="1" t="n">
@@ -14580,21 +14718,21 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility Studies</t>
+          <t>Innovate UK Innovation Loans Round 24</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025-10-31 08:18</t>
+          <t>2025-10-24 08:19</t>
         </is>
       </c>
       <c r="E250" s="1" t="n">
-        <v>45961.34583333333</v>
+        <v>45954.34652777778</v>
       </c>
       <c r="F250" t="b">
         <v>1</v>
@@ -14607,19 +14745,19 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 7 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L250" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>46029.45833333334</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N250" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="251">
@@ -14630,21 +14768,21 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-25 08:16</t>
         </is>
       </c>
       <c r="E251" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45955.34444444445</v>
       </c>
       <c r="F251" t="b">
         <v>1</v>
@@ -14665,11 +14803,11 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>£3.4 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N251" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="252">
@@ -14680,21 +14818,21 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Increasing EV charging capacity on the strategic road network</t>
+          <t>National Materials Innovation Programme: Feasibility Studies</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-31 08:18</t>
         </is>
       </c>
       <c r="E252" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45961.34583333333</v>
       </c>
       <c r="F252" t="b">
         <v>1</v>
@@ -14707,15 +14845,15 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L252" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N252" s="1" t="n">
@@ -14730,21 +14868,21 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
+          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E253" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F253" t="b">
         <v>1</v>
@@ -14757,19 +14895,19 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L253" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£3.4 million</t>
         </is>
       </c>
       <c r="N253" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="254">
@@ -14780,21 +14918,21 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
+          <t>Increasing EV charging capacity on the strategic road network</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E254" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F254" t="b">
         <v>1</v>
@@ -14807,19 +14945,19 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L254" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N254" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="255">
@@ -14830,12 +14968,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – November 2025</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -14857,13 +14995,17 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L255" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M255" t="inlineStr"/>
+        <v>46001.45833333334</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
       <c r="N255" s="1" t="n">
         <v>45966</v>
       </c>
@@ -14876,21 +15018,21 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025-11-11 08:19</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E256" s="1" t="n">
-        <v>45972.34652777778</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F256" t="b">
         <v>1</v>
@@ -14903,15 +15045,15 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L256" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N256" s="1" t="n">
@@ -14926,21 +15068,21 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Women in Innovation Awards 2025/26</t>
+          <t>ATI Programme strategic batch EoI – November 2025</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025-11-27 13:23</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E257" s="1" t="n">
-        <v>45988.55763888889</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F257" t="b">
         <v>1</v>
@@ -14953,19 +15095,15 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L257" s="1" t="n">
-        <v>46057.45833333334</v>
-      </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>£75,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M257" t="inlineStr"/>
       <c r="N257" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="258">
@@ -14976,21 +15114,21 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025-12-02 08:22</t>
+          <t>2025-11-11 08:19</t>
         </is>
       </c>
       <c r="E258" s="1" t="n">
-        <v>45993.34861111111</v>
+        <v>45972.34652777778</v>
       </c>
       <c r="F258" t="b">
         <v>1</v>
@@ -15003,19 +15141,19 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L258" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N258" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="259">
@@ -15026,21 +15164,21 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
+          <t>Women in Innovation Awards 2025/26</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025-12-11 08:22</t>
+          <t>2025-11-27 13:23</t>
         </is>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46002.34861111111</v>
+        <v>45988.55763888889</v>
       </c>
       <c r="F259" t="b">
         <v>1</v>
@@ -15053,19 +15191,19 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Tuesday 3 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L259" s="1" t="n">
-        <v>46056.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£75,000</t>
         </is>
       </c>
       <c r="N259" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="260">
@@ -15076,21 +15214,21 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 5</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025-12-12 08:22</t>
+          <t>2025-12-02 08:22</t>
         </is>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46003.34861111111</v>
+        <v>45993.34861111111</v>
       </c>
       <c r="F260" t="b">
         <v>1</v>
@@ -15111,11 +15249,11 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N260" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="261">
@@ -15126,21 +15264,21 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 6</t>
+          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-11 08:22</t>
         </is>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46002.34861111111</v>
       </c>
       <c r="F261" t="b">
         <v>1</v>
@@ -15153,19 +15291,19 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Tuesday 3 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L261" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46056.45833333334</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N261" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="262">
@@ -15176,21 +15314,21 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
+          <t>Full ADOPT Grant: Round 5</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-12 08:22</t>
         </is>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46003.34861111111</v>
       </c>
       <c r="F262" t="b">
         <v>1</v>
@@ -15203,19 +15341,19 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Thursday 7 May 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L262" s="1" t="n">
-        <v>46149.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N262" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="263">
@@ -15226,21 +15364,21 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – mid stage</t>
+          <t>ADOPT Facilitator Support Grant: Round 6</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F263" t="b">
         <v>1</v>
@@ -15253,19 +15391,19 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L263" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N263" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="264">
@@ -15276,21 +15414,21 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – late stage</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F264" t="b">
         <v>1</v>
@@ -15303,19 +15441,19 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Thursday 7 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L264" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N264" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="265">
@@ -15326,12 +15464,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – early stage</t>
+          <t>Energy catalyst round 11 – mid stage</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -15361,7 +15499,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N265" s="1" t="n">
@@ -15376,12 +15514,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
+          <t>Energy catalyst round 11 – late stage</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -15403,15 +15541,15 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L266" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N266" s="1" t="n">
@@ -15426,12 +15564,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
+          <t>Energy catalyst round 11 – early stage</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -15453,15 +15591,15 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L267" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N267" s="1" t="n">
@@ -15476,21 +15614,21 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 25</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-01-08 08:22</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46030.34861111111</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F268" t="b">
         <v>1</v>
@@ -15503,19 +15641,19 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L268" s="1" t="n">
-        <v>46085.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N268" s="1" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="269">
@@ -15526,21 +15664,21 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-01-15 08:23</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46037.34930555556</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F269" t="b">
         <v>1</v>
@@ -15553,19 +15691,19 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Wednesday 11 February 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L269" s="1" t="n">
-        <v>46064.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N269" s="1" t="n">
-        <v>46036</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="270">
@@ -15576,21 +15714,21 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
+          <t>Innovate UK Innovation Loans Round 25</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-01-20 08:24</t>
+          <t>2026-01-08 08:22</t>
         </is>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46042.35</v>
+        <v>46030.34861111111</v>
       </c>
       <c r="F270" t="b">
         <v>1</v>
@@ -15603,19 +15741,19 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L270" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46085.45833333334</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N270" s="1" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="271">
@@ -15626,21 +15764,21 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation FS</t>
+          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-01-26 12:10</t>
+          <t>2026-01-15 08:23</t>
         </is>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46048.50694444445</v>
+        <v>46037.34930555556</v>
       </c>
       <c r="F271" t="b">
         <v>1</v>
@@ -15653,19 +15791,19 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 11 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L271" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46064.45833333334</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N271" s="1" t="n">
-        <v>46043</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="272">
@@ -15676,21 +15814,21 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-20 08:24</t>
         </is>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46042.35</v>
       </c>
       <c r="F272" t="b">
         <v>1</v>
@@ -15703,19 +15841,19 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L272" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>£225,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N272" s="1" t="n">
-        <v>46050</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="273">
@@ -15726,21 +15864,21 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
+          <t>Advanced manufacturing supply chain innovation FS</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-26 12:10</t>
         </is>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46048.50694444445</v>
       </c>
       <c r="F273" t="b">
         <v>1</v>
@@ -15753,19 +15891,19 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L273" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N273" s="1" t="n">
-        <v>46050</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="274">
@@ -15776,21 +15914,21 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Robotics Adoption Programme skills development</t>
+          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-02-02 10:39</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46055.44375</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F274" t="b">
         <v>1</v>
@@ -15803,15 +15941,15 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L274" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£225,000</t>
         </is>
       </c>
       <c r="N274" s="1" t="n">
@@ -15826,21 +15964,21 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
+          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F275" t="b">
         <v>1</v>
@@ -15853,15 +15991,15 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L275" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N275" s="1" t="n">
@@ -15876,21 +16014,21 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
+          <t>Robotics Adoption Programme skills development</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-02-02 10:39</t>
         </is>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46055.44375</v>
       </c>
       <c r="F276" t="b">
         <v>1</v>
@@ -15903,13 +16041,17 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L276" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M276" t="inlineStr"/>
+        <v>46106.45833333334</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>£500,000</t>
+        </is>
+      </c>
       <c r="N276" s="1" t="n">
         <v>46050</v>
       </c>
@@ -15922,12 +16064,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -15949,13 +16091,17 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L277" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M277" t="inlineStr"/>
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N277" s="1" t="n">
         <v>46050</v>
       </c>
@@ -15968,21 +16114,21 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 6</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-02-09 10:53</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46062.45347222222</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F278" t="b">
         <v>1</v>
@@ -15995,19 +16141,15 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L278" s="1" t="n">
-        <v>46120.45833333334</v>
-      </c>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>£100,000</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M278" t="inlineStr"/>
       <c r="N278" s="1" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="279">
@@ -16018,21 +16160,21 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Zero Emission Flight Demonstrator Round 1</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F279" t="b">
         <v>1</v>
@@ -16045,19 +16187,15 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L279" s="1" t="n">
-        <v>46113.45833333334</v>
-      </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>£5.0 million</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M279" t="inlineStr"/>
       <c r="N279" s="1" t="n">
-        <v>46064</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="280">
@@ -16068,21 +16206,21 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
+          <t>Full ADOPT Grant: Round 6</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-09 10:53</t>
         </is>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46062.45347222222</v>
       </c>
       <c r="F280" t="b">
         <v>1</v>
@@ -16095,19 +16233,19 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L280" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N280" s="1" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="281">
@@ -16118,12 +16256,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
+          <t>Zero Emission Flight Demonstrator Round 1</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -16145,15 +16283,15 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L281" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>£10.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N281" s="1" t="n">
@@ -16168,21 +16306,21 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
+          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46066.44097222222</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F282" t="b">
         <v>1</v>
@@ -16195,15 +16333,15 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L282" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N282" s="1" t="n">
@@ -16218,21 +16356,21 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-02-17 10:40</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46070.44444444445</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F283" t="b">
         <v>1</v>
@@ -16245,15 +16383,15 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L283" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N283" s="1" t="n">
@@ -16268,21 +16406,21 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-13 10:35</t>
         </is>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46066.44097222222</v>
       </c>
       <c r="F284" t="b">
         <v>1</v>
@@ -16295,19 +16433,19 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L284" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N284" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="285">
@@ -16318,21 +16456,21 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-17 10:40</t>
         </is>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46070.44444444445</v>
       </c>
       <c r="F285" t="b">
         <v>1</v>
@@ -16353,11 +16491,11 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>£7.5 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N285" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="286">
@@ -16368,21 +16506,21 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>Semiconductors and components for smart electronic platforms</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-20 10:32</t>
         </is>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46073.43888888889</v>
       </c>
       <c r="F286" t="b">
         <v>1</v>
@@ -16395,11 +16533,11 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L286" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M286" t="inlineStr">
         <is>
@@ -16418,21 +16556,21 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 7</t>
+          <t>Robotics Adoption Hubs</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-02-26 10:40</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46079.44444444445</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F287" t="b">
         <v>1</v>
@@ -16445,19 +16583,19 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L287" s="1" t="n">
-        <v>46120.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£7.5 million</t>
         </is>
       </c>
       <c r="N287" s="1" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="288">
@@ -16468,21 +16606,21 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
+          <t>Robotics Adoption Central Convening Body</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-03-03 10:34</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46084.44027777778</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F288" t="b">
         <v>1</v>
@@ -16495,19 +16633,19 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L288" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N288" s="1" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="289">
@@ -16518,21 +16656,21 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-02-26 10:40</t>
         </is>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46079.44444444445</v>
       </c>
       <c r="F289" t="b">
         <v>1</v>
@@ -16545,19 +16683,19 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L289" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N289" s="1" t="n">
-        <v>46092</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="290">
@@ -16568,21 +16706,21 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
+          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-03-03 10:34</t>
         </is>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46084.44027777778</v>
       </c>
       <c r="F290" t="b">
         <v>1</v>
@@ -16595,19 +16733,19 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L290" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N290" s="1" t="n">
-        <v>46092</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="291">
@@ -16618,12 +16756,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -16653,7 +16791,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>£15.0 million</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N291" s="1" t="n">
@@ -16668,21 +16806,21 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>AI Champions: Frontier AI Phase 1</t>
+          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-03-12 10:34</t>
+          <t>2026-03-11 10:34</t>
         </is>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46093.44027777778</v>
+        <v>46092.44027777778</v>
       </c>
       <c r="F292" t="b">
         <v>1</v>
@@ -16695,15 +16833,15 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Wednesday 29 April 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L292" s="1" t="n">
-        <v>46141.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N292" s="1" t="n">
@@ -16718,21 +16856,21 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Frontier AI Discovery</t>
+          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-03-17 10:45</t>
+          <t>2026-03-11 10:34</t>
         </is>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46098.44791666666</v>
+        <v>46092.44027777778</v>
       </c>
       <c r="F293" t="b">
         <v>1</v>
@@ -16745,15 +16883,15 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L293" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£15.0 million</t>
         </is>
       </c>
       <c r="N293" s="1" t="n">
@@ -16768,21 +16906,21 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Secure Software for Resilient Growth</t>
+          <t>AI Champions: Frontier AI Phase 1</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-03-17 10:45</t>
+          <t>2026-03-12 10:34</t>
         </is>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46098.44791666666</v>
+        <v>46093.44027777778</v>
       </c>
       <c r="F294" t="b">
         <v>1</v>
@@ -16803,7 +16941,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N294" s="1" t="n">
@@ -16818,12 +16956,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
+          <t>Frontier AI Discovery</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -16845,18 +16983,118 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
+          <t>Wednesday 10 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L295" s="1" t="n">
+        <v>46183.45833333334</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>£50,000</t>
+        </is>
+      </c>
+      <c r="N295" s="1" t="n">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Secure Software for Resilient Growth</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2026-03-17 10:45</t>
+        </is>
+      </c>
+      <c r="E296" s="1" t="n">
+        <v>46098.44791666666</v>
+      </c>
+      <c r="F296" t="b">
+        <v>1</v>
+      </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="b">
+        <v>0</v>
+      </c>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Wednesday 29 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L296" s="1" t="n">
+        <v>46141.45833333334</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>£750,000</t>
+        </is>
+      </c>
+      <c r="N296" s="1" t="n">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026-03-17 10:45</t>
+        </is>
+      </c>
+      <c r="E297" s="1" t="n">
+        <v>46098.44791666666</v>
+      </c>
+      <c r="F297" t="b">
+        <v>1</v>
+      </c>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="b">
+        <v>0</v>
+      </c>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
           <t>Wednesday 22 April 2026 11:00am</t>
         </is>
       </c>
-      <c r="L295" s="1" t="n">
+      <c r="L297" s="1" t="n">
         <v>46134.45833333334</v>
       </c>
-      <c r="M295" t="inlineStr">
+      <c r="M297" t="inlineStr">
         <is>
           <t>£100,000</t>
         </is>
       </c>
-      <c r="N295" s="1" t="n">
+      <c r="N297" s="1" t="n">
         <v>46092</v>
       </c>
     </row>
@@ -16898,10 +17136,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C2" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3">
@@ -16924,10 +17162,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C4" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -1377,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,6 +1450,118 @@
         <is>
           <t>Week commencing (Wed)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dual-use aviation systems and autonomy</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/dual-use-aviation-systems-and-autonomy/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:22</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46141.47361111111</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>03/06/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>£10.0 million</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Counter UAS (Uncrewed Aerial Systems) Technologies</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/counter-uas-uncrewed-aerial-systems-technologies/</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:22</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46141.47361111111</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>03/06/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>£5.0 million</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>46141</v>
       </c>
     </row>
   </sheetData>
@@ -1463,7 +1575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1490,329 +1602,329 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="B3" t="n">
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46099</v>
+        <v>46106</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46071</v>
+        <v>46078</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
         <v>9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46029</v>
+        <v>46036</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46008</v>
+        <v>46015</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45994</v>
+        <v>46001</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45980</v>
+        <v>45987</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45973</v>
+        <v>45980</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -1826,91 +1938,91 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45966</v>
+        <v>45973</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45959</v>
+        <v>45966</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45952</v>
+        <v>45959</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45945</v>
+        <v>45952</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45938</v>
+        <v>45945</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45931</v>
+        <v>45938</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45924</v>
+        <v>45931</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -1924,35 +2036,35 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45910</v>
+        <v>45917</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45903</v>
+        <v>45910</v>
       </c>
       <c r="B35" t="n">
         <v>2</v>
@@ -1966,169 +2078,183 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45896</v>
+        <v>45903</v>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45889</v>
+        <v>45896</v>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45882</v>
+        <v>45889</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45875</v>
+        <v>45882</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45868</v>
+        <v>45875</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45861</v>
+        <v>45868</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45854</v>
+        <v>45861</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45847</v>
+        <v>45854</v>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45840</v>
+        <v>45847</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45833</v>
+        <v>45840</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45826</v>
+        <v>45833</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
         <v>45819</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B48" t="n">
         <v>25</v>
       </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
         <v>25</v>
       </c>
     </row>
@@ -2143,7 +2269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N379"/>
+  <dimension ref="A1:N381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14473,26 +14599,26 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
+          <t>Dual-use aviation systems and autonomy</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/dual-use-aviation-systems-and-autonomy/</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-04-29 11:22</t>
         </is>
       </c>
       <c r="E238" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46141.47361111111</v>
       </c>
       <c r="F238" t="b">
         <v>1</v>
@@ -14501,48 +14627,54 @@
       <c r="H238" t="b">
         <v>0</v>
       </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J238" s="1" t="n">
+        <v>46147</v>
+      </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>03/06/2026                              11:00</t>
         </is>
       </c>
       <c r="L238" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N238" s="1" t="n">
-        <v>45819</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 2</t>
+          <t>Counter UAS (Uncrewed Aerial Systems) Technologies</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/counter-uas-uncrewed-aerial-systems-technologies/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-04-29 11:22</t>
         </is>
       </c>
       <c r="E239" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46141.47361111111</v>
       </c>
       <c r="F239" t="b">
         <v>1</v>
@@ -14551,23 +14683,29 @@
       <c r="H239" t="b">
         <v>0</v>
       </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J239" s="1" t="n">
+        <v>46147</v>
+      </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Thursday 24 July 2025 11:00am</t>
+          <t>03/06/2026                              11:00</t>
         </is>
       </c>
       <c r="L239" s="1" t="n">
-        <v>45862.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N239" s="1" t="n">
-        <v>45819</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="240">
@@ -14578,12 +14716,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
+          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -14605,15 +14743,15 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L240" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N240" s="1" t="n">
@@ -14628,12 +14766,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>New Innovators in Marine and Maritime, Great South West</t>
+          <t>ADOPT Facilitator Support Grant: Round 2</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -14655,15 +14793,15 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 24 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L241" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45862.45833333334</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N241" s="1" t="n">
@@ -14678,12 +14816,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -14705,15 +14843,15 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Thursday 4 September 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L242" s="1" t="n">
-        <v>45904.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N242" s="1" t="n">
@@ -14728,12 +14866,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – June 2025</t>
+          <t>New Innovators in Marine and Maritime, Great South West</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -14755,13 +14893,17 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L243" s="1" t="n">
-        <v>45826.45833333334</v>
-      </c>
-      <c r="M243" t="inlineStr"/>
+        <v>45840.45833333334</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>£50,000</t>
+        </is>
+      </c>
       <c r="N243" s="1" t="n">
         <v>45819</v>
       </c>
@@ -14774,12 +14916,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -14801,15 +14943,15 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 4 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L244" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45904.45833333334</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N244" s="1" t="n">
@@ -14824,12 +14966,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
+          <t>ATI Programme strategic batch: EoI – June 2025</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -14851,17 +14993,13 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L245" s="1" t="n">
-        <v>45833.45833333334</v>
-      </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>£150,000</t>
-        </is>
-      </c>
+        <v>45826.45833333334</v>
+      </c>
+      <c r="M245" t="inlineStr"/>
       <c r="N245" s="1" t="n">
         <v>45819</v>
       </c>
@@ -14874,12 +15012,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -14901,15 +15039,15 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L246" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N246" s="1" t="n">
@@ -14924,12 +15062,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -14951,15 +15089,15 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L247" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N247" s="1" t="n">
@@ -14974,12 +15112,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
+          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -15001,15 +15139,15 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L248" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N248" s="1" t="n">
@@ -15024,12 +15162,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
+          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -15051,15 +15189,15 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L249" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N249" s="1" t="n">
@@ -15074,12 +15212,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Clean Air, Phase 3</t>
+          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -15101,15 +15239,15 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L250" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N250" s="1" t="n">
@@ -15124,12 +15262,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
+          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -15151,15 +15289,15 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L251" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N251" s="1" t="n">
@@ -15174,12 +15312,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
+          <t>Contracts for Innovation: Clean Air, Phase 3</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -15201,15 +15339,15 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L252" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N252" s="1" t="n">
@@ -15224,12 +15362,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Canada-UK Semiconductors</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -15251,15 +15389,15 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L253" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N253" s="1" t="n">
@@ -15274,12 +15412,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15301,15 +15439,15 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L254" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N254" s="1" t="n">
@@ -15324,12 +15462,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Innovate UK innovation loans future economy: Round 21</t>
+          <t>Canada-UK Semiconductors</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -15351,15 +15489,15 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L255" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N255" s="1" t="n">
@@ -15374,12 +15512,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
+          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -15401,15 +15539,15 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L256" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N256" s="1" t="n">
@@ -15424,12 +15562,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
+          <t>Innovate UK innovation loans future economy: Round 21</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -15451,15 +15589,15 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L257" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N257" s="1" t="n">
@@ -15474,12 +15612,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
+          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -15501,15 +15639,15 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L258" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N258" s="1" t="n">
@@ -15524,12 +15662,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 1</t>
+          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -15559,7 +15697,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N259" s="1" t="n">
@@ -15574,12 +15712,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
+          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -15601,11 +15739,17 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
+          <t>Wednesday 2 July 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L260" s="1" t="n">
+        <v>45840.45833333334</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
       <c r="N260" s="1" t="n">
         <v>45819</v>
       </c>
@@ -15618,12 +15762,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee Extension</t>
+          <t>Full ADOPT Grant: Round 1</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -15645,11 +15789,17 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L261" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N261" s="1" t="n">
         <v>45819</v>
       </c>
@@ -15662,21 +15812,21 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
+          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025-06-16 22:04</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E262" s="1" t="n">
-        <v>45824.91944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F262" t="b">
         <v>1</v>
@@ -15689,17 +15839,11 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L262" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>£8,500</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
       <c r="N262" s="1" t="n">
         <v>45819</v>
       </c>
@@ -15712,21 +15856,21 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
+          <t>Horizon Europe Guarantee Extension</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E263" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F263" t="b">
         <v>1</v>
@@ -15739,19 +15883,13 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L263" s="1" t="n">
-        <v>45889.45833333334</v>
-      </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>£500,000</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
       <c r="N263" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="264">
@@ -15762,21 +15900,21 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 2</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-16 22:04</t>
         </is>
       </c>
       <c r="E264" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45824.91944444444</v>
       </c>
       <c r="F264" t="b">
         <v>1</v>
@@ -15789,19 +15927,19 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L264" s="1" t="n">
-        <v>45889.45833333334</v>
+        <v>45917.45833333334</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N264" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="265">
@@ -15812,21 +15950,21 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 22</t>
+          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025-07-03 08:52</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E265" s="1" t="n">
-        <v>45841.36944444444</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F265" t="b">
         <v>1</v>
@@ -15839,19 +15977,19 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L265" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N265" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="266">
@@ -15862,21 +16000,21 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Growth Catalyst Early Stage: New Innovators</t>
+          <t>Full ADOPT Grant Round 2</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E266" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F266" t="b">
         <v>1</v>
@@ -15889,19 +16027,19 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Wednesday 6 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L266" s="1" t="n">
-        <v>45875.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N266" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="267">
@@ -15912,21 +16050,21 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – July 2025</t>
+          <t>Innovate UK Innovation Loans Round 22</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-07-03 08:52</t>
         </is>
       </c>
       <c r="E267" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45841.36944444444</v>
       </c>
       <c r="F267" t="b">
         <v>1</v>
@@ -15939,13 +16077,17 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Wednesday 23 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L267" s="1" t="n">
-        <v>45861.45833333334</v>
-      </c>
-      <c r="M267" t="inlineStr"/>
+        <v>45896.45833333334</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>£5.0 million</t>
+        </is>
+      </c>
       <c r="N267" s="1" t="n">
         <v>45840</v>
       </c>
@@ -15958,21 +16100,21 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
+          <t>Growth Catalyst Early Stage: New Innovators</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E268" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F268" t="b">
         <v>1</v>
@@ -15985,19 +16127,19 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 6 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L268" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45875.45833333334</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N268" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="269">
@@ -16008,21 +16150,21 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
+          <t>ATI Programme strategic batch: EoI – July 2025</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E269" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F269" t="b">
         <v>1</v>
@@ -16035,19 +16177,15 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 23 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L269" s="1" t="n">
-        <v>45896.45833333334</v>
-      </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+        <v>45861.45833333334</v>
+      </c>
+      <c r="M269" t="inlineStr"/>
       <c r="N269" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="270">
@@ -16058,12 +16196,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -16108,12 +16246,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Future Flight: Regional Demonstrator 2</t>
+          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -16135,15 +16273,15 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Thursday 17 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L271" s="1" t="n">
-        <v>45855.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N271" s="1" t="n">
@@ -16158,21 +16296,21 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies</t>
+          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E272" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F272" t="b">
         <v>1</v>
@@ -16185,15 +16323,15 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L272" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N272" s="1" t="n">
@@ -16208,21 +16346,21 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate</t>
+          <t>Future Flight: Regional Demonstrator 2</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E273" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F273" t="b">
         <v>1</v>
@@ -16235,15 +16373,15 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Thursday 17 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L273" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45855.45833333334</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N273" s="1" t="n">
@@ -16258,12 +16396,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -16285,15 +16423,15 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L274" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N274" s="1" t="n">
@@ -16308,21 +16446,21 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 3</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025-07-25 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E275" s="1" t="n">
-        <v>45863.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F275" t="b">
         <v>1</v>
@@ -16335,19 +16473,19 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L275" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N275" s="1" t="n">
-        <v>45861</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="276">
@@ -16358,21 +16496,21 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Sovereign AI - Proof of concept</t>
+          <t>DRIVE35 Innovation Fund: Collaborate</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025-08-07 08:21</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E276" s="1" t="n">
-        <v>45876.34791666667</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F276" t="b">
         <v>1</v>
@@ -16385,19 +16523,19 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L276" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>£120,000</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N276" s="1" t="n">
-        <v>45875</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="277">
@@ -16408,21 +16546,21 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
+          <t>ADOPT Facilitator Support Grant: Round 3</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-07-25 08:20</t>
         </is>
       </c>
       <c r="E277" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45863.34722222222</v>
       </c>
       <c r="F277" t="b">
         <v>1</v>
@@ -16435,19 +16573,19 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L277" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N277" s="1" t="n">
-        <v>45882</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="278">
@@ -16458,21 +16596,21 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
+          <t>Sovereign AI - Proof of concept</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-08-07 08:21</t>
         </is>
       </c>
       <c r="E278" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45876.34791666667</v>
       </c>
       <c r="F278" t="b">
         <v>1</v>
@@ -16485,19 +16623,19 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L278" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>£4.5 million</t>
+          <t>£120,000</t>
         </is>
       </c>
       <c r="N278" s="1" t="n">
-        <v>45882</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="279">
@@ -16508,12 +16646,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -16543,7 +16681,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£8.0 million</t>
         </is>
       </c>
       <c r="N279" s="1" t="n">
@@ -16558,21 +16696,21 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2025-08-26 08:20</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E280" s="1" t="n">
-        <v>45895.34722222222</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F280" t="b">
         <v>1</v>
@@ -16585,19 +16723,19 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L280" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£4.5 million</t>
         </is>
       </c>
       <c r="N280" s="1" t="n">
-        <v>45889</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="281">
@@ -16608,21 +16746,21 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 3</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025-08-27 08:18</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E281" s="1" t="n">
-        <v>45896.34583333333</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F281" t="b">
         <v>1</v>
@@ -16635,19 +16773,19 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L281" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N281" s="1" t="n">
-        <v>45896</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="282">
@@ -16658,21 +16796,21 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – September 2025</t>
+          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2025-09-01 08:20</t>
+          <t>2025-08-26 08:20</t>
         </is>
       </c>
       <c r="E282" s="1" t="n">
-        <v>45901.34722222222</v>
+        <v>45895.34722222222</v>
       </c>
       <c r="F282" t="b">
         <v>1</v>
@@ -16685,15 +16823,19 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L282" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M282" t="inlineStr"/>
+        <v>45910.45833333334</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N282" s="1" t="n">
-        <v>45896</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="283">
@@ -16704,21 +16846,21 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
+          <t>Full ADOPT Grant Round 3</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2025-09-02 08:19</t>
+          <t>2025-08-27 08:18</t>
         </is>
       </c>
       <c r="E283" s="1" t="n">
-        <v>45902.34652777778</v>
+        <v>45896.34583333333</v>
       </c>
       <c r="F283" t="b">
         <v>1</v>
@@ -16731,15 +16873,15 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L283" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N283" s="1" t="n">
@@ -16754,21 +16896,21 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 4</t>
+          <t>ATI Programme strategic batch: EoI – September 2025</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025-09-04 08:18</t>
+          <t>2025-09-01 08:20</t>
         </is>
       </c>
       <c r="E284" s="1" t="n">
-        <v>45904.34583333333</v>
+        <v>45901.34722222222</v>
       </c>
       <c r="F284" t="b">
         <v>1</v>
@@ -16781,19 +16923,15 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L284" s="1" t="n">
-        <v>45945.45833333334</v>
-      </c>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>£2,500</t>
-        </is>
-      </c>
+        <v>45917.45833333334</v>
+      </c>
+      <c r="M284" t="inlineStr"/>
       <c r="N284" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="285">
@@ -16804,21 +16942,21 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 23</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025-09-05 08:18</t>
+          <t>2025-09-02 08:19</t>
         </is>
       </c>
       <c r="E285" s="1" t="n">
-        <v>45905.34583333333</v>
+        <v>45902.34652777778</v>
       </c>
       <c r="F285" t="b">
         <v>1</v>
@@ -16831,19 +16969,19 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L285" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N285" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="286">
@@ -16854,21 +16992,21 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
+          <t>ADOPT Facilitator Support Grant: Round 4</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2025-09-12 08:17</t>
+          <t>2025-09-04 08:18</t>
         </is>
       </c>
       <c r="E286" s="1" t="n">
-        <v>45912.34513888889</v>
+        <v>45904.34583333333</v>
       </c>
       <c r="F286" t="b">
         <v>1</v>
@@ -16881,19 +17019,19 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Tuesday 28 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L286" s="1" t="n">
-        <v>45958.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N286" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="287">
@@ -16904,21 +17042,21 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
+          <t>Innovate UK Innovation Loans Round 23</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025-09-16 08:19</t>
+          <t>2025-09-05 08:18</t>
         </is>
       </c>
       <c r="E287" s="1" t="n">
-        <v>45916.34652777778</v>
+        <v>45905.34583333333</v>
       </c>
       <c r="F287" t="b">
         <v>1</v>
@@ -16931,19 +17069,19 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L287" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N287" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="288">
@@ -16954,21 +17092,21 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025-09-17 08:18</t>
+          <t>2025-09-12 08:17</t>
         </is>
       </c>
       <c r="E288" s="1" t="n">
-        <v>45917.34583333333</v>
+        <v>45912.34513888889</v>
       </c>
       <c r="F288" t="b">
         <v>1</v>
@@ -16981,17 +17119,19 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L288" t="inlineStr"/>
+          <t>Tuesday 28 October 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L288" s="1" t="n">
+        <v>45958.45833333334</v>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N288" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="289">
@@ -17002,21 +17142,21 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025-09-18 08:17</t>
+          <t>2025-09-16 08:19</t>
         </is>
       </c>
       <c r="E289" s="1" t="n">
-        <v>45918.34513888889</v>
+        <v>45916.34652777778</v>
       </c>
       <c r="F289" t="b">
         <v>1</v>
@@ -17029,19 +17169,19 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Thursday 4 December 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L289" s="1" t="n">
-        <v>45995.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="N289" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="290">
@@ -17052,21 +17192,21 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Resource efficiency for resilience and sustainability FS</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025-09-20 08:16</t>
+          <t>2025-09-17 08:18</t>
         </is>
       </c>
       <c r="E290" s="1" t="n">
-        <v>45920.34444444445</v>
+        <v>45917.34583333333</v>
       </c>
       <c r="F290" t="b">
         <v>1</v>
@@ -17079,15 +17219,13 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Monday 3 November 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L290" s="1" t="n">
-        <v>45964.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N290" s="1" t="n">
@@ -17102,21 +17240,21 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025-09-23 08:18</t>
+          <t>2025-09-18 08:17</t>
         </is>
       </c>
       <c r="E291" s="1" t="n">
-        <v>45923.34583333333</v>
+        <v>45918.34513888889</v>
       </c>
       <c r="F291" t="b">
         <v>1</v>
@@ -17129,15 +17267,15 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Thursday 4 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L291" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45995.45833333334</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N291" s="1" t="n">
@@ -17152,21 +17290,21 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 4</t>
+          <t>Resource efficiency for resilience and sustainability FS</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025-09-29 08:20</t>
+          <t>2025-09-20 08:16</t>
         </is>
       </c>
       <c r="E292" s="1" t="n">
-        <v>45929.34722222222</v>
+        <v>45920.34444444445</v>
       </c>
       <c r="F292" t="b">
         <v>1</v>
@@ -17179,19 +17317,19 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Wednesday 3 December 2025 11:00am</t>
+          <t>Monday 3 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L292" s="1" t="n">
-        <v>45994.45833333334</v>
+        <v>45964.45833333334</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N292" s="1" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="293">
@@ -17202,21 +17340,21 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Eureka GlobalStars Japan 2026</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025-10-03 08:17</t>
+          <t>2025-09-23 08:18</t>
         </is>
       </c>
       <c r="E293" s="1" t="n">
-        <v>45933.34513888889</v>
+        <v>45923.34583333333</v>
       </c>
       <c r="F293" t="b">
         <v>1</v>
@@ -17229,19 +17367,19 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Wednesday 21 January 2026 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L293" s="1" t="n">
-        <v>46043.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N293" s="1" t="n">
-        <v>45931</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="294">
@@ -17252,21 +17390,21 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Feasibility studies 2</t>
+          <t>Farming Innovation Programme: Feasibility Round 4</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025-10-10 08:18</t>
+          <t>2025-09-29 08:20</t>
         </is>
       </c>
       <c r="E294" s="1" t="n">
-        <v>45940.34583333333</v>
+        <v>45929.34722222222</v>
       </c>
       <c r="F294" t="b">
         <v>1</v>
@@ -17279,19 +17417,19 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 3 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L294" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>45994.45833333334</v>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N294" s="1" t="n">
-        <v>45938</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="295">
@@ -17302,21 +17440,21 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – October 2025</t>
+          <t>Eureka GlobalStars Japan 2026</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2025-10-14 08:17</t>
+          <t>2025-10-03 08:17</t>
         </is>
       </c>
       <c r="E295" s="1" t="n">
-        <v>45944.34513888889</v>
+        <v>45933.34513888889</v>
       </c>
       <c r="F295" t="b">
         <v>1</v>
@@ -17329,15 +17467,19 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 21 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L295" s="1" t="n">
-        <v>45952.45833333334</v>
-      </c>
-      <c r="M295" t="inlineStr"/>
+        <v>46043.45833333334</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>£600,000</t>
+        </is>
+      </c>
       <c r="N295" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="296">
@@ -17348,21 +17490,21 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Enable</t>
+          <t>CAM Pathfinder: Feasibility studies 2</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-10 08:18</t>
         </is>
       </c>
       <c r="E296" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45940.34583333333</v>
       </c>
       <c r="F296" t="b">
         <v>1</v>
@@ -17375,19 +17517,19 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L296" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N296" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="297">
@@ -17398,21 +17540,21 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Demonstrate</t>
+          <t>ATI Programme strategic batch EoI – October 2025</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-14 08:17</t>
         </is>
       </c>
       <c r="E297" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45944.34513888889</v>
       </c>
       <c r="F297" t="b">
         <v>1</v>
@@ -17425,19 +17567,15 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L297" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>£2.0 million</t>
-        </is>
-      </c>
+        <v>45952.45833333334</v>
+      </c>
+      <c r="M297" t="inlineStr"/>
       <c r="N297" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="298">
@@ -17448,21 +17586,21 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
+          <t>CAM Pathfinder: Enable</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025-10-16 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E298" s="1" t="n">
-        <v>45946.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F298" t="b">
         <v>1</v>
@@ -17475,15 +17613,15 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L298" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N298" s="1" t="n">
@@ -17498,21 +17636,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 5</t>
+          <t>CAM Pathfinder: Demonstrate</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2025-10-17 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E299" s="1" t="n">
-        <v>45947.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F299" t="b">
         <v>1</v>
@@ -17525,15 +17663,15 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L299" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N299" s="1" t="n">
@@ -17548,21 +17686,21 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Battery Innovation Feasibility Studies Round 1</t>
+          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-16 08:19</t>
         </is>
       </c>
       <c r="E300" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45946.34652777778</v>
       </c>
       <c r="F300" t="b">
         <v>1</v>
@@ -17575,15 +17713,15 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L300" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N300" s="1" t="n">
@@ -17598,21 +17736,21 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Battery Innovation Concept Development Round 1</t>
+          <t>ADOPT Facilitator Support Grant: Round 5</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-17 08:19</t>
         </is>
       </c>
       <c r="E301" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45947.34652777778</v>
       </c>
       <c r="F301" t="b">
         <v>1</v>
@@ -17625,15 +17763,15 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L301" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N301" s="1" t="n">
@@ -17648,21 +17786,21 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>The Agentic AI Pioneers Prize</t>
+          <t>Battery Innovation Feasibility Studies Round 1</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2025-10-21 08:20</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E302" s="1" t="n">
-        <v>45951.34722222222</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F302" t="b">
         <v>1</v>
@@ -17675,13 +17813,17 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L302" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M302" t="inlineStr"/>
+        <v>46008.45833333334</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>£500,000</t>
+        </is>
+      </c>
       <c r="N302" s="1" t="n">
         <v>45945</v>
       </c>
@@ -17694,21 +17836,21 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy efficiency – industrial research</t>
+          <t>Battery Innovation Concept Development Round 1</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E303" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F303" t="b">
         <v>1</v>
@@ -17721,19 +17863,19 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L303" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N303" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="304">
@@ -17744,21 +17886,21 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
+          <t>The Agentic AI Pioneers Prize</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-21 08:20</t>
         </is>
       </c>
       <c r="E304" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45951.34722222222</v>
       </c>
       <c r="F304" t="b">
         <v>1</v>
@@ -17771,19 +17913,15 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L304" s="1" t="n">
-        <v>46001.45833333334</v>
-      </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>£150,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M304" t="inlineStr"/>
       <c r="N304" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="305">
@@ -17794,21 +17932,21 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 4</t>
+          <t>MSI: SME resource and energy efficiency – industrial research</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2025-10-23 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E305" s="1" t="n">
-        <v>45953.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F305" t="b">
         <v>1</v>
@@ -17829,7 +17967,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N305" s="1" t="n">
@@ -17844,21 +17982,21 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 24</t>
+          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2025-10-24 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E306" s="1" t="n">
-        <v>45954.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F306" t="b">
         <v>1</v>
@@ -17871,15 +18009,15 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Wednesday 7 January 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L306" s="1" t="n">
-        <v>46029.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N306" s="1" t="n">
@@ -17894,21 +18032,21 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
+          <t>Full ADOPT Grant Round 4</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2025-10-25 08:16</t>
+          <t>2025-10-23 08:19</t>
         </is>
       </c>
       <c r="E307" s="1" t="n">
-        <v>45955.34444444445</v>
+        <v>45953.34652777778</v>
       </c>
       <c r="F307" t="b">
         <v>1</v>
@@ -17921,15 +18059,15 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L307" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N307" s="1" t="n">
@@ -17944,21 +18082,21 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility Studies</t>
+          <t>Innovate UK Innovation Loans Round 24</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2025-10-31 08:18</t>
+          <t>2025-10-24 08:19</t>
         </is>
       </c>
       <c r="E308" s="1" t="n">
-        <v>45961.34583333333</v>
+        <v>45954.34652777778</v>
       </c>
       <c r="F308" t="b">
         <v>1</v>
@@ -17971,19 +18109,19 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 7 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L308" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>46029.45833333334</v>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N308" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="309">
@@ -17994,21 +18132,21 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-25 08:16</t>
         </is>
       </c>
       <c r="E309" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45955.34444444445</v>
       </c>
       <c r="F309" t="b">
         <v>1</v>
@@ -18029,11 +18167,11 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>£3.4 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N309" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="310">
@@ -18044,21 +18182,21 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Increasing EV charging capacity on the strategic road network</t>
+          <t>National Materials Innovation Programme: Feasibility Studies</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-31 08:18</t>
         </is>
       </c>
       <c r="E310" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45961.34583333333</v>
       </c>
       <c r="F310" t="b">
         <v>1</v>
@@ -18071,15 +18209,15 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L310" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N310" s="1" t="n">
@@ -18094,21 +18232,21 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
+          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E311" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F311" t="b">
         <v>1</v>
@@ -18121,19 +18259,19 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L311" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£3.4 million</t>
         </is>
       </c>
       <c r="N311" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="312">
@@ -18144,21 +18282,21 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
+          <t>Increasing EV charging capacity on the strategic road network</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E312" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F312" t="b">
         <v>1</v>
@@ -18171,19 +18309,19 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L312" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N312" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="313">
@@ -18194,12 +18332,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – November 2025</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -18221,13 +18359,17 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L313" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M313" t="inlineStr"/>
+        <v>46001.45833333334</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
       <c r="N313" s="1" t="n">
         <v>45966</v>
       </c>
@@ -18240,21 +18382,21 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2025-11-11 08:19</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E314" s="1" t="n">
-        <v>45972.34652777778</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F314" t="b">
         <v>1</v>
@@ -18267,15 +18409,15 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L314" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N314" s="1" t="n">
@@ -18290,21 +18432,21 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Women in Innovation Awards 2025/26</t>
+          <t>ATI Programme strategic batch EoI – November 2025</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2025-11-27 13:23</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E315" s="1" t="n">
-        <v>45988.55763888889</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F315" t="b">
         <v>1</v>
@@ -18317,19 +18459,15 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L315" s="1" t="n">
-        <v>46057.45833333334</v>
-      </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>£75,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M315" t="inlineStr"/>
       <c r="N315" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="316">
@@ -18340,21 +18478,21 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2025-12-02 08:22</t>
+          <t>2025-11-11 08:19</t>
         </is>
       </c>
       <c r="E316" s="1" t="n">
-        <v>45993.34861111111</v>
+        <v>45972.34652777778</v>
       </c>
       <c r="F316" t="b">
         <v>1</v>
@@ -18367,19 +18505,19 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L316" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N316" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="317">
@@ -18390,21 +18528,21 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
+          <t>Women in Innovation Awards 2025/26</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2025-12-11 08:22</t>
+          <t>2025-11-27 13:23</t>
         </is>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46002.34861111111</v>
+        <v>45988.55763888889</v>
       </c>
       <c r="F317" t="b">
         <v>1</v>
@@ -18417,19 +18555,19 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Tuesday 3 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L317" s="1" t="n">
-        <v>46056.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£75,000</t>
         </is>
       </c>
       <c r="N317" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="318">
@@ -18440,21 +18578,21 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 5</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2025-12-12 08:22</t>
+          <t>2025-12-02 08:22</t>
         </is>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46003.34861111111</v>
+        <v>45993.34861111111</v>
       </c>
       <c r="F318" t="b">
         <v>1</v>
@@ -18475,11 +18613,11 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N318" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="319">
@@ -18490,21 +18628,21 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 6</t>
+          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-11 08:22</t>
         </is>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46002.34861111111</v>
       </c>
       <c r="F319" t="b">
         <v>1</v>
@@ -18517,19 +18655,19 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Tuesday 3 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L319" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46056.45833333334</v>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N319" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="320">
@@ -18540,21 +18678,21 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
+          <t>Full ADOPT Grant: Round 5</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-12 08:22</t>
         </is>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46003.34861111111</v>
       </c>
       <c r="F320" t="b">
         <v>1</v>
@@ -18567,19 +18705,19 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Thursday 7 May 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L320" s="1" t="n">
-        <v>46149.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N320" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="321">
@@ -18590,21 +18728,21 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – mid stage</t>
+          <t>ADOPT Facilitator Support Grant: Round 6</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F321" t="b">
         <v>1</v>
@@ -18617,19 +18755,19 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L321" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N321" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="322">
@@ -18640,21 +18778,21 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – late stage</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F322" t="b">
         <v>1</v>
@@ -18667,19 +18805,19 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Thursday 7 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L322" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N322" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="323">
@@ -18690,12 +18828,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – early stage</t>
+          <t>Energy catalyst round 11 – mid stage</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -18725,7 +18863,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N323" s="1" t="n">
@@ -18740,12 +18878,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
+          <t>Energy catalyst round 11 – late stage</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -18767,15 +18905,15 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L324" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N324" s="1" t="n">
@@ -18790,12 +18928,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
+          <t>Energy catalyst round 11 – early stage</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -18817,15 +18955,15 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L325" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N325" s="1" t="n">
@@ -18840,21 +18978,21 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 25</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-01-08 08:22</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46030.34861111111</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F326" t="b">
         <v>1</v>
@@ -18867,19 +19005,19 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L326" s="1" t="n">
-        <v>46085.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N326" s="1" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="327">
@@ -18890,21 +19028,21 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-01-15 08:23</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46037.34930555556</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F327" t="b">
         <v>1</v>
@@ -18917,19 +19055,19 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Wednesday 11 February 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L327" s="1" t="n">
-        <v>46064.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N327" s="1" t="n">
-        <v>46036</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="328">
@@ -18940,21 +19078,21 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
+          <t>Innovate UK Innovation Loans Round 25</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-01-20 08:24</t>
+          <t>2026-01-08 08:22</t>
         </is>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46042.35</v>
+        <v>46030.34861111111</v>
       </c>
       <c r="F328" t="b">
         <v>1</v>
@@ -18967,19 +19105,19 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L328" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46085.45833333334</v>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N328" s="1" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="329">
@@ -18990,21 +19128,21 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation FS</t>
+          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-01-26 12:10</t>
+          <t>2026-01-15 08:23</t>
         </is>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46048.50694444445</v>
+        <v>46037.34930555556</v>
       </c>
       <c r="F329" t="b">
         <v>1</v>
@@ -19017,19 +19155,19 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 11 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L329" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46064.45833333334</v>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N329" s="1" t="n">
-        <v>46043</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="330">
@@ -19040,21 +19178,21 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-20 08:24</t>
         </is>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46042.35</v>
       </c>
       <c r="F330" t="b">
         <v>1</v>
@@ -19067,19 +19205,19 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L330" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>£225,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N330" s="1" t="n">
-        <v>46050</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="331">
@@ -19090,21 +19228,21 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
+          <t>Advanced manufacturing supply chain innovation FS</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-26 12:10</t>
         </is>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46048.50694444445</v>
       </c>
       <c r="F331" t="b">
         <v>1</v>
@@ -19117,19 +19255,19 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L331" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N331" s="1" t="n">
-        <v>46050</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="332">
@@ -19140,21 +19278,21 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Robotics Adoption Programme skills development</t>
+          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-02-02 10:39</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46055.44375</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F332" t="b">
         <v>1</v>
@@ -19167,15 +19305,15 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L332" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£225,000</t>
         </is>
       </c>
       <c r="N332" s="1" t="n">
@@ -19190,21 +19328,21 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
+          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F333" t="b">
         <v>1</v>
@@ -19217,15 +19355,15 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L333" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N333" s="1" t="n">
@@ -19240,21 +19378,21 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
+          <t>Robotics Adoption Programme skills development</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-02-02 10:39</t>
         </is>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46055.44375</v>
       </c>
       <c r="F334" t="b">
         <v>1</v>
@@ -19267,13 +19405,17 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L334" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M334" t="inlineStr"/>
+        <v>46106.45833333334</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>£500,000</t>
+        </is>
+      </c>
       <c r="N334" s="1" t="n">
         <v>46050</v>
       </c>
@@ -19286,12 +19428,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -19313,13 +19455,17 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L335" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M335" t="inlineStr"/>
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N335" s="1" t="n">
         <v>46050</v>
       </c>
@@ -19332,21 +19478,21 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 6</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-02-09 10:53</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46062.45347222222</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F336" t="b">
         <v>1</v>
@@ -19359,19 +19505,15 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L336" s="1" t="n">
-        <v>46120.45833333334</v>
-      </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>£100,000</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M336" t="inlineStr"/>
       <c r="N336" s="1" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="337">
@@ -19382,21 +19524,21 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Zero Emission Flight Demonstrator Round 1</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F337" t="b">
         <v>1</v>
@@ -19409,19 +19551,15 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L337" s="1" t="n">
-        <v>46113.45833333334</v>
-      </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>£5.0 million</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M337" t="inlineStr"/>
       <c r="N337" s="1" t="n">
-        <v>46064</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="338">
@@ -19432,21 +19570,21 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
+          <t>Full ADOPT Grant: Round 6</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-09 10:53</t>
         </is>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46062.45347222222</v>
       </c>
       <c r="F338" t="b">
         <v>1</v>
@@ -19459,19 +19597,19 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L338" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N338" s="1" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="339">
@@ -19482,12 +19620,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
+          <t>Zero Emission Flight Demonstrator Round 1</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -19509,15 +19647,15 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L339" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>£10.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N339" s="1" t="n">
@@ -19532,21 +19670,21 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
+          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46066.44097222222</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F340" t="b">
         <v>1</v>
@@ -19559,15 +19697,15 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L340" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N340" s="1" t="n">
@@ -19582,21 +19720,21 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-02-17 10:40</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46070.44444444445</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F341" t="b">
         <v>1</v>
@@ -19609,15 +19747,15 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L341" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N341" s="1" t="n">
@@ -19632,21 +19770,21 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-13 10:35</t>
         </is>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46066.44097222222</v>
       </c>
       <c r="F342" t="b">
         <v>1</v>
@@ -19659,19 +19797,19 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L342" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N342" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="343">
@@ -19682,21 +19820,21 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-17 10:40</t>
         </is>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46070.44444444445</v>
       </c>
       <c r="F343" t="b">
         <v>1</v>
@@ -19717,11 +19855,11 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>£7.5 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N343" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="344">
@@ -19732,21 +19870,21 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>Semiconductors and components for smart electronic platforms</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-20 10:32</t>
         </is>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46073.43888888889</v>
       </c>
       <c r="F344" t="b">
         <v>1</v>
@@ -19759,11 +19897,11 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L344" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M344" t="inlineStr">
         <is>
@@ -19782,21 +19920,21 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 7</t>
+          <t>Robotics Adoption Hubs</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-02-26 10:40</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46079.44444444445</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F345" t="b">
         <v>1</v>
@@ -19809,19 +19947,19 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L345" s="1" t="n">
-        <v>46120.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£7.5 million</t>
         </is>
       </c>
       <c r="N345" s="1" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="346">
@@ -19832,21 +19970,21 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
+          <t>Robotics Adoption Central Convening Body</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-03-03 10:34</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46084.44027777778</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F346" t="b">
         <v>1</v>
@@ -19859,19 +19997,19 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L346" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N346" s="1" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="347">
@@ -19882,21 +20020,21 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-02-26 10:40</t>
         </is>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46079.44444444445</v>
       </c>
       <c r="F347" t="b">
         <v>1</v>
@@ -19909,19 +20047,19 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L347" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N347" s="1" t="n">
-        <v>46092</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="348">
@@ -19932,21 +20070,21 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
+          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-03-03 10:34</t>
         </is>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46084.44027777778</v>
       </c>
       <c r="F348" t="b">
         <v>1</v>
@@ -19959,19 +20097,19 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L348" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N348" s="1" t="n">
-        <v>46092</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="349">
@@ -19982,12 +20120,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -20017,7 +20155,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>£15.0 million</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N349" s="1" t="n">
@@ -20032,21 +20170,21 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>AI Champions: Frontier AI Phase 1</t>
+          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-03-12 10:34</t>
+          <t>2026-03-11 10:34</t>
         </is>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46093.44027777778</v>
+        <v>46092.44027777778</v>
       </c>
       <c r="F350" t="b">
         <v>1</v>
@@ -20059,15 +20197,15 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Wednesday 29 April 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L350" s="1" t="n">
-        <v>46141.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N350" s="1" t="n">
@@ -20082,21 +20220,21 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Frontier AI Discovery</t>
+          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-03-17 10:45</t>
+          <t>2026-03-11 10:34</t>
         </is>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46098.44791666666</v>
+        <v>46092.44027777778</v>
       </c>
       <c r="F351" t="b">
         <v>1</v>
@@ -20109,15 +20247,15 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L351" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£15.0 million</t>
         </is>
       </c>
       <c r="N351" s="1" t="n">
@@ -20132,21 +20270,21 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Secure Software for Resilient Growth</t>
+          <t>AI Champions: Frontier AI Phase 1</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-03-17 10:45</t>
+          <t>2026-03-12 10:34</t>
         </is>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46098.44791666666</v>
+        <v>46093.44027777778</v>
       </c>
       <c r="F352" t="b">
         <v>1</v>
@@ -20167,7 +20305,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N352" s="1" t="n">
@@ -20182,12 +20320,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
+          <t>Frontier AI Discovery</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -20209,15 +20347,15 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Wednesday 22 April 2026 11:00am</t>
+          <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L353" s="1" t="n">
-        <v>46134.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N353" s="1" t="n">
@@ -20232,21 +20370,21 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Frontier AI Benchmarking Datasets</t>
+          <t>Secure Software for Resilient Growth</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2424/overview/e618b7a8-ab7f-45f3-a098-57c01b334fcd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-03-23 10:49</t>
+          <t>2026-03-17 10:45</t>
         </is>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46104.45069444444</v>
+        <v>46098.44791666666</v>
       </c>
       <c r="F354" t="b">
         <v>1</v>
@@ -20259,11 +20397,11 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
+          <t>Wednesday 29 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L354" s="1" t="n">
-        <v>46169.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="M354" t="inlineStr">
         <is>
@@ -20271,7 +20409,7 @@
         </is>
       </c>
       <c r="N354" s="1" t="n">
-        <v>46099</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="355">
@@ -20282,21 +20420,21 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Medicines Manufacturing: Labs of the Future</t>
+          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2417/overview/5ec76f19-8bd0-4dfa-b869-f4f0401448de</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-03-24 10:47</t>
+          <t>2026-03-17 10:45</t>
         </is>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46105.44930555556</v>
+        <v>46098.44791666666</v>
       </c>
       <c r="F355" t="b">
         <v>1</v>
@@ -20309,19 +20447,19 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
+          <t>Wednesday 22 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L355" s="1" t="n">
-        <v>46169.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N355" s="1" t="n">
-        <v>46099</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="356">
@@ -20332,21 +20470,21 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>AgriScale - Accelerating Agri-tech manufacturing: Industrial Research</t>
+          <t>Frontier AI Benchmarking Datasets</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2428/overview/85fd40be-646f-4b95-8a12-f881334d871d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2424/overview/e618b7a8-ab7f-45f3-a098-57c01b334fcd</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-03-24 10:47</t>
+          <t>2026-03-23 10:49</t>
         </is>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46105.44930555556</v>
+        <v>46104.45069444444</v>
       </c>
       <c r="F356" t="b">
         <v>1</v>
@@ -20359,11 +20497,11 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L356" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M356" t="inlineStr">
         <is>
@@ -20382,12 +20520,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>AgriScale - Accelerating Agri-tech manufacturing: Experimental Development</t>
+          <t>Medicines Manufacturing: Labs of the Future</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2427/overview/cb071e4d-3a72-4d77-9350-b2ae3d50a79f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2417/overview/5ec76f19-8bd0-4dfa-b869-f4f0401448de</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -20409,15 +20547,15 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L357" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N357" s="1" t="n">
@@ -20432,21 +20570,21 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
+          <t>AgriScale - Accelerating Agri-tech manufacturing: Industrial Research</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2428/overview/85fd40be-646f-4b95-8a12-f881334d871d</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-03-26 10:49</t>
+          <t>2026-03-24 10:47</t>
         </is>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46107.45069444444</v>
+        <v>46105.44930555556</v>
       </c>
       <c r="F358" t="b">
         <v>1</v>
@@ -20459,19 +20597,19 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L358" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>£60.0 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N358" s="1" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="359">
@@ -20482,21 +20620,21 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
+          <t>AgriScale - Accelerating Agri-tech manufacturing: Experimental Development</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2427/overview/cb071e4d-3a72-4d77-9350-b2ae3d50a79f</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-03-26 10:49</t>
+          <t>2026-03-24 10:47</t>
         </is>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46107.45069444444</v>
+        <v>46105.44930555556</v>
       </c>
       <c r="F359" t="b">
         <v>1</v>
@@ -20509,19 +20647,19 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L359" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>£60.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N359" s="1" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="360">
@@ -20532,12 +20670,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -20582,21 +20720,21 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms: applications with academic partners</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2441/overview/5ad05ad0-9f9a-47b7-8660-085608a668e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-03-27 10:43</t>
+          <t>2026-03-26 10:49</t>
         </is>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46108.44652777778</v>
+        <v>46107.45069444444</v>
       </c>
       <c r="F361" t="b">
         <v>1</v>
@@ -20609,15 +20747,15 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L361" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£60.0 million</t>
         </is>
       </c>
       <c r="N361" s="1" t="n">
@@ -20632,21 +20770,21 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: ProQure - Scaling UK Quantum Computing</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2439/overview/06423ffe-b763-4cac-b83b-f80208dfe2f2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-03-28 10:27</t>
+          <t>2026-03-26 10:49</t>
         </is>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46109.43541666667</v>
+        <v>46107.45069444444</v>
       </c>
       <c r="F362" t="b">
         <v>1</v>
@@ -20659,15 +20797,15 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Friday 29 May 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L362" s="1" t="n">
-        <v>46171.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>£14.0 million</t>
+          <t>£60.0 million</t>
         </is>
       </c>
       <c r="N362" s="1" t="n">
@@ -20682,21 +20820,21 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: industrial research</t>
+          <t>Semiconductors and components for smart electronic platforms: applications with academic partners</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2433/overview/4458acff-f0d2-4e2d-836c-c151ebd82a1d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2441/overview/5ad05ad0-9f9a-47b7-8660-085608a668e0</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-04-01 10:50</t>
+          <t>2026-03-27 10:43</t>
         </is>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46113.45138888889</v>
+        <v>46108.44652777778</v>
       </c>
       <c r="F363" t="b">
         <v>1</v>
@@ -20709,19 +20847,19 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L363" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N363" s="1" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="364">
@@ -20732,21 +20870,21 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: feasibility studies</t>
+          <t>Contracts for Innovation: ProQure - Scaling UK Quantum Computing</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2432/overview/49f165f4-40af-4d16-8986-ba241fd2741a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2439/overview/06423ffe-b763-4cac-b83b-f80208dfe2f2</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-04-01 10:50</t>
+          <t>2026-03-28 10:27</t>
         </is>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46113.45138888889</v>
+        <v>46109.43541666667</v>
       </c>
       <c r="F364" t="b">
         <v>1</v>
@@ -20759,19 +20897,19 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Friday 29 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L364" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£14.0 million</t>
         </is>
       </c>
       <c r="N364" s="1" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="365">
@@ -20782,12 +20920,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Solution Development for Advanced Connectivity Technologies</t>
+          <t>Future offshore wind technologies: industrial research</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2420/overview/00926b83-c904-4919-b7d0-2be6e12269a0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2433/overview/4458acff-f0d2-4e2d-836c-c151ebd82a1d</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -20809,15 +20947,15 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Wednesday 13 May 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L365" s="1" t="n">
-        <v>46155.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N365" s="1" t="n">
@@ -20832,12 +20970,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>CfI: Advanced Connectivity Technologies (ACT) – Call 1</t>
+          <t>Future offshore wind technologies: feasibility studies</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2437/overview/1123379f-9949-4cf0-acce-df748923a207</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2432/overview/49f165f4-40af-4d16-8986-ba241fd2741a</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -20867,7 +21005,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N366" s="1" t="n">
@@ -20882,21 +21020,21 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Enabling Commercial Quantum Networking</t>
+          <t>Solution Development for Advanced Connectivity Technologies</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2426/overview/4766704a-4888-49f8-b4f3-1e370e9ee0c5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2420/overview/00926b83-c904-4919-b7d0-2be6e12269a0</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-04-07 10:51</t>
+          <t>2026-04-01 10:50</t>
         </is>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46119.45208333333</v>
+        <v>46113.45138888889</v>
       </c>
       <c r="F367" t="b">
         <v>1</v>
@@ -20909,15 +21047,15 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Wednesday 20 May 2026 11:00am</t>
+          <t>Wednesday 13 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L367" s="1" t="n">
-        <v>46162.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N367" s="1" t="n">
@@ -20932,21 +21070,21 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 7</t>
+          <t>CfI: Advanced Connectivity Technologies (ACT) – Call 1</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2442/overview/b9c07f24-e02d-4495-8351-0ed24aa9668d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2437/overview/1123379f-9949-4cf0-acce-df748923a207</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-04-09 10:54</t>
+          <t>2026-04-01 10:50</t>
         </is>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46121.45416666667</v>
+        <v>46113.45138888889</v>
       </c>
       <c r="F368" t="b">
         <v>1</v>
@@ -20967,11 +21105,11 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N368" s="1" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="369">
@@ -20982,21 +21120,21 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Contracts for Innovation: Enabling Commercial Quantum Networking</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2426/overview/4766704a-4888-49f8-b4f3-1e370e9ee0c5</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-04-11 10:30</t>
+          <t>2026-04-07 10:51</t>
         </is>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46123.4375</v>
+        <v>46119.45208333333</v>
       </c>
       <c r="F369" t="b">
         <v>1</v>
@@ -21009,17 +21147,19 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Wednesday 1 July 2026 12:00pm</t>
-        </is>
-      </c>
-      <c r="L369" t="inlineStr"/>
+          <t>Wednesday 20 May 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L369" s="1" t="n">
+        <v>46162.45833333334</v>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N369" s="1" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="370">
@@ -21030,21 +21170,21 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Battery innovation feasibility studies round 2</t>
+          <t>Full ADOPT Grant: Round 7</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2444/overview/b355177a-c85f-4cd6-b5b5-c4836d09df3e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2442/overview/b9c07f24-e02d-4495-8351-0ed24aa9668d</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-04-14 10:58</t>
+          <t>2026-04-09 10:54</t>
         </is>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46126.45694444444</v>
+        <v>46121.45416666667</v>
       </c>
       <c r="F370" t="b">
         <v>1</v>
@@ -21057,15 +21197,15 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L370" s="1" t="n">
-        <v>46169.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N370" s="1" t="n">
@@ -21080,21 +21220,21 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Battery innovation concept development round 2</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2443/overview/adca814a-3966-4fbb-afbe-a2ccbd4c3bae</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-04-14 10:58</t>
+          <t>2026-04-11 10:30</t>
         </is>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46126.45694444444</v>
+        <v>46123.4375</v>
       </c>
       <c r="F371" t="b">
         <v>1</v>
@@ -21107,15 +21247,13 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L371" s="1" t="n">
-        <v>46169.45833333334</v>
-      </c>
+          <t>Wednesday 1 July 2026 12:00pm</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr"/>
       <c r="M371" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N371" s="1" t="n">
@@ -21130,21 +21268,21 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 8</t>
+          <t>Battery innovation feasibility studies round 2</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2440/overview/630d8177-1633-413b-8c56-ad3fdcc8af82</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2444/overview/b355177a-c85f-4cd6-b5b5-c4836d09df3e</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-04-15 10:55</t>
+          <t>2026-04-14 10:58</t>
         </is>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46127.45486111111</v>
+        <v>46126.45694444444</v>
       </c>
       <c r="F372" t="b">
         <v>1</v>
@@ -21165,11 +21303,11 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N372" s="1" t="n">
-        <v>46127</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="373">
@@ -21180,21 +21318,21 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Growth Cohorts: Next generation low carbon concrete cohort entry</t>
+          <t>Battery innovation concept development round 2</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2450/overview/261cbeea-5b87-4730-9fe9-4d04acc3725f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2443/overview/adca814a-3966-4fbb-afbe-a2ccbd4c3bae</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-04-18 10:35</t>
+          <t>2026-04-14 10:58</t>
         </is>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46130.44097222222</v>
+        <v>46126.45694444444</v>
       </c>
       <c r="F373" t="b">
         <v>1</v>
@@ -21207,19 +21345,19 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L373" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N373" s="1" t="n">
-        <v>46127</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="374">
@@ -21230,21 +21368,21 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 2</t>
+          <t>ADOPT Facilitator Support Grant: Round 8</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2398/overview/318a8834-930f-4577-9069-26459a0def93</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2440/overview/630d8177-1633-413b-8c56-ad3fdcc8af82</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-04-20 11:16</t>
+          <t>2026-04-15 10:55</t>
         </is>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46132.46944444445</v>
+        <v>46127.45486111111</v>
       </c>
       <c r="F374" t="b">
         <v>1</v>
@@ -21257,15 +21395,15 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L374" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N374" s="1" t="n">
@@ -21280,21 +21418,21 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation: CRD</t>
+          <t>Growth Cohorts: Next generation low carbon concrete cohort entry</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2453/overview/79b9483b-140e-44e9-86af-db7792c594d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2450/overview/261cbeea-5b87-4730-9fe9-4d04acc3725f</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-04-21 11:02</t>
+          <t>2026-04-18 10:35</t>
         </is>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46133.45972222222</v>
+        <v>46130.44097222222</v>
       </c>
       <c r="F375" t="b">
         <v>1</v>
@@ -21307,15 +21445,15 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L375" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N375" s="1" t="n">
@@ -21330,21 +21468,21 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 2</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2457/overview/343a1d9f-29cb-4184-96bc-565bcfd09462</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2398/overview/318a8834-930f-4577-9069-26459a0def93</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-04-22 11:00</t>
+          <t>2026-04-20 11:16</t>
         </is>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46134.45833333334</v>
+        <v>46132.46944444445</v>
       </c>
       <c r="F376" t="b">
         <v>1</v>
@@ -21357,13 +21495,19 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L376" t="inlineStr"/>
-      <c r="M376" t="inlineStr"/>
+          <t>Wednesday 24 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L376" s="1" t="n">
+        <v>46197.45833333334</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N376" s="1" t="n">
-        <v>46134</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="377">
@@ -21374,21 +21518,21 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
+          <t>Advanced manufacturing supply chain innovation: CRD</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2452/overview/df0addbf-9146-4b7f-b8b5-e78470917675</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2453/overview/79b9483b-140e-44e9-86af-db7792c594d2</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-04-23 11:03</t>
+          <t>2026-04-21 11:02</t>
         </is>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46135.46041666667</v>
+        <v>46133.45972222222</v>
       </c>
       <c r="F377" t="b">
         <v>1</v>
@@ -21409,11 +21553,11 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N377" s="1" t="n">
-        <v>46134</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="378">
@@ -21424,21 +21568,21 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Dual-use aviation systems and autonomy</t>
+          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2467/overview/3ac02a1d-68e5-460b-bddb-0ecacdabfb00</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2457/overview/343a1d9f-29cb-4184-96bc-565bcfd09462</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-04-28 11:42</t>
+          <t>2026-04-22 11:00</t>
         </is>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46140.4875</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="F378" t="b">
         <v>1</v>
@@ -21451,17 +21595,11 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L378" s="1" t="n">
-        <v>46176.45833333334</v>
-      </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>£1.2 million</t>
-        </is>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
       <c r="N378" s="1" t="n">
         <v>46134</v>
       </c>
@@ -21474,21 +21612,21 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Counter UAS Technologies</t>
+          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2468/overview/6be7375d-717c-49b4-9411-f7709bb9e6ea</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2452/overview/df0addbf-9146-4b7f-b8b5-e78470917675</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-04-28 11:42</t>
+          <t>2026-04-23 11:03</t>
         </is>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46140.4875</v>
+        <v>46135.46041666667</v>
       </c>
       <c r="F379" t="b">
         <v>1</v>
@@ -21501,18 +21639,118 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
+          <t>Wednesday 10 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L379" s="1" t="n">
+        <v>46183.45833333334</v>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>£300,000</t>
+        </is>
+      </c>
+      <c r="N379" s="1" t="n">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Dual-use aviation systems and autonomy</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2467/overview/3ac02a1d-68e5-460b-bddb-0ecacdabfb00</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:42</t>
+        </is>
+      </c>
+      <c r="E380" s="1" t="n">
+        <v>46140.4875</v>
+      </c>
+      <c r="F380" t="b">
+        <v>1</v>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="b">
+        <v>0</v>
+      </c>
+      <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
           <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
-      <c r="L379" s="1" t="n">
+      <c r="L380" s="1" t="n">
         <v>46176.45833333334</v>
       </c>
-      <c r="M379" t="inlineStr">
+      <c r="M380" t="inlineStr">
         <is>
           <t>£1.2 million</t>
         </is>
       </c>
-      <c r="N379" s="1" t="n">
+      <c r="N380" s="1" t="n">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Counter UAS Technologies</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2468/overview/6be7375d-717c-49b4-9411-f7709bb9e6ea</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:42</t>
+        </is>
+      </c>
+      <c r="E381" s="1" t="n">
+        <v>46140.4875</v>
+      </c>
+      <c r="F381" t="b">
+        <v>1</v>
+      </c>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="b">
+        <v>0</v>
+      </c>
+      <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Wednesday 3 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L381" s="1" t="n">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>£1.2 million</t>
+        </is>
+      </c>
+      <c r="N381" s="1" t="n">
         <v>46134</v>
       </c>
     </row>
@@ -21554,10 +21792,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C2" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3">
@@ -21580,10 +21818,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C4" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -943,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,6 +1016,62 @@
         <is>
           <t>Week commencing (Wed)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Contracts for Innovation: Boosting fathers’ engagement to improve child outcomes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/cfi-boosting-fathers-engagement-to-improve-child-outcomes/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:42</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46148.4875</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>10/06/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>46183.45833333334</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>46148</v>
       </c>
     </row>
   </sheetData>
@@ -1029,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,343 +1112,343 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46141</v>
+        <v>46148</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="B7" t="n">
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46099</v>
+        <v>46106</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46071</v>
+        <v>46078</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
         <v>9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46029</v>
+        <v>46036</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46008</v>
+        <v>46015</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45994</v>
+        <v>46001</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45980</v>
+        <v>45987</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45973</v>
+        <v>45980</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1406,91 +1462,91 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45966</v>
+        <v>45973</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45959</v>
+        <v>45966</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45952</v>
+        <v>45959</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45945</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45938</v>
+        <v>45945</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45931</v>
+        <v>45938</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45924</v>
+        <v>45931</v>
       </c>
       <c r="B33" t="n">
         <v>1</v>
@@ -1504,35 +1560,35 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45910</v>
+        <v>45917</v>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45903</v>
+        <v>45910</v>
       </c>
       <c r="B36" t="n">
         <v>2</v>
@@ -1546,169 +1602,183 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45896</v>
+        <v>45903</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45889</v>
+        <v>45896</v>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45882</v>
+        <v>45889</v>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45875</v>
+        <v>45882</v>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45868</v>
+        <v>45875</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45861</v>
+        <v>45868</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45854</v>
+        <v>45861</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45847</v>
+        <v>45854</v>
       </c>
       <c r="B44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45840</v>
+        <v>45847</v>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45833</v>
+        <v>45840</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45826</v>
+        <v>45833</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
         <v>45819</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B49" t="n">
         <v>25</v>
       </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1723,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N387"/>
+  <dimension ref="A1:N388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14385,26 +14455,26 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
+          <t>Contracts for Innovation: Boosting fathers’ engagement to improve child outcomes</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/cfi-boosting-fathers-engagement-to-improve-child-outcomes/</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-05-06 11:42</t>
         </is>
       </c>
       <c r="E244" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46148.4875</v>
       </c>
       <c r="F244" t="b">
         <v>1</v>
@@ -14413,23 +14483,29 @@
       <c r="H244" t="b">
         <v>0</v>
       </c>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J244" s="1" t="n">
+        <v>46147</v>
+      </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>10/06/2026                              11:00</t>
         </is>
       </c>
       <c r="L244" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N244" s="1" t="n">
-        <v>45819</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="245">
@@ -14440,12 +14516,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 2</t>
+          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -14467,15 +14543,15 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Thursday 24 July 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L245" s="1" t="n">
-        <v>45862.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N245" s="1" t="n">
@@ -14490,12 +14566,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
+          <t>ADOPT Facilitator Support Grant: Round 2</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -14517,15 +14593,15 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 24 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L246" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45862.45833333334</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N246" s="1" t="n">
@@ -14540,12 +14616,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>New Innovators in Marine and Maritime, Great South West</t>
+          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -14575,7 +14651,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N247" s="1" t="n">
@@ -14590,12 +14666,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>New Innovators in Marine and Maritime, Great South West</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -14617,15 +14693,15 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Thursday 4 September 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L248" s="1" t="n">
-        <v>45904.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N248" s="1" t="n">
@@ -14640,12 +14716,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – June 2025</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -14667,13 +14743,17 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Thursday 4 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L249" s="1" t="n">
-        <v>45826.45833333334</v>
-      </c>
-      <c r="M249" t="inlineStr"/>
+        <v>45904.45833333334</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N249" s="1" t="n">
         <v>45819</v>
       </c>
@@ -14686,12 +14766,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>ATI Programme strategic batch: EoI – June 2025</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -14713,17 +14793,13 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L250" s="1" t="n">
-        <v>45840.45833333334</v>
-      </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45826.45833333334</v>
+      </c>
+      <c r="M250" t="inlineStr"/>
       <c r="N250" s="1" t="n">
         <v>45819</v>
       </c>
@@ -14736,12 +14812,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -14763,15 +14839,15 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L251" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N251" s="1" t="n">
@@ -14786,12 +14862,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -14836,12 +14912,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
+          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -14863,15 +14939,15 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L253" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N253" s="1" t="n">
@@ -14886,12 +14962,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
+          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -14913,15 +14989,15 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L254" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N254" s="1" t="n">
@@ -14936,12 +15012,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
+          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -14963,15 +15039,15 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L255" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N255" s="1" t="n">
@@ -14986,12 +15062,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Clean Air, Phase 3</t>
+          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -15036,12 +15112,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
+          <t>Contracts for Innovation: Clean Air, Phase 3</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -15063,15 +15139,15 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L257" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N257" s="1" t="n">
@@ -15086,12 +15162,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -15121,7 +15197,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N258" s="1" t="n">
@@ -15136,12 +15212,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Canada-UK Semiconductors</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -15163,15 +15239,15 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L259" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N259" s="1" t="n">
@@ -15186,12 +15262,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
+          <t>Canada-UK Semiconductors</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -15213,15 +15289,15 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L260" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N260" s="1" t="n">
@@ -15236,12 +15312,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Innovate UK innovation loans future economy: Round 21</t>
+          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -15271,7 +15347,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N261" s="1" t="n">
@@ -15286,12 +15362,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
+          <t>Innovate UK innovation loans future economy: Round 21</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -15313,15 +15389,15 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L262" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N262" s="1" t="n">
@@ -15336,12 +15412,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
+          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -15386,12 +15462,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
+          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -15413,15 +15489,15 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L264" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N264" s="1" t="n">
@@ -15436,12 +15512,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 1</t>
+          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -15463,15 +15539,15 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L265" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N265" s="1" t="n">
@@ -15486,12 +15562,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
+          <t>Full ADOPT Grant: Round 1</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -15513,11 +15589,17 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L266" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N266" s="1" t="n">
         <v>45819</v>
       </c>
@@ -15530,12 +15612,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee Extension</t>
+          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -15574,21 +15656,21 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
+          <t>Horizon Europe Guarantee Extension</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025-06-16 22:04</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E268" s="1" t="n">
-        <v>45824.91944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F268" t="b">
         <v>1</v>
@@ -15601,17 +15683,11 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L268" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>£8,500</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
       <c r="N268" s="1" t="n">
         <v>45819</v>
       </c>
@@ -15624,21 +15700,21 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-16 22:04</t>
         </is>
       </c>
       <c r="E269" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45824.91944444444</v>
       </c>
       <c r="F269" t="b">
         <v>1</v>
@@ -15651,19 +15727,19 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L269" s="1" t="n">
-        <v>45889.45833333334</v>
+        <v>45917.45833333334</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N269" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="270">
@@ -15674,12 +15750,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 2</t>
+          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -15709,7 +15785,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N270" s="1" t="n">
@@ -15724,21 +15800,21 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 22</t>
+          <t>Full ADOPT Grant Round 2</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025-07-03 08:52</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E271" s="1" t="n">
-        <v>45841.36944444444</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F271" t="b">
         <v>1</v>
@@ -15751,19 +15827,19 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L271" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N271" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="272">
@@ -15774,21 +15850,21 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Growth Catalyst Early Stage: New Innovators</t>
+          <t>Innovate UK Innovation Loans Round 22</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-07-03 08:52</t>
         </is>
       </c>
       <c r="E272" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45841.36944444444</v>
       </c>
       <c r="F272" t="b">
         <v>1</v>
@@ -15801,15 +15877,15 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Wednesday 6 August 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L272" s="1" t="n">
-        <v>45875.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N272" s="1" t="n">
@@ -15824,12 +15900,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – July 2025</t>
+          <t>Growth Catalyst Early Stage: New Innovators</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -15851,13 +15927,17 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Wednesday 23 July 2025 11:00am</t>
+          <t>Wednesday 6 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L273" s="1" t="n">
-        <v>45861.45833333334</v>
-      </c>
-      <c r="M273" t="inlineStr"/>
+        <v>45875.45833333334</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>£50,000</t>
+        </is>
+      </c>
       <c r="N273" s="1" t="n">
         <v>45840</v>
       </c>
@@ -15870,21 +15950,21 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
+          <t>ATI Programme strategic batch: EoI – July 2025</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E274" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F274" t="b">
         <v>1</v>
@@ -15897,19 +15977,15 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 23 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L274" s="1" t="n">
-        <v>45896.45833333334</v>
-      </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+        <v>45861.45833333334</v>
+      </c>
+      <c r="M274" t="inlineStr"/>
       <c r="N274" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="275">
@@ -15920,12 +15996,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -15970,12 +16046,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -16020,12 +16096,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Future Flight: Regional Demonstrator 2</t>
+          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -16047,15 +16123,15 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Thursday 17 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L277" s="1" t="n">
-        <v>45855.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N277" s="1" t="n">
@@ -16070,21 +16146,21 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies</t>
+          <t>Future Flight: Regional Demonstrator 2</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E278" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F278" t="b">
         <v>1</v>
@@ -16097,15 +16173,15 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Thursday 17 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L278" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45855.45833333334</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N278" s="1" t="n">
@@ -16120,12 +16196,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -16147,15 +16223,15 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L279" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N279" s="1" t="n">
@@ -16170,12 +16246,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -16205,7 +16281,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N280" s="1" t="n">
@@ -16220,21 +16296,21 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 3</t>
+          <t>DRIVE35 Innovation Fund: Collaborate</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025-07-25 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E281" s="1" t="n">
-        <v>45863.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F281" t="b">
         <v>1</v>
@@ -16247,19 +16323,19 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L281" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N281" s="1" t="n">
-        <v>45861</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="282">
@@ -16270,21 +16346,21 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Sovereign AI - Proof of concept</t>
+          <t>ADOPT Facilitator Support Grant: Round 3</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2025-08-07 08:21</t>
+          <t>2025-07-25 08:20</t>
         </is>
       </c>
       <c r="E282" s="1" t="n">
-        <v>45876.34791666667</v>
+        <v>45863.34722222222</v>
       </c>
       <c r="F282" t="b">
         <v>1</v>
@@ -16297,19 +16373,19 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L282" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>£120,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N282" s="1" t="n">
-        <v>45875</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="283">
@@ -16320,21 +16396,21 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
+          <t>Sovereign AI - Proof of concept</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-08-07 08:21</t>
         </is>
       </c>
       <c r="E283" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45876.34791666667</v>
       </c>
       <c r="F283" t="b">
         <v>1</v>
@@ -16347,19 +16423,19 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L283" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£120,000</t>
         </is>
       </c>
       <c r="N283" s="1" t="n">
-        <v>45882</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="284">
@@ -16370,12 +16446,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -16405,7 +16481,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>£4.5 million</t>
+          <t>£8.0 million</t>
         </is>
       </c>
       <c r="N284" s="1" t="n">
@@ -16420,12 +16496,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -16455,7 +16531,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£4.5 million</t>
         </is>
       </c>
       <c r="N285" s="1" t="n">
@@ -16470,21 +16546,21 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2025-08-26 08:20</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E286" s="1" t="n">
-        <v>45895.34722222222</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F286" t="b">
         <v>1</v>
@@ -16497,19 +16573,19 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L286" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N286" s="1" t="n">
-        <v>45889</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="287">
@@ -16520,21 +16596,21 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 3</t>
+          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025-08-27 08:18</t>
+          <t>2025-08-26 08:20</t>
         </is>
       </c>
       <c r="E287" s="1" t="n">
-        <v>45896.34583333333</v>
+        <v>45895.34722222222</v>
       </c>
       <c r="F287" t="b">
         <v>1</v>
@@ -16547,11 +16623,11 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L287" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
@@ -16559,7 +16635,7 @@
         </is>
       </c>
       <c r="N287" s="1" t="n">
-        <v>45896</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="288">
@@ -16570,21 +16646,21 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – September 2025</t>
+          <t>Full ADOPT Grant Round 3</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025-09-01 08:20</t>
+          <t>2025-08-27 08:18</t>
         </is>
       </c>
       <c r="E288" s="1" t="n">
-        <v>45901.34722222222</v>
+        <v>45896.34583333333</v>
       </c>
       <c r="F288" t="b">
         <v>1</v>
@@ -16597,13 +16673,17 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L288" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M288" t="inlineStr"/>
+        <v>45945.45833333334</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N288" s="1" t="n">
         <v>45896</v>
       </c>
@@ -16616,21 +16696,21 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
+          <t>ATI Programme strategic batch: EoI – September 2025</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025-09-02 08:19</t>
+          <t>2025-09-01 08:20</t>
         </is>
       </c>
       <c r="E289" s="1" t="n">
-        <v>45902.34652777778</v>
+        <v>45901.34722222222</v>
       </c>
       <c r="F289" t="b">
         <v>1</v>
@@ -16643,17 +16723,13 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L289" s="1" t="n">
-        <v>45966.45833333334</v>
-      </c>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45917.45833333334</v>
+      </c>
+      <c r="M289" t="inlineStr"/>
       <c r="N289" s="1" t="n">
         <v>45896</v>
       </c>
@@ -16666,21 +16742,21 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 4</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025-09-04 08:18</t>
+          <t>2025-09-02 08:19</t>
         </is>
       </c>
       <c r="E290" s="1" t="n">
-        <v>45904.34583333333</v>
+        <v>45902.34652777778</v>
       </c>
       <c r="F290" t="b">
         <v>1</v>
@@ -16693,19 +16769,19 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L290" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N290" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="291">
@@ -16716,21 +16792,21 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 23</t>
+          <t>ADOPT Facilitator Support Grant: Round 4</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025-09-05 08:18</t>
+          <t>2025-09-04 08:18</t>
         </is>
       </c>
       <c r="E291" s="1" t="n">
-        <v>45905.34583333333</v>
+        <v>45904.34583333333</v>
       </c>
       <c r="F291" t="b">
         <v>1</v>
@@ -16743,15 +16819,15 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L291" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N291" s="1" t="n">
@@ -16766,21 +16842,21 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
+          <t>Innovate UK Innovation Loans Round 23</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025-09-12 08:17</t>
+          <t>2025-09-05 08:18</t>
         </is>
       </c>
       <c r="E292" s="1" t="n">
-        <v>45912.34513888889</v>
+        <v>45905.34583333333</v>
       </c>
       <c r="F292" t="b">
         <v>1</v>
@@ -16793,19 +16869,19 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Tuesday 28 October 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L292" s="1" t="n">
-        <v>45958.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N292" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="293">
@@ -16816,21 +16892,21 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
+          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025-09-16 08:19</t>
+          <t>2025-09-12 08:17</t>
         </is>
       </c>
       <c r="E293" s="1" t="n">
-        <v>45916.34652777778</v>
+        <v>45912.34513888889</v>
       </c>
       <c r="F293" t="b">
         <v>1</v>
@@ -16843,15 +16919,15 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Tuesday 28 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L293" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45958.45833333334</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N293" s="1" t="n">
@@ -16866,21 +16942,21 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025-09-17 08:18</t>
+          <t>2025-09-16 08:19</t>
         </is>
       </c>
       <c r="E294" s="1" t="n">
-        <v>45917.34583333333</v>
+        <v>45916.34652777778</v>
       </c>
       <c r="F294" t="b">
         <v>1</v>
@@ -16893,17 +16969,19 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L294" t="inlineStr"/>
+          <t>Wednesday 15 October 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L294" s="1" t="n">
+        <v>45945.45833333334</v>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="N294" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="295">
@@ -16914,21 +16992,21 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2025-09-18 08:17</t>
+          <t>2025-09-17 08:18</t>
         </is>
       </c>
       <c r="E295" s="1" t="n">
-        <v>45918.34513888889</v>
+        <v>45917.34583333333</v>
       </c>
       <c r="F295" t="b">
         <v>1</v>
@@ -16941,15 +17019,13 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Thursday 4 December 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L295" s="1" t="n">
-        <v>45995.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N295" s="1" t="n">
@@ -16964,21 +17040,21 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Resource efficiency for resilience and sustainability FS</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025-09-20 08:16</t>
+          <t>2025-09-18 08:17</t>
         </is>
       </c>
       <c r="E296" s="1" t="n">
-        <v>45920.34444444445</v>
+        <v>45918.34513888889</v>
       </c>
       <c r="F296" t="b">
         <v>1</v>
@@ -16991,15 +17067,15 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Monday 3 November 2025 11:00am</t>
+          <t>Thursday 4 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L296" s="1" t="n">
-        <v>45964.45833333334</v>
+        <v>45995.45833333334</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N296" s="1" t="n">
@@ -17014,21 +17090,21 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
+          <t>Resource efficiency for resilience and sustainability FS</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025-09-23 08:18</t>
+          <t>2025-09-20 08:16</t>
         </is>
       </c>
       <c r="E297" s="1" t="n">
-        <v>45923.34583333333</v>
+        <v>45920.34444444445</v>
       </c>
       <c r="F297" t="b">
         <v>1</v>
@@ -17041,15 +17117,15 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Monday 3 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L297" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45964.45833333334</v>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N297" s="1" t="n">
@@ -17064,21 +17140,21 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 4</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025-09-29 08:20</t>
+          <t>2025-09-23 08:18</t>
         </is>
       </c>
       <c r="E298" s="1" t="n">
-        <v>45929.34722222222</v>
+        <v>45923.34583333333</v>
       </c>
       <c r="F298" t="b">
         <v>1</v>
@@ -17091,19 +17167,19 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Wednesday 3 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L298" s="1" t="n">
-        <v>45994.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N298" s="1" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="299">
@@ -17114,21 +17190,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Eureka GlobalStars Japan 2026</t>
+          <t>Farming Innovation Programme: Feasibility Round 4</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2025-10-03 08:17</t>
+          <t>2025-09-29 08:20</t>
         </is>
       </c>
       <c r="E299" s="1" t="n">
-        <v>45933.34513888889</v>
+        <v>45929.34722222222</v>
       </c>
       <c r="F299" t="b">
         <v>1</v>
@@ -17141,19 +17217,19 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Wednesday 21 January 2026 11:00am</t>
+          <t>Wednesday 3 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L299" s="1" t="n">
-        <v>46043.45833333334</v>
+        <v>45994.45833333334</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N299" s="1" t="n">
-        <v>45931</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="300">
@@ -17164,21 +17240,21 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Feasibility studies 2</t>
+          <t>Eureka GlobalStars Japan 2026</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2025-10-10 08:18</t>
+          <t>2025-10-03 08:17</t>
         </is>
       </c>
       <c r="E300" s="1" t="n">
-        <v>45940.34583333333</v>
+        <v>45933.34513888889</v>
       </c>
       <c r="F300" t="b">
         <v>1</v>
@@ -17191,19 +17267,19 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 21 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L300" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46043.45833333334</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£600,000</t>
         </is>
       </c>
       <c r="N300" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="301">
@@ -17214,21 +17290,21 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – October 2025</t>
+          <t>CAM Pathfinder: Feasibility studies 2</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025-10-14 08:17</t>
+          <t>2025-10-10 08:18</t>
         </is>
       </c>
       <c r="E301" s="1" t="n">
-        <v>45944.34513888889</v>
+        <v>45940.34583333333</v>
       </c>
       <c r="F301" t="b">
         <v>1</v>
@@ -17241,13 +17317,17 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L301" s="1" t="n">
-        <v>45952.45833333334</v>
-      </c>
-      <c r="M301" t="inlineStr"/>
+        <v>45987.45833333334</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N301" s="1" t="n">
         <v>45938</v>
       </c>
@@ -17260,21 +17340,21 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Enable</t>
+          <t>ATI Programme strategic batch EoI – October 2025</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-14 08:17</t>
         </is>
       </c>
       <c r="E302" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45944.34513888889</v>
       </c>
       <c r="F302" t="b">
         <v>1</v>
@@ -17287,19 +17367,15 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L302" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>£4.0 million</t>
-        </is>
-      </c>
+        <v>45952.45833333334</v>
+      </c>
+      <c r="M302" t="inlineStr"/>
       <c r="N302" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="303">
@@ -17310,12 +17386,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Demonstrate</t>
+          <t>CAM Pathfinder: Enable</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -17345,7 +17421,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N303" s="1" t="n">
@@ -17360,21 +17436,21 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
+          <t>CAM Pathfinder: Demonstrate</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2025-10-16 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E304" s="1" t="n">
-        <v>45946.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F304" t="b">
         <v>1</v>
@@ -17387,15 +17463,15 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L304" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N304" s="1" t="n">
@@ -17410,21 +17486,21 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 5</t>
+          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2025-10-17 08:19</t>
+          <t>2025-10-16 08:19</t>
         </is>
       </c>
       <c r="E305" s="1" t="n">
-        <v>45947.34652777778</v>
+        <v>45946.34652777778</v>
       </c>
       <c r="F305" t="b">
         <v>1</v>
@@ -17445,7 +17521,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N305" s="1" t="n">
@@ -17460,21 +17536,21 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Battery Innovation Feasibility Studies Round 1</t>
+          <t>ADOPT Facilitator Support Grant: Round 5</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-17 08:19</t>
         </is>
       </c>
       <c r="E306" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45947.34652777778</v>
       </c>
       <c r="F306" t="b">
         <v>1</v>
@@ -17487,15 +17563,15 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L306" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N306" s="1" t="n">
@@ -17510,12 +17586,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Battery Innovation Concept Development Round 1</t>
+          <t>Battery Innovation Feasibility Studies Round 1</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -17545,7 +17621,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N307" s="1" t="n">
@@ -17560,21 +17636,21 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>The Agentic AI Pioneers Prize</t>
+          <t>Battery Innovation Concept Development Round 1</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2025-10-21 08:20</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E308" s="1" t="n">
-        <v>45951.34722222222</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F308" t="b">
         <v>1</v>
@@ -17587,13 +17663,17 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L308" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M308" t="inlineStr"/>
+        <v>46008.45833333334</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N308" s="1" t="n">
         <v>45945</v>
       </c>
@@ -17606,21 +17686,21 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy efficiency – industrial research</t>
+          <t>The Agentic AI Pioneers Prize</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-21 08:20</t>
         </is>
       </c>
       <c r="E309" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45951.34722222222</v>
       </c>
       <c r="F309" t="b">
         <v>1</v>
@@ -17633,19 +17713,15 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L309" s="1" t="n">
-        <v>46001.45833333334</v>
-      </c>
-      <c r="M309" t="inlineStr">
-        <is>
-          <t>£1.0 million</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M309" t="inlineStr"/>
       <c r="N309" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="310">
@@ -17656,12 +17732,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
+          <t>MSI: SME resource and energy efficiency – industrial research</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -17691,7 +17767,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N310" s="1" t="n">
@@ -17706,21 +17782,21 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 4</t>
+          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2025-10-23 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E311" s="1" t="n">
-        <v>45953.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F311" t="b">
         <v>1</v>
@@ -17741,7 +17817,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N311" s="1" t="n">
@@ -17756,21 +17832,21 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 24</t>
+          <t>Full ADOPT Grant Round 4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2025-10-24 08:19</t>
+          <t>2025-10-23 08:19</t>
         </is>
       </c>
       <c r="E312" s="1" t="n">
-        <v>45954.34652777778</v>
+        <v>45953.34652777778</v>
       </c>
       <c r="F312" t="b">
         <v>1</v>
@@ -17783,15 +17859,15 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Wednesday 7 January 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L312" s="1" t="n">
-        <v>46029.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N312" s="1" t="n">
@@ -17806,21 +17882,21 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
+          <t>Innovate UK Innovation Loans Round 24</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2025-10-25 08:16</t>
+          <t>2025-10-24 08:19</t>
         </is>
       </c>
       <c r="E313" s="1" t="n">
-        <v>45955.34444444445</v>
+        <v>45954.34652777778</v>
       </c>
       <c r="F313" t="b">
         <v>1</v>
@@ -17833,15 +17909,15 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 7 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L313" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46029.45833333334</v>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N313" s="1" t="n">
@@ -17856,21 +17932,21 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility Studies</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2025-10-31 08:18</t>
+          <t>2025-10-25 08:16</t>
         </is>
       </c>
       <c r="E314" s="1" t="n">
-        <v>45961.34583333333</v>
+        <v>45955.34444444445</v>
       </c>
       <c r="F314" t="b">
         <v>1</v>
@@ -17883,19 +17959,19 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L314" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N314" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="315">
@@ -17906,21 +17982,21 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
+          <t>National Materials Innovation Programme: Feasibility Studies</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-31 08:18</t>
         </is>
       </c>
       <c r="E315" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45961.34583333333</v>
       </c>
       <c r="F315" t="b">
         <v>1</v>
@@ -17933,15 +18009,15 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L315" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>£3.4 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N315" s="1" t="n">
@@ -17956,12 +18032,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Increasing EV charging capacity on the strategic road network</t>
+          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -17983,15 +18059,15 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L316" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£3.4 million</t>
         </is>
       </c>
       <c r="N316" s="1" t="n">
@@ -18006,21 +18082,21 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
+          <t>Increasing EV charging capacity on the strategic road network</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E317" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F317" t="b">
         <v>1</v>
@@ -18033,19 +18109,19 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L317" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N317" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="318">
@@ -18056,12 +18132,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -18091,7 +18167,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N318" s="1" t="n">
@@ -18106,12 +18182,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – November 2025</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -18133,13 +18209,17 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L319" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M319" t="inlineStr"/>
+        <v>46001.45833333334</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N319" s="1" t="n">
         <v>45966</v>
       </c>
@@ -18152,21 +18232,21 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
+          <t>ATI Programme strategic batch EoI – November 2025</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2025-11-11 08:19</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E320" s="1" t="n">
-        <v>45972.34652777778</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F320" t="b">
         <v>1</v>
@@ -18179,17 +18259,13 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L320" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M320" t="inlineStr">
-        <is>
-          <t>£750,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M320" t="inlineStr"/>
       <c r="N320" s="1" t="n">
         <v>45966</v>
       </c>
@@ -18202,21 +18278,21 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Women in Innovation Awards 2025/26</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2025-11-27 13:23</t>
+          <t>2025-11-11 08:19</t>
         </is>
       </c>
       <c r="E321" s="1" t="n">
-        <v>45988.55763888889</v>
+        <v>45972.34652777778</v>
       </c>
       <c r="F321" t="b">
         <v>1</v>
@@ -18229,19 +18305,19 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L321" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>£75,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N321" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="322">
@@ -18252,21 +18328,21 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
+          <t>Women in Innovation Awards 2025/26</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2025-12-02 08:22</t>
+          <t>2025-11-27 13:23</t>
         </is>
       </c>
       <c r="E322" s="1" t="n">
-        <v>45993.34861111111</v>
+        <v>45988.55763888889</v>
       </c>
       <c r="F322" t="b">
         <v>1</v>
@@ -18287,7 +18363,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£75,000</t>
         </is>
       </c>
       <c r="N322" s="1" t="n">
@@ -18302,21 +18378,21 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2025-12-11 08:22</t>
+          <t>2025-12-02 08:22</t>
         </is>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46002.34861111111</v>
+        <v>45993.34861111111</v>
       </c>
       <c r="F323" t="b">
         <v>1</v>
@@ -18329,19 +18405,19 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Tuesday 3 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L323" s="1" t="n">
-        <v>46056.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N323" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="324">
@@ -18352,21 +18428,21 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 5</t>
+          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2025-12-12 08:22</t>
+          <t>2025-12-11 08:22</t>
         </is>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46003.34861111111</v>
+        <v>46002.34861111111</v>
       </c>
       <c r="F324" t="b">
         <v>1</v>
@@ -18379,15 +18455,15 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Tuesday 3 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L324" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46056.45833333334</v>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N324" s="1" t="n">
@@ -18402,21 +18478,21 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 6</t>
+          <t>Full ADOPT Grant: Round 5</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-12 08:22</t>
         </is>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46003.34861111111</v>
       </c>
       <c r="F325" t="b">
         <v>1</v>
@@ -18429,19 +18505,19 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L325" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N325" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="326">
@@ -18452,12 +18528,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
+          <t>ADOPT Facilitator Support Grant: Round 6</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -18479,15 +18555,15 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Thursday 7 May 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L326" s="1" t="n">
-        <v>46149.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N326" s="1" t="n">
@@ -18502,21 +18578,21 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – mid stage</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F327" t="b">
         <v>1</v>
@@ -18529,19 +18605,19 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Thursday 7 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L327" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N327" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="328">
@@ -18552,12 +18628,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – late stage</t>
+          <t>Energy catalyst round 11 – mid stage</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -18587,7 +18663,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N328" s="1" t="n">
@@ -18602,12 +18678,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – early stage</t>
+          <t>Energy catalyst round 11 – late stage</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -18637,7 +18713,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N329" s="1" t="n">
@@ -18652,12 +18728,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
+          <t>Energy catalyst round 11 – early stage</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -18679,15 +18755,15 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L330" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N330" s="1" t="n">
@@ -18702,12 +18778,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -18729,15 +18805,15 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L331" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N331" s="1" t="n">
@@ -18752,21 +18828,21 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 25</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-01-08 08:22</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46030.34861111111</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F332" t="b">
         <v>1</v>
@@ -18779,19 +18855,19 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L332" s="1" t="n">
-        <v>46085.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N332" s="1" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="333">
@@ -18802,21 +18878,21 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
+          <t>Innovate UK Innovation Loans Round 25</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-01-15 08:23</t>
+          <t>2026-01-08 08:22</t>
         </is>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46037.34930555556</v>
+        <v>46030.34861111111</v>
       </c>
       <c r="F333" t="b">
         <v>1</v>
@@ -18829,19 +18905,19 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Wednesday 11 February 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L333" s="1" t="n">
-        <v>46064.45833333334</v>
+        <v>46085.45833333334</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N333" s="1" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="334">
@@ -18852,21 +18928,21 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
+          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-01-20 08:24</t>
+          <t>2026-01-15 08:23</t>
         </is>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46042.35</v>
+        <v>46037.34930555556</v>
       </c>
       <c r="F334" t="b">
         <v>1</v>
@@ -18879,15 +18955,15 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 11 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L334" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46064.45833333334</v>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N334" s="1" t="n">
@@ -18902,21 +18978,21 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation FS</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-01-26 12:10</t>
+          <t>2026-01-20 08:24</t>
         </is>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46048.50694444445</v>
+        <v>46042.35</v>
       </c>
       <c r="F335" t="b">
         <v>1</v>
@@ -18929,19 +19005,19 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L335" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N335" s="1" t="n">
-        <v>46043</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="336">
@@ -18952,21 +19028,21 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
+          <t>Advanced manufacturing supply chain innovation FS</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-26 12:10</t>
         </is>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46048.50694444445</v>
       </c>
       <c r="F336" t="b">
         <v>1</v>
@@ -18979,19 +19055,19 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L336" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>£225,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N336" s="1" t="n">
-        <v>46050</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="337">
@@ -19002,12 +19078,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
+          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -19037,7 +19113,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£225,000</t>
         </is>
       </c>
       <c r="N337" s="1" t="n">
@@ -19052,21 +19128,21 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Robotics Adoption Programme skills development</t>
+          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-02-02 10:39</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46055.44375</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F338" t="b">
         <v>1</v>
@@ -19079,15 +19155,15 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L338" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N338" s="1" t="n">
@@ -19102,21 +19178,21 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
+          <t>Robotics Adoption Programme skills development</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-02-02 10:39</t>
         </is>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46055.44375</v>
       </c>
       <c r="F339" t="b">
         <v>1</v>
@@ -19129,15 +19205,15 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L339" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N339" s="1" t="n">
@@ -19152,12 +19228,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -19179,13 +19255,17 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L340" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M340" t="inlineStr"/>
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N340" s="1" t="n">
         <v>46050</v>
       </c>
@@ -19198,12 +19278,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -19244,21 +19324,21 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 6</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-02-09 10:53</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46062.45347222222</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F342" t="b">
         <v>1</v>
@@ -19271,19 +19351,15 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L342" s="1" t="n">
-        <v>46120.45833333334</v>
-      </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>£100,000</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M342" t="inlineStr"/>
       <c r="N342" s="1" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="343">
@@ -19294,21 +19370,21 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Zero Emission Flight Demonstrator Round 1</t>
+          <t>Full ADOPT Grant: Round 6</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-09 10:53</t>
         </is>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46062.45347222222</v>
       </c>
       <c r="F343" t="b">
         <v>1</v>
@@ -19321,19 +19397,19 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L343" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N343" s="1" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="344">
@@ -19344,12 +19420,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
+          <t>Zero Emission Flight Demonstrator Round 1</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -19371,15 +19447,15 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L344" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N344" s="1" t="n">
@@ -19394,12 +19470,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
+          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -19429,7 +19505,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>£10.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N345" s="1" t="n">
@@ -19444,21 +19520,21 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
+          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46066.44097222222</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F346" t="b">
         <v>1</v>
@@ -19471,15 +19547,15 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L346" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N346" s="1" t="n">
@@ -19494,21 +19570,21 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-02-17 10:40</t>
+          <t>2026-02-13 10:35</t>
         </is>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46070.44444444445</v>
+        <v>46066.44097222222</v>
       </c>
       <c r="F347" t="b">
         <v>1</v>
@@ -19529,7 +19605,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N347" s="1" t="n">
@@ -19544,21 +19620,21 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-17 10:40</t>
         </is>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46070.44444444445</v>
       </c>
       <c r="F348" t="b">
         <v>1</v>
@@ -19571,19 +19647,19 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L348" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N348" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="349">
@@ -19594,21 +19670,21 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>Semiconductors and components for smart electronic platforms</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-20 10:32</t>
         </is>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46073.43888888889</v>
       </c>
       <c r="F349" t="b">
         <v>1</v>
@@ -19621,15 +19697,15 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L349" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>£7.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N349" s="1" t="n">
@@ -19644,12 +19720,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>Robotics Adoption Hubs</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -19679,7 +19755,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£7.5 million</t>
         </is>
       </c>
       <c r="N350" s="1" t="n">
@@ -19694,21 +19770,21 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 7</t>
+          <t>Robotics Adoption Central Convening Body</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-02-26 10:40</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46079.44444444445</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F351" t="b">
         <v>1</v>
@@ -19721,19 +19797,19 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L351" s="1" t="n">
-        <v>46120.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N351" s="1" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="352">
@@ -19744,21 +19820,21 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-03-03 10:34</t>
+          <t>2026-02-26 10:40</t>
         </is>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46084.44027777778</v>
+        <v>46079.44444444445</v>
       </c>
       <c r="F352" t="b">
         <v>1</v>
@@ -19771,15 +19847,15 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L352" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N352" s="1" t="n">
@@ -19794,21 +19870,21 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
+          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-03-03 10:34</t>
         </is>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46084.44027777778</v>
       </c>
       <c r="F353" t="b">
         <v>1</v>
@@ -19821,19 +19897,19 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L353" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N353" s="1" t="n">
-        <v>46092</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="354">
@@ -19844,12 +19920,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
+          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -19879,7 +19955,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N354" s="1" t="n">
@@ -19894,12 +19970,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -19929,7 +20005,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>£15.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N355" s="1" t="n">
@@ -19944,21 +20020,21 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>AI Champions: Frontier AI Phase 1</t>
+          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-03-12 10:34</t>
+          <t>2026-03-11 10:34</t>
         </is>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46093.44027777778</v>
+        <v>46092.44027777778</v>
       </c>
       <c r="F356" t="b">
         <v>1</v>
@@ -19971,15 +20047,15 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Wednesday 29 April 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L356" s="1" t="n">
-        <v>46141.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£15.0 million</t>
         </is>
       </c>
       <c r="N356" s="1" t="n">
@@ -19994,21 +20070,21 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Frontier AI Discovery</t>
+          <t>AI Champions: Frontier AI Phase 1</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-03-17 10:45</t>
+          <t>2026-03-12 10:34</t>
         </is>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46098.44791666666</v>
+        <v>46093.44027777778</v>
       </c>
       <c r="F357" t="b">
         <v>1</v>
@@ -20021,15 +20097,15 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 29 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L357" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N357" s="1" t="n">
@@ -20044,12 +20120,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Secure Software for Resilient Growth</t>
+          <t>Frontier AI Discovery</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -20071,15 +20147,15 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Wednesday 29 April 2026 11:00am</t>
+          <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L358" s="1" t="n">
-        <v>46141.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N358" s="1" t="n">
@@ -20094,12 +20170,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
+          <t>Secure Software for Resilient Growth</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -20121,15 +20197,15 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Wednesday 22 April 2026 11:00am</t>
+          <t>Wednesday 29 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L359" s="1" t="n">
-        <v>46134.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N359" s="1" t="n">
@@ -20144,21 +20220,21 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Frontier AI Benchmarking Datasets</t>
+          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2424/overview/e618b7a8-ab7f-45f3-a098-57c01b334fcd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-03-23 10:49</t>
+          <t>2026-03-17 10:45</t>
         </is>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46104.45069444444</v>
+        <v>46098.44791666666</v>
       </c>
       <c r="F360" t="b">
         <v>1</v>
@@ -20171,19 +20247,19 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
+          <t>Wednesday 22 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L360" s="1" t="n">
-        <v>46169.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N360" s="1" t="n">
-        <v>46099</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="361">
@@ -20194,21 +20270,21 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Medicines Manufacturing: Labs of the Future</t>
+          <t>Frontier AI Benchmarking Datasets</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2417/overview/5ec76f19-8bd0-4dfa-b869-f4f0401448de</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2424/overview/e618b7a8-ab7f-45f3-a098-57c01b334fcd</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-03-24 10:47</t>
+          <t>2026-03-23 10:49</t>
         </is>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46105.44930555556</v>
+        <v>46104.45069444444</v>
       </c>
       <c r="F361" t="b">
         <v>1</v>
@@ -20229,7 +20305,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N361" s="1" t="n">
@@ -20244,12 +20320,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>AgriScale - Accelerating Agri-tech manufacturing: Industrial Research</t>
+          <t>Medicines Manufacturing: Labs of the Future</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2428/overview/85fd40be-646f-4b95-8a12-f881334d871d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2417/overview/5ec76f19-8bd0-4dfa-b869-f4f0401448de</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -20271,15 +20347,15 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L362" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N362" s="1" t="n">
@@ -20294,12 +20370,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>AgriScale - Accelerating Agri-tech manufacturing: Experimental Development</t>
+          <t>AgriScale - Accelerating Agri-tech manufacturing: Industrial Research</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2427/overview/cb071e4d-3a72-4d77-9350-b2ae3d50a79f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2428/overview/85fd40be-646f-4b95-8a12-f881334d871d</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -20329,7 +20405,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N363" s="1" t="n">
@@ -20344,21 +20420,21 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
+          <t>AgriScale - Accelerating Agri-tech manufacturing: Experimental Development</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2427/overview/cb071e4d-3a72-4d77-9350-b2ae3d50a79f</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-03-26 10:49</t>
+          <t>2026-03-24 10:47</t>
         </is>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46107.45069444444</v>
+        <v>46105.44930555556</v>
       </c>
       <c r="F364" t="b">
         <v>1</v>
@@ -20371,19 +20447,19 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L364" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>£60.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N364" s="1" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="365">
@@ -20394,12 +20470,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -20444,12 +20520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -20494,21 +20570,21 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms: applications with academic partners</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2441/overview/5ad05ad0-9f9a-47b7-8660-085608a668e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-03-27 10:43</t>
+          <t>2026-03-26 10:49</t>
         </is>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46108.44652777778</v>
+        <v>46107.45069444444</v>
       </c>
       <c r="F367" t="b">
         <v>1</v>
@@ -20521,15 +20597,15 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L367" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£60.0 million</t>
         </is>
       </c>
       <c r="N367" s="1" t="n">
@@ -20544,21 +20620,21 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: ProQure - Scaling UK Quantum Computing</t>
+          <t>Semiconductors and components for smart electronic platforms: applications with academic partners</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2439/overview/06423ffe-b763-4cac-b83b-f80208dfe2f2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2441/overview/5ad05ad0-9f9a-47b7-8660-085608a668e0</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-03-28 10:27</t>
+          <t>2026-03-27 10:43</t>
         </is>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46109.43541666667</v>
+        <v>46108.44652777778</v>
       </c>
       <c r="F368" t="b">
         <v>1</v>
@@ -20571,15 +20647,15 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>Friday 29 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L368" s="1" t="n">
-        <v>46171.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>£14.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N368" s="1" t="n">
@@ -20594,21 +20670,21 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: industrial research</t>
+          <t>Contracts for Innovation: ProQure - Scaling UK Quantum Computing</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2433/overview/4458acff-f0d2-4e2d-836c-c151ebd82a1d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2439/overview/06423ffe-b763-4cac-b83b-f80208dfe2f2</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-04-01 10:50</t>
+          <t>2026-03-28 10:27</t>
         </is>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46113.45138888889</v>
+        <v>46109.43541666667</v>
       </c>
       <c r="F369" t="b">
         <v>1</v>
@@ -20621,19 +20697,19 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Friday 29 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L369" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£14.0 million</t>
         </is>
       </c>
       <c r="N369" s="1" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="370">
@@ -20644,12 +20720,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: feasibility studies</t>
+          <t>Future offshore wind technologies: industrial research</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2432/overview/49f165f4-40af-4d16-8986-ba241fd2741a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2433/overview/4458acff-f0d2-4e2d-836c-c151ebd82a1d</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -20679,7 +20755,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N370" s="1" t="n">
@@ -20694,12 +20770,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Solution Development for Advanced Connectivity Technologies</t>
+          <t>Future offshore wind technologies: feasibility studies</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2420/overview/00926b83-c904-4919-b7d0-2be6e12269a0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2432/overview/49f165f4-40af-4d16-8986-ba241fd2741a</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -20721,15 +20797,15 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Wednesday 13 May 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L371" s="1" t="n">
-        <v>46155.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N371" s="1" t="n">
@@ -20744,12 +20820,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>CfI: Advanced Connectivity Technologies (ACT) – Call 1</t>
+          <t>Solution Development for Advanced Connectivity Technologies</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2437/overview/1123379f-9949-4cf0-acce-df748923a207</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2420/overview/00926b83-c904-4919-b7d0-2be6e12269a0</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -20771,15 +20847,15 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 13 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L372" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N372" s="1" t="n">
@@ -20794,21 +20870,21 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Enabling Commercial Quantum Networking</t>
+          <t>CfI: Advanced Connectivity Technologies (ACT) – Call 1</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2426/overview/4766704a-4888-49f8-b4f3-1e370e9ee0c5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2437/overview/1123379f-9949-4cf0-acce-df748923a207</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-04-07 10:51</t>
+          <t>2026-04-01 10:50</t>
         </is>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46119.45208333333</v>
+        <v>46113.45138888889</v>
       </c>
       <c r="F373" t="b">
         <v>1</v>
@@ -20821,15 +20897,15 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Wednesday 20 May 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L373" s="1" t="n">
-        <v>46162.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N373" s="1" t="n">
@@ -20844,21 +20920,21 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 7</t>
+          <t>Contracts for Innovation: Enabling Commercial Quantum Networking</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2442/overview/b9c07f24-e02d-4495-8351-0ed24aa9668d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2426/overview/4766704a-4888-49f8-b4f3-1e370e9ee0c5</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-04-09 10:54</t>
+          <t>2026-04-07 10:51</t>
         </is>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46121.45416666667</v>
+        <v>46119.45208333333</v>
       </c>
       <c r="F374" t="b">
         <v>1</v>
@@ -20871,19 +20947,19 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 20 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L374" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46162.45833333334</v>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N374" s="1" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="375">
@@ -20894,21 +20970,21 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Full ADOPT Grant: Round 7</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2442/overview/b9c07f24-e02d-4495-8351-0ed24aa9668d</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-04-11 10:30</t>
+          <t>2026-04-09 10:54</t>
         </is>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46123.4375</v>
+        <v>46121.45416666667</v>
       </c>
       <c r="F375" t="b">
         <v>1</v>
@@ -20921,13 +20997,15 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Wednesday 1 July 2026 12:00pm</t>
-        </is>
-      </c>
-      <c r="L375" t="inlineStr"/>
+          <t>Wednesday 3 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L375" s="1" t="n">
+        <v>46176.45833333334</v>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N375" s="1" t="n">
@@ -20942,21 +21020,21 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Battery innovation feasibility studies round 2</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2444/overview/b355177a-c85f-4cd6-b5b5-c4836d09df3e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-04-14 10:58</t>
+          <t>2026-04-11 10:30</t>
         </is>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46126.45694444444</v>
+        <v>46123.4375</v>
       </c>
       <c r="F376" t="b">
         <v>1</v>
@@ -20969,15 +21047,13 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L376" s="1" t="n">
-        <v>46169.45833333334</v>
-      </c>
+          <t>Wednesday 1 July 2026 12:00pm</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr"/>
       <c r="M376" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N376" s="1" t="n">
@@ -20992,12 +21068,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Battery innovation concept development round 2</t>
+          <t>Battery innovation feasibility studies round 2</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2443/overview/adca814a-3966-4fbb-afbe-a2ccbd4c3bae</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2444/overview/b355177a-c85f-4cd6-b5b5-c4836d09df3e</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -21027,7 +21103,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N377" s="1" t="n">
@@ -21042,21 +21118,21 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 8</t>
+          <t>Battery innovation concept development round 2</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2440/overview/630d8177-1633-413b-8c56-ad3fdcc8af82</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2443/overview/adca814a-3966-4fbb-afbe-a2ccbd4c3bae</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-04-15 10:55</t>
+          <t>2026-04-14 10:58</t>
         </is>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46127.45486111111</v>
+        <v>46126.45694444444</v>
       </c>
       <c r="F378" t="b">
         <v>1</v>
@@ -21077,11 +21153,11 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N378" s="1" t="n">
-        <v>46127</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="379">
@@ -21092,21 +21168,21 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Growth Cohorts: Next generation low carbon concrete cohort entry</t>
+          <t>ADOPT Facilitator Support Grant: Round 8</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2450/overview/261cbeea-5b87-4730-9fe9-4d04acc3725f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2440/overview/630d8177-1633-413b-8c56-ad3fdcc8af82</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-04-18 10:35</t>
+          <t>2026-04-15 10:55</t>
         </is>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46130.44097222222</v>
+        <v>46127.45486111111</v>
       </c>
       <c r="F379" t="b">
         <v>1</v>
@@ -21119,15 +21195,15 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L379" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N379" s="1" t="n">
@@ -21142,21 +21218,21 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 2</t>
+          <t>Growth Cohorts: Next generation low carbon concrete cohort entry</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2398/overview/318a8834-930f-4577-9069-26459a0def93</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2450/overview/261cbeea-5b87-4730-9fe9-4d04acc3725f</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-04-20 11:16</t>
+          <t>2026-04-18 10:35</t>
         </is>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46132.46944444445</v>
+        <v>46130.44097222222</v>
       </c>
       <c r="F380" t="b">
         <v>1</v>
@@ -21169,15 +21245,15 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L380" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N380" s="1" t="n">
@@ -21192,21 +21268,21 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation: CRD</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 2</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2453/overview/79b9483b-140e-44e9-86af-db7792c594d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2398/overview/318a8834-930f-4577-9069-26459a0def93</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-04-21 11:02</t>
+          <t>2026-04-20 11:16</t>
         </is>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46133.45972222222</v>
+        <v>46132.46944444445</v>
       </c>
       <c r="F381" t="b">
         <v>1</v>
@@ -21219,15 +21295,15 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 24 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L381" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46197.45833333334</v>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N381" s="1" t="n">
@@ -21242,21 +21318,21 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
+          <t>Advanced manufacturing supply chain innovation: CRD</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2457/overview/343a1d9f-29cb-4184-96bc-565bcfd09462</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2453/overview/79b9483b-140e-44e9-86af-db7792c594d2</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-04-22 11:00</t>
+          <t>2026-04-21 11:02</t>
         </is>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46134.45833333334</v>
+        <v>46133.45972222222</v>
       </c>
       <c r="F382" t="b">
         <v>1</v>
@@ -21269,13 +21345,19 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L382" t="inlineStr"/>
-      <c r="M382" t="inlineStr"/>
+          <t>Wednesday 10 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L382" s="1" t="n">
+        <v>46183.45833333334</v>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
       <c r="N382" s="1" t="n">
-        <v>46134</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="383">
@@ -21286,21 +21368,21 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
+          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2452/overview/df0addbf-9146-4b7f-b8b5-e78470917675</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2457/overview/343a1d9f-29cb-4184-96bc-565bcfd09462</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-04-23 11:03</t>
+          <t>2026-04-22 11:00</t>
         </is>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46135.46041666667</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="F383" t="b">
         <v>1</v>
@@ -21313,17 +21395,11 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L383" s="1" t="n">
-        <v>46183.45833333334</v>
-      </c>
-      <c r="M383" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr"/>
       <c r="N383" s="1" t="n">
         <v>46134</v>
       </c>
@@ -21336,21 +21412,21 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Dual-use aviation systems and autonomy</t>
+          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2467/overview/3ac02a1d-68e5-460b-bddb-0ecacdabfb00</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2452/overview/df0addbf-9146-4b7f-b8b5-e78470917675</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-04-28 11:42</t>
+          <t>2026-04-23 11:03</t>
         </is>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46140.4875</v>
+        <v>46135.46041666667</v>
       </c>
       <c r="F384" t="b">
         <v>1</v>
@@ -21363,15 +21439,15 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L384" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>£1.2 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N384" s="1" t="n">
@@ -21386,12 +21462,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Counter UAS Technologies</t>
+          <t>Dual-use aviation systems and autonomy</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2468/overview/6be7375d-717c-49b4-9411-f7709bb9e6ea</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2467/overview/3ac02a1d-68e5-460b-bddb-0ecacdabfb00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -21436,21 +21512,21 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility studies Rd 2</t>
+          <t>Counter UAS Technologies</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2469/overview/63ad7c49-77d4-4e13-b07f-0078c28d718e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2468/overview/6be7375d-717c-49b4-9411-f7709bb9e6ea</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-04-30 11:25</t>
+          <t>2026-04-28 11:42</t>
         </is>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46142.47569444445</v>
+        <v>46140.4875</v>
       </c>
       <c r="F386" t="b">
         <v>1</v>
@@ -21463,19 +21539,19 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L386" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.2 million</t>
         </is>
       </c>
       <c r="N386" s="1" t="n">
-        <v>46141</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="387">
@@ -21486,21 +21562,21 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>CfI: Boosting fathers’ engagement to improve child outcomes</t>
+          <t>National Materials Innovation Programme: Feasibility studies Rd 2</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2458/overview/bd6562cf-e556-4860-9348-663db48bb1a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2469/overview/63ad7c49-77d4-4e13-b07f-0078c28d718e</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-05-05 11:13</t>
+          <t>2026-04-30 11:25</t>
         </is>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46147.46736111111</v>
+        <v>46142.47569444445</v>
       </c>
       <c r="F387" t="b">
         <v>1</v>
@@ -21513,18 +21589,68 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
+          <t>Wednesday 24 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L387" s="1" t="n">
+        <v>46197.45833333334</v>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
+      <c r="N387" s="1" t="n">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>CfI: Boosting fathers’ engagement to improve child outcomes</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2458/overview/bd6562cf-e556-4860-9348-663db48bb1a8</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026-05-05 11:13</t>
+        </is>
+      </c>
+      <c r="E388" s="1" t="n">
+        <v>46147.46736111111</v>
+      </c>
+      <c r="F388" t="b">
+        <v>1</v>
+      </c>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="b">
+        <v>0</v>
+      </c>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
           <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
-      <c r="L387" s="1" t="n">
+      <c r="L388" s="1" t="n">
         <v>46183.45833333334</v>
       </c>
-      <c r="M387" t="inlineStr">
+      <c r="M388" t="inlineStr">
         <is>
           <t>£500,000</t>
         </is>
       </c>
-      <c r="N387" s="1" t="n">
+      <c r="N388" s="1" t="n">
         <v>46141</v>
       </c>
     </row>
@@ -21566,10 +21692,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3">
@@ -21592,10 +21718,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5">
